--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C273" s="9" t="inlineStr">
         <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
@@ -26013,7 +26013,7 @@
       </c>
       <c r="C463" s="9" t="inlineStr">
         <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D463" s="9" t="inlineStr">

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -4433,7 +4433,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H148" s="9" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H227" s="9" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H243" s="9" t="inlineStr">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="G256" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H256" s="9" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H260" s="9" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="G273" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H273" s="9" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="G274" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H274" s="9" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="G297" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H297" s="9" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="G299" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H299" s="9" t="inlineStr">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="G308" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H308" s="9" t="inlineStr">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="G346" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H346" s="9" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G412" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H412" s="9" t="inlineStr">
@@ -23921,7 +23921,7 @@
       </c>
       <c r="G419" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
@@ -24737,7 +24737,7 @@
       </c>
       <c r="G436" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H436" s="9" t="inlineStr">
@@ -25025,7 +25025,7 @@
       </c>
       <c r="G442" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H442" s="9" t="inlineStr">
@@ -25601,7 +25601,7 @@
       </c>
       <c r="G454" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H454" s="9" t="inlineStr">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="G463" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H463" s="9" t="inlineStr">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="G464" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H464" s="9" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H514" s="9" t="inlineStr">

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$7:$I$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'list'!$A$1:$J$559</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'list'!$A$1:$K$559</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -3806,7 +3806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J559"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -3818,6 +3818,7 @@
     <col width="14" customWidth="1" style="16" min="7" max="7"/>
     <col width="26" customWidth="1" style="16" min="8" max="8"/>
     <col width="16" customWidth="1" style="16" min="9" max="9"/>
+    <col width="42" customWidth="1" style="16" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="16">
@@ -3871,6 +3872,11 @@
           <t>CB approval</t>
         </is>
       </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>UoL module 2026/27 (current code)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="16">
       <c r="A2" s="10" t="inlineStr">
@@ -3919,6 +3925,11 @@
         </is>
       </c>
       <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="16">
       <c r="A3" s="10" t="inlineStr">
@@ -3967,6 +3978,11 @@
         </is>
       </c>
       <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="16">
       <c r="A4" s="10" t="inlineStr">
@@ -4015,6 +4031,11 @@
         </is>
       </c>
       <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="16">
       <c r="A5" s="10" t="inlineStr">
@@ -4063,6 +4084,11 @@
         </is>
       </c>
       <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="16">
       <c r="A6" s="10" t="inlineStr">
@@ -4111,6 +4137,11 @@
         </is>
       </c>
       <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="16">
       <c r="A7" s="9" t="inlineStr">
@@ -4159,6 +4190,11 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="16">
       <c r="A8" s="9" t="inlineStr">
@@ -4207,6 +4243,11 @@
         </is>
       </c>
       <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="16">
       <c r="A9" s="9" t="inlineStr">
@@ -4255,6 +4296,11 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="16">
       <c r="A10" s="9" t="inlineStr">
@@ -4303,6 +4349,11 @@
         </is>
       </c>
       <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="11" s="16">
       <c r="A11" s="9" t="inlineStr">
@@ -4351,6 +4402,11 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="16">
       <c r="A12" s="9" t="inlineStr">
@@ -4399,6 +4455,11 @@
         </is>
       </c>
       <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="16">
       <c r="A13" s="9" t="inlineStr">
@@ -4447,6 +4508,11 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="16">
       <c r="A14" s="9" t="inlineStr">
@@ -4495,6 +4561,11 @@
         </is>
       </c>
       <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="16">
       <c r="A15" s="9" t="inlineStr">
@@ -4543,6 +4614,11 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="16">
       <c r="A16" s="9" t="inlineStr">
@@ -4591,6 +4667,11 @@
         </is>
       </c>
       <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="16">
       <c r="A17" s="9" t="inlineStr">
@@ -4639,6 +4720,11 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="16">
       <c r="A18" s="9" t="inlineStr">
@@ -4687,6 +4773,11 @@
         </is>
       </c>
       <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="16">
       <c r="A19" s="9" t="inlineStr">
@@ -4735,6 +4826,11 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="16">
       <c r="A20" s="9" t="inlineStr">
@@ -4783,6 +4879,11 @@
         </is>
       </c>
       <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="16">
       <c r="A21" s="9" t="inlineStr">
@@ -4831,6 +4932,11 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="16">
       <c r="A22" s="9" t="inlineStr">
@@ -4879,6 +4985,11 @@
         </is>
       </c>
       <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="16">
       <c r="A23" s="9" t="inlineStr">
@@ -4927,6 +5038,11 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="16">
       <c r="A24" s="9" t="inlineStr">
@@ -4975,6 +5091,11 @@
         </is>
       </c>
       <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="16">
       <c r="A25" s="9" t="inlineStr">
@@ -5023,6 +5144,11 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="16">
       <c r="A26" s="9" t="inlineStr">
@@ -5071,6 +5197,11 @@
         </is>
       </c>
       <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="16">
       <c r="A27" s="9" t="inlineStr">
@@ -5119,6 +5250,11 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="45" customHeight="1" s="16">
       <c r="A28" s="9" t="inlineStr">
@@ -5167,6 +5303,11 @@
         </is>
       </c>
       <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="45" customHeight="1" s="16">
       <c r="A29" s="9" t="inlineStr">
@@ -5215,6 +5356,11 @@
         </is>
       </c>
       <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="45" customHeight="1" s="16">
       <c r="A30" s="9" t="inlineStr">
@@ -5263,6 +5409,11 @@
         </is>
       </c>
       <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="45" customHeight="1" s="16">
       <c r="A31" s="9" t="inlineStr">
@@ -5311,6 +5462,11 @@
         </is>
       </c>
       <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="45" customHeight="1" s="16">
       <c r="A32" s="9" t="inlineStr">
@@ -5359,6 +5515,11 @@
         </is>
       </c>
       <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="45" customHeight="1" s="16">
       <c r="A33" s="9" t="inlineStr">
@@ -5407,6 +5568,11 @@
         </is>
       </c>
       <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="16">
       <c r="A34" s="9" t="inlineStr">
@@ -5455,6 +5621,11 @@
         </is>
       </c>
       <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="16">
       <c r="A35" s="9" t="inlineStr">
@@ -5503,6 +5674,11 @@
         </is>
       </c>
       <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="16">
       <c r="A36" s="9" t="inlineStr">
@@ -5551,6 +5727,11 @@
         </is>
       </c>
       <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="16">
       <c r="A37" s="9" t="inlineStr">
@@ -5599,6 +5780,11 @@
         </is>
       </c>
       <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="16">
       <c r="A38" s="9" t="inlineStr">
@@ -5647,6 +5833,11 @@
         </is>
       </c>
       <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1" s="16">
       <c r="A39" s="9" t="inlineStr">
@@ -5695,6 +5886,11 @@
         </is>
       </c>
       <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1" s="16">
       <c r="A40" s="9" t="inlineStr">
@@ -5743,6 +5939,11 @@
         </is>
       </c>
       <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1" s="16">
       <c r="A41" s="9" t="inlineStr">
@@ -5791,6 +5992,11 @@
         </is>
       </c>
       <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1" s="16">
       <c r="A42" s="9" t="inlineStr">
@@ -5839,6 +6045,11 @@
         </is>
       </c>
       <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1" s="16">
       <c r="A43" s="9" t="inlineStr">
@@ -5887,6 +6098,11 @@
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1" s="16">
       <c r="A44" s="9" t="inlineStr">
@@ -5935,6 +6151,11 @@
         </is>
       </c>
       <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1" s="16">
       <c r="A45" s="9" t="inlineStr">
@@ -5983,6 +6204,11 @@
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1" s="16">
       <c r="A46" s="9" t="inlineStr">
@@ -6031,6 +6257,11 @@
         </is>
       </c>
       <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1" s="16">
       <c r="A47" s="9" t="inlineStr">
@@ -6079,6 +6310,11 @@
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1" s="16">
       <c r="A48" s="9" t="inlineStr">
@@ -6127,6 +6363,11 @@
         </is>
       </c>
       <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1" s="16">
       <c r="A49" s="9" t="inlineStr">
@@ -6175,6 +6416,11 @@
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="45" customHeight="1" s="16">
       <c r="A50" s="9" t="inlineStr">
@@ -6223,6 +6469,11 @@
         </is>
       </c>
       <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>ENVS282/286/288 Field Class (Belfast/Edinburgh/Glasgow) (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="45" customHeight="1" s="16">
       <c r="A51" s="9" t="inlineStr">
@@ -6271,6 +6522,11 @@
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="45" customHeight="1" s="16">
       <c r="A52" s="9" t="inlineStr">
@@ -6319,6 +6575,11 @@
         </is>
       </c>
       <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="45" customHeight="1" s="16">
       <c r="A53" s="9" t="inlineStr">
@@ -6367,6 +6628,11 @@
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="45" customHeight="1" s="16">
       <c r="A54" s="9" t="inlineStr">
@@ -6415,6 +6681,11 @@
         </is>
       </c>
       <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="45" customHeight="1" s="16">
       <c r="A55" s="9" t="inlineStr">
@@ -6463,6 +6734,11 @@
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="45" customHeight="1" s="16">
       <c r="A56" s="10" t="inlineStr">
@@ -6511,6 +6787,11 @@
         </is>
       </c>
       <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="45" customHeight="1" s="16">
       <c r="A57" s="9" t="inlineStr">
@@ -6559,6 +6840,11 @@
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="45" customHeight="1" s="16">
       <c r="A58" s="9" t="inlineStr">
@@ -6607,6 +6893,11 @@
         </is>
       </c>
       <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="45" customHeight="1" s="16">
       <c r="A59" s="9" t="inlineStr">
@@ -6655,6 +6946,11 @@
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="45" customHeight="1" s="16">
       <c r="A60" s="9" t="inlineStr">
@@ -6703,6 +6999,11 @@
         </is>
       </c>
       <c r="J60" s="9" t="n"/>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1" s="16">
       <c r="A61" s="9" t="inlineStr">
@@ -6751,6 +7052,11 @@
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1" s="16">
       <c r="A62" s="9" t="inlineStr">
@@ -6799,6 +7105,11 @@
         </is>
       </c>
       <c r="J62" s="9" t="n"/>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1" s="16">
       <c r="A63" s="9" t="inlineStr">
@@ -6847,6 +7158,11 @@
         </is>
       </c>
       <c r="J63" s="9" t="n"/>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1" s="16">
       <c r="A64" s="9" t="inlineStr">
@@ -6895,6 +7211,11 @@
         </is>
       </c>
       <c r="J64" s="9" t="n"/>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="30" customHeight="1" s="16">
       <c r="A65" s="9" t="inlineStr">
@@ -6943,6 +7264,11 @@
         </is>
       </c>
       <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1" s="16">
       <c r="A66" s="9" t="inlineStr">
@@ -6991,6 +7317,11 @@
         </is>
       </c>
       <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1" s="16">
       <c r="A67" s="9" t="inlineStr">
@@ -7039,6 +7370,11 @@
         </is>
       </c>
       <c r="J67" s="9" t="n"/>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1" s="16">
       <c r="A68" s="9" t="inlineStr">
@@ -7087,6 +7423,11 @@
         </is>
       </c>
       <c r="J68" s="9" t="n"/>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1" s="16">
       <c r="A69" s="9" t="inlineStr">
@@ -7135,6 +7476,11 @@
         </is>
       </c>
       <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1" s="16">
       <c r="A70" s="9" t="inlineStr">
@@ -7183,6 +7529,11 @@
         </is>
       </c>
       <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1" s="16">
       <c r="A71" s="9" t="inlineStr">
@@ -7231,6 +7582,11 @@
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1" s="16">
       <c r="A72" s="9" t="inlineStr">
@@ -7279,6 +7635,11 @@
         </is>
       </c>
       <c r="J72" s="9" t="n"/>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1" s="16">
       <c r="A73" s="9" t="inlineStr">
@@ -7327,6 +7688,11 @@
         </is>
       </c>
       <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1" s="16">
       <c r="A74" s="9" t="inlineStr">
@@ -7375,6 +7741,11 @@
         </is>
       </c>
       <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1" s="16">
       <c r="A75" s="9" t="inlineStr">
@@ -7423,6 +7794,11 @@
         </is>
       </c>
       <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="30" customHeight="1" s="16">
       <c r="A76" s="9" t="inlineStr">
@@ -7471,6 +7847,11 @@
         </is>
       </c>
       <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1" s="16">
       <c r="A77" s="9" t="inlineStr">
@@ -7519,6 +7900,11 @@
         </is>
       </c>
       <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="45" customHeight="1" s="16">
       <c r="A78" s="9" t="inlineStr">
@@ -7567,6 +7953,11 @@
         </is>
       </c>
       <c r="J78" s="9" t="n"/>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="45" customHeight="1" s="16">
       <c r="A79" s="9" t="inlineStr">
@@ -7615,6 +8006,11 @@
         </is>
       </c>
       <c r="J79" s="9" t="n"/>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="45" customHeight="1" s="16">
       <c r="A80" s="9" t="inlineStr">
@@ -7663,6 +8059,11 @@
         </is>
       </c>
       <c r="J80" s="9" t="n"/>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="45" customHeight="1" s="16">
       <c r="A81" s="10" t="inlineStr">
@@ -7711,6 +8112,11 @@
         </is>
       </c>
       <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="45" customHeight="1" s="16">
       <c r="A82" s="10" t="inlineStr">
@@ -7759,6 +8165,11 @@
         </is>
       </c>
       <c r="J82" s="10" t="n"/>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="60" customHeight="1" s="16">
       <c r="A83" s="11" t="inlineStr">
@@ -7807,6 +8218,11 @@
         </is>
       </c>
       <c r="J83" s="11" t="n"/>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="60" customHeight="1" s="16">
       <c r="A84" s="11" t="inlineStr">
@@ -7855,6 +8271,11 @@
         </is>
       </c>
       <c r="J84" s="11" t="n"/>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="60" customHeight="1" s="16">
       <c r="A85" s="10" t="inlineStr">
@@ -7903,6 +8324,11 @@
         </is>
       </c>
       <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="60" customHeight="1" s="16">
       <c r="A86" s="10" t="inlineStr">
@@ -7951,6 +8377,11 @@
         </is>
       </c>
       <c r="J86" s="10" t="n"/>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="60" customHeight="1" s="16">
       <c r="A87" s="10" t="inlineStr">
@@ -7999,6 +8430,11 @@
         </is>
       </c>
       <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="60" customHeight="1" s="16">
       <c r="A88" s="10" t="inlineStr">
@@ -8047,6 +8483,11 @@
         </is>
       </c>
       <c r="J88" s="10" t="n"/>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="60" customHeight="1" s="16">
       <c r="A89" s="10" t="inlineStr">
@@ -8095,6 +8536,11 @@
         </is>
       </c>
       <c r="J89" s="10" t="n"/>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="60" customHeight="1" s="16">
       <c r="A90" s="10" t="inlineStr">
@@ -8143,6 +8589,11 @@
         </is>
       </c>
       <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="60" customHeight="1" s="16">
       <c r="A91" s="10" t="inlineStr">
@@ -8191,6 +8642,11 @@
         </is>
       </c>
       <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="60" customHeight="1" s="16">
       <c r="A92" s="10" t="inlineStr">
@@ -8239,6 +8695,11 @@
         </is>
       </c>
       <c r="J92" s="10" t="n"/>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="60" customHeight="1" s="16">
       <c r="A93" s="9" t="inlineStr">
@@ -8287,6 +8748,11 @@
         </is>
       </c>
       <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="60" customHeight="1" s="16">
       <c r="A94" s="9" t="inlineStr">
@@ -8335,6 +8801,11 @@
         </is>
       </c>
       <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="60" customHeight="1" s="16">
       <c r="A95" s="9" t="inlineStr">
@@ -8383,6 +8854,11 @@
         </is>
       </c>
       <c r="J95" s="9" t="n"/>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="60" customHeight="1" s="16">
       <c r="A96" s="9" t="inlineStr">
@@ -8431,6 +8907,11 @@
         </is>
       </c>
       <c r="J96" s="9" t="n"/>
+      <c r="K96" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="60" customHeight="1" s="16">
       <c r="A97" s="9" t="inlineStr">
@@ -8479,6 +8960,11 @@
         </is>
       </c>
       <c r="J97" s="9" t="n"/>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="60" customHeight="1" s="16">
       <c r="A98" s="9" t="inlineStr">
@@ -8527,6 +9013,11 @@
         </is>
       </c>
       <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="60" customHeight="1" s="16">
       <c r="A99" s="9" t="inlineStr">
@@ -8575,6 +9066,11 @@
         </is>
       </c>
       <c r="J99" s="9" t="n"/>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="60" customHeight="1" s="16">
       <c r="A100" s="9" t="inlineStr">
@@ -8623,6 +9119,11 @@
         </is>
       </c>
       <c r="J100" s="9" t="n"/>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1" s="16">
       <c r="A101" s="9" t="inlineStr">
@@ -8671,6 +9172,11 @@
         </is>
       </c>
       <c r="J101" s="9" t="n"/>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="30" customHeight="1" s="16">
       <c r="A102" s="9" t="inlineStr">
@@ -8719,6 +9225,11 @@
         </is>
       </c>
       <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="103" s="16">
       <c r="A103" s="9" t="inlineStr">
@@ -8767,6 +9278,11 @@
         </is>
       </c>
       <c r="J103" s="9" t="n"/>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="104" s="16">
       <c r="A104" s="9" t="inlineStr">
@@ -8815,6 +9331,11 @@
         </is>
       </c>
       <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="30" customHeight="1" s="16">
       <c r="A105" s="9" t="inlineStr">
@@ -8863,6 +9384,11 @@
         </is>
       </c>
       <c r="J105" s="9" t="n"/>
+      <c r="K105" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="30" customHeight="1" s="16">
       <c r="A106" s="9" t="inlineStr">
@@ -8911,6 +9437,11 @@
         </is>
       </c>
       <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="107" s="16">
       <c r="A107" s="9" t="inlineStr">
@@ -8959,6 +9490,11 @@
         </is>
       </c>
       <c r="J107" s="9" t="n"/>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="108" s="16">
       <c r="A108" s="9" t="inlineStr">
@@ -9007,6 +9543,11 @@
         </is>
       </c>
       <c r="J108" s="9" t="n"/>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="109" s="16">
       <c r="A109" s="9" t="inlineStr">
@@ -9055,6 +9596,11 @@
         </is>
       </c>
       <c r="J109" s="9" t="n"/>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="110" s="16">
       <c r="A110" s="9" t="inlineStr">
@@ -9103,6 +9649,11 @@
         </is>
       </c>
       <c r="J110" s="9" t="n"/>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1" s="16">
       <c r="A111" s="9" t="inlineStr">
@@ -9151,6 +9702,11 @@
         </is>
       </c>
       <c r="J111" s="9" t="n"/>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="30" customHeight="1" s="16">
       <c r="A112" s="9" t="inlineStr">
@@ -9199,6 +9755,11 @@
         </is>
       </c>
       <c r="J112" s="9" t="n"/>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="113" s="16">
       <c r="A113" s="9" t="inlineStr">
@@ -9247,6 +9808,11 @@
         </is>
       </c>
       <c r="J113" s="9" t="n"/>
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="114" s="16">
       <c r="A114" s="9" t="inlineStr">
@@ -9295,6 +9861,11 @@
         </is>
       </c>
       <c r="J114" s="9" t="n"/>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="30" customHeight="1" s="16">
       <c r="A115" s="9" t="inlineStr">
@@ -9343,6 +9914,11 @@
         </is>
       </c>
       <c r="J115" s="9" t="n"/>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="116" s="16">
       <c r="A116" s="9" t="inlineStr">
@@ -9391,6 +9967,11 @@
         </is>
       </c>
       <c r="J116" s="9" t="n"/>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="117" s="16">
       <c r="A117" s="9" t="inlineStr">
@@ -9439,6 +10020,11 @@
         </is>
       </c>
       <c r="J117" s="9" t="n"/>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="118" s="16">
       <c r="A118" s="9" t="inlineStr">
@@ -9487,6 +10073,11 @@
         </is>
       </c>
       <c r="J118" s="9" t="n"/>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="30" customHeight="1" s="16">
       <c r="A119" s="9" t="inlineStr">
@@ -9535,6 +10126,11 @@
         </is>
       </c>
       <c r="J119" s="9" t="n"/>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="30" customHeight="1" s="16">
       <c r="A120" s="9" t="inlineStr">
@@ -9583,6 +10179,11 @@
         </is>
       </c>
       <c r="J120" s="9" t="n"/>
+      <c r="K120" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="30" customHeight="1" s="16">
       <c r="A121" s="9" t="inlineStr">
@@ -9631,6 +10232,11 @@
         </is>
       </c>
       <c r="J121" s="9" t="n"/>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="30" customHeight="1" s="16">
       <c r="A122" s="9" t="inlineStr">
@@ -9679,6 +10285,11 @@
         </is>
       </c>
       <c r="J122" s="9" t="n"/>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="30" customHeight="1" s="16">
       <c r="A123" s="9" t="inlineStr">
@@ -9727,6 +10338,11 @@
         </is>
       </c>
       <c r="J123" s="9" t="n"/>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1" s="16">
       <c r="A124" s="9" t="inlineStr">
@@ -9775,6 +10391,11 @@
         </is>
       </c>
       <c r="J124" s="9" t="n"/>
+      <c r="K124" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1" s="16">
       <c r="A125" s="9" t="inlineStr">
@@ -9823,6 +10444,11 @@
         </is>
       </c>
       <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="30" customHeight="1" s="16">
       <c r="A126" s="9" t="inlineStr">
@@ -9871,6 +10497,11 @@
         </is>
       </c>
       <c r="J126" s="9" t="n"/>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="30" customHeight="1" s="16">
       <c r="A127" s="9" t="inlineStr">
@@ -9919,6 +10550,11 @@
         </is>
       </c>
       <c r="J127" s="9" t="n"/>
+      <c r="K127" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="30" customHeight="1" s="16">
       <c r="A128" s="9" t="inlineStr">
@@ -9967,6 +10603,11 @@
         </is>
       </c>
       <c r="J128" s="9" t="n"/>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1" s="16">
       <c r="A129" s="9" t="inlineStr">
@@ -10015,6 +10656,11 @@
         </is>
       </c>
       <c r="J129" s="9" t="n"/>
+      <c r="K129" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="30" customHeight="1" s="16">
       <c r="A130" s="9" t="inlineStr">
@@ -10063,6 +10709,11 @@
         </is>
       </c>
       <c r="J130" s="9" t="n"/>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="30" customHeight="1" s="16">
       <c r="A131" s="9" t="inlineStr">
@@ -10111,6 +10762,11 @@
         </is>
       </c>
       <c r="J131" s="9" t="n"/>
+      <c r="K131" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="30" customHeight="1" s="16">
       <c r="A132" s="9" t="inlineStr">
@@ -10159,6 +10815,11 @@
         </is>
       </c>
       <c r="J132" s="9" t="n"/>
+      <c r="K132" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="30" customHeight="1" s="16">
       <c r="A133" s="9" t="inlineStr">
@@ -10207,6 +10868,11 @@
         </is>
       </c>
       <c r="J133" s="9" t="n"/>
+      <c r="K133" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="30" customHeight="1" s="16">
       <c r="A134" s="9" t="inlineStr">
@@ -10255,6 +10921,11 @@
         </is>
       </c>
       <c r="J134" s="9" t="n"/>
+      <c r="K134" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="30" customHeight="1" s="16">
       <c r="A135" s="9" t="inlineStr">
@@ -10303,6 +10974,11 @@
         </is>
       </c>
       <c r="J135" s="9" t="n"/>
+      <c r="K135" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="30" customHeight="1" s="16">
       <c r="A136" s="9" t="inlineStr">
@@ -10351,6 +11027,11 @@
         </is>
       </c>
       <c r="J136" s="9" t="n"/>
+      <c r="K136" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="30" customHeight="1" s="16">
       <c r="A137" s="9" t="inlineStr">
@@ -10399,6 +11080,11 @@
         </is>
       </c>
       <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="30" customHeight="1" s="16">
       <c r="A138" s="9" t="inlineStr">
@@ -10447,6 +11133,11 @@
         </is>
       </c>
       <c r="J138" s="9" t="n"/>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="30" customHeight="1" s="16">
       <c r="A139" s="9" t="inlineStr">
@@ -10495,6 +11186,11 @@
         </is>
       </c>
       <c r="J139" s="9" t="n"/>
+      <c r="K139" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="30" customHeight="1" s="16">
       <c r="A140" s="9" t="inlineStr">
@@ -10543,6 +11239,11 @@
         </is>
       </c>
       <c r="J140" s="9" t="n"/>
+      <c r="K140" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="30" customHeight="1" s="16">
       <c r="A141" s="9" t="inlineStr">
@@ -10591,6 +11292,11 @@
         </is>
       </c>
       <c r="J141" s="9" t="n"/>
+      <c r="K141" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="30" customHeight="1" s="16">
       <c r="A142" s="9" t="inlineStr">
@@ -10639,6 +11345,11 @@
         </is>
       </c>
       <c r="J142" s="9" t="n"/>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="30" customHeight="1" s="16">
       <c r="A143" s="9" t="inlineStr">
@@ -10687,6 +11398,11 @@
         </is>
       </c>
       <c r="J143" s="9" t="n"/>
+      <c r="K143" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="30" customHeight="1" s="16">
       <c r="A144" s="9" t="inlineStr">
@@ -10735,6 +11451,11 @@
         </is>
       </c>
       <c r="J144" s="9" t="n"/>
+      <c r="K144" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="30" customHeight="1" s="16">
       <c r="A145" s="9" t="inlineStr">
@@ -10783,6 +11504,11 @@
         </is>
       </c>
       <c r="J145" s="9" t="n"/>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="30" customHeight="1" s="16">
       <c r="A146" s="9" t="inlineStr">
@@ -10831,6 +11557,11 @@
         </is>
       </c>
       <c r="J146" s="9" t="n"/>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="30" customHeight="1" s="16">
       <c r="A147" s="9" t="inlineStr">
@@ -10879,6 +11610,11 @@
         </is>
       </c>
       <c r="J147" s="9" t="n"/>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="30" customHeight="1" s="16">
       <c r="A148" s="9" t="inlineStr">
@@ -10927,6 +11663,11 @@
         </is>
       </c>
       <c r="J148" s="9" t="n"/>
+      <c r="K148" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="30" customHeight="1" s="16">
       <c r="A149" s="9" t="inlineStr">
@@ -10975,6 +11716,11 @@
         </is>
       </c>
       <c r="J149" s="9" t="n"/>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="30" customHeight="1" s="16">
       <c r="A150" s="9" t="inlineStr">
@@ -11023,6 +11769,11 @@
         </is>
       </c>
       <c r="J150" s="9" t="n"/>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="30" customHeight="1" s="16">
       <c r="A151" s="9" t="inlineStr">
@@ -11071,6 +11822,11 @@
         </is>
       </c>
       <c r="J151" s="9" t="n"/>
+      <c r="K151" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="152" s="16">
       <c r="A152" s="9" t="inlineStr">
@@ -11119,6 +11875,11 @@
         </is>
       </c>
       <c r="J152" s="9" t="n"/>
+      <c r="K152" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="153" s="16">
       <c r="A153" s="9" t="inlineStr">
@@ -11167,6 +11928,11 @@
         </is>
       </c>
       <c r="J153" s="9" t="n"/>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="154" s="16">
       <c r="A154" s="9" t="inlineStr">
@@ -11215,6 +11981,11 @@
         </is>
       </c>
       <c r="J154" s="9" t="n"/>
+      <c r="K154" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="30" customHeight="1" s="16">
       <c r="A155" s="9" t="inlineStr">
@@ -11263,6 +12034,11 @@
         </is>
       </c>
       <c r="J155" s="9" t="n"/>
+      <c r="K155" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="30" customHeight="1" s="16">
       <c r="A156" s="9" t="inlineStr">
@@ -11311,6 +12087,11 @@
         </is>
       </c>
       <c r="J156" s="9" t="n"/>
+      <c r="K156" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="30" customHeight="1" s="16">
       <c r="A157" s="10" t="inlineStr">
@@ -11359,6 +12140,11 @@
         </is>
       </c>
       <c r="J157" s="10" t="n"/>
+      <c r="K157" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="30" customHeight="1" s="16">
       <c r="A158" s="9" t="inlineStr">
@@ -11407,6 +12193,11 @@
         </is>
       </c>
       <c r="J158" s="9" t="n"/>
+      <c r="K158" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="30" customHeight="1" s="16">
       <c r="A159" s="9" t="inlineStr">
@@ -11455,6 +12246,11 @@
         </is>
       </c>
       <c r="J159" s="9" t="n"/>
+      <c r="K159" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="30" customHeight="1" s="16">
       <c r="A160" s="9" t="inlineStr">
@@ -11503,6 +12299,11 @@
         </is>
       </c>
       <c r="J160" s="9" t="n"/>
+      <c r="K160" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="30" customHeight="1" s="16">
       <c r="A161" s="9" t="inlineStr">
@@ -11551,6 +12352,11 @@
         </is>
       </c>
       <c r="J161" s="9" t="n"/>
+      <c r="K161" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="30" customHeight="1" s="16">
       <c r="A162" s="9" t="inlineStr">
@@ -11599,6 +12405,11 @@
         </is>
       </c>
       <c r="J162" s="9" t="n"/>
+      <c r="K162" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="30" customHeight="1" s="16">
       <c r="A163" s="9" t="inlineStr">
@@ -11647,6 +12458,11 @@
         </is>
       </c>
       <c r="J163" s="9" t="n"/>
+      <c r="K163" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="75" customHeight="1" s="16">
       <c r="A164" s="9" t="inlineStr">
@@ -11695,6 +12511,11 @@
         </is>
       </c>
       <c r="J164" s="9" t="n"/>
+      <c r="K164" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="75" customHeight="1" s="16">
       <c r="A165" s="9" t="inlineStr">
@@ -11743,6 +12564,11 @@
         </is>
       </c>
       <c r="J165" s="9" t="n"/>
+      <c r="K165" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="30" customHeight="1" s="16">
       <c r="A166" s="9" t="inlineStr">
@@ -11791,6 +12617,11 @@
         </is>
       </c>
       <c r="J166" s="9" t="n"/>
+      <c r="K166" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="30" customHeight="1" s="16">
       <c r="A167" s="9" t="inlineStr">
@@ -11839,6 +12670,11 @@
         </is>
       </c>
       <c r="J167" s="9" t="n"/>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="30" customHeight="1" s="16">
       <c r="A168" s="9" t="inlineStr">
@@ -11887,6 +12723,11 @@
         </is>
       </c>
       <c r="J168" s="9" t="n"/>
+      <c r="K168" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="45" customHeight="1" s="16">
       <c r="A169" s="9" t="inlineStr">
@@ -11935,6 +12776,11 @@
         </is>
       </c>
       <c r="J169" s="9" t="n"/>
+      <c r="K169" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="45" customHeight="1" s="16">
       <c r="A170" s="9" t="inlineStr">
@@ -11983,6 +12829,11 @@
         </is>
       </c>
       <c r="J170" s="9" t="n"/>
+      <c r="K170" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="45" customHeight="1" s="16">
       <c r="A171" s="9" t="inlineStr">
@@ -12031,6 +12882,11 @@
         </is>
       </c>
       <c r="J171" s="9" t="n"/>
+      <c r="K171" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="45" customHeight="1" s="16">
       <c r="A172" s="9" t="inlineStr">
@@ -12079,6 +12935,11 @@
         </is>
       </c>
       <c r="J172" s="9" t="n"/>
+      <c r="K172" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="45" customHeight="1" s="16">
       <c r="A173" s="9" t="inlineStr">
@@ -12127,6 +12988,11 @@
         </is>
       </c>
       <c r="J173" s="9" t="n"/>
+      <c r="K173" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="45" customHeight="1" s="16">
       <c r="A174" s="9" t="inlineStr">
@@ -12175,6 +13041,11 @@
         </is>
       </c>
       <c r="J174" s="9" t="n"/>
+      <c r="K174" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="45" customHeight="1" s="16">
       <c r="A175" s="9" t="inlineStr">
@@ -12223,6 +13094,11 @@
         </is>
       </c>
       <c r="J175" s="9" t="n"/>
+      <c r="K175" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="45" customHeight="1" s="16">
       <c r="A176" s="9" t="inlineStr">
@@ -12271,6 +13147,11 @@
         </is>
       </c>
       <c r="J176" s="9" t="n"/>
+      <c r="K176" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="45" customHeight="1" s="16">
       <c r="A177" s="9" t="inlineStr">
@@ -12319,6 +13200,11 @@
         </is>
       </c>
       <c r="J177" s="9" t="n"/>
+      <c r="K177" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="45" customHeight="1" s="16">
       <c r="A178" s="9" t="inlineStr">
@@ -12367,6 +13253,11 @@
         </is>
       </c>
       <c r="J178" s="9" t="n"/>
+      <c r="K178" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="45" customHeight="1" s="16">
       <c r="A179" s="9" t="inlineStr">
@@ -12415,6 +13306,11 @@
         </is>
       </c>
       <c r="J179" s="9" t="n"/>
+      <c r="K179" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="45" customHeight="1" s="16">
       <c r="A180" s="9" t="inlineStr">
@@ -12463,6 +13359,11 @@
         </is>
       </c>
       <c r="J180" s="9" t="n"/>
+      <c r="K180" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="30" customHeight="1" s="16">
       <c r="A181" s="9" t="inlineStr">
@@ -12511,6 +13412,11 @@
         </is>
       </c>
       <c r="J181" s="9" t="n"/>
+      <c r="K181" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="30" customHeight="1" s="16">
       <c r="A182" s="9" t="inlineStr">
@@ -12559,6 +13465,11 @@
         </is>
       </c>
       <c r="J182" s="9" t="n"/>
+      <c r="K182" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="30" customHeight="1" s="16">
       <c r="A183" s="9" t="inlineStr">
@@ -12607,6 +13518,11 @@
         </is>
       </c>
       <c r="J183" s="9" t="n"/>
+      <c r="K183" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="30" customHeight="1" s="16">
       <c r="A184" s="9" t="inlineStr">
@@ -12655,6 +13571,11 @@
         </is>
       </c>
       <c r="J184" s="9" t="n"/>
+      <c r="K184" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="30" customHeight="1" s="16">
       <c r="A185" s="9" t="inlineStr">
@@ -12703,6 +13624,11 @@
         </is>
       </c>
       <c r="J185" s="9" t="n"/>
+      <c r="K185" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="30" customHeight="1" s="16">
       <c r="A186" s="9" t="inlineStr">
@@ -12751,6 +13677,11 @@
         </is>
       </c>
       <c r="J186" s="9" t="n"/>
+      <c r="K186" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="30" customHeight="1" s="16">
       <c r="A187" s="9" t="inlineStr">
@@ -12799,6 +13730,11 @@
         </is>
       </c>
       <c r="J187" s="9" t="n"/>
+      <c r="K187" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="30" customHeight="1" s="16">
       <c r="A188" s="9" t="inlineStr">
@@ -12847,6 +13783,11 @@
         </is>
       </c>
       <c r="J188" s="9" t="n"/>
+      <c r="K188" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="189" s="16">
       <c r="A189" s="9" t="inlineStr">
@@ -12895,6 +13836,11 @@
         </is>
       </c>
       <c r="J189" s="9" t="n"/>
+      <c r="K189" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="30" customHeight="1" s="16">
       <c r="A190" s="9" t="inlineStr">
@@ -12943,6 +13889,11 @@
         </is>
       </c>
       <c r="J190" s="9" t="n"/>
+      <c r="K190" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="30" customHeight="1" s="16">
       <c r="A191" s="9" t="inlineStr">
@@ -12991,6 +13942,11 @@
         </is>
       </c>
       <c r="J191" s="9" t="n"/>
+      <c r="K191" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="192" s="16">
       <c r="A192" s="9" t="inlineStr">
@@ -13039,6 +13995,11 @@
         </is>
       </c>
       <c r="J192" s="9" t="n"/>
+      <c r="K192" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="30" customHeight="1" s="16">
       <c r="A193" s="9" t="inlineStr">
@@ -13087,6 +14048,11 @@
         </is>
       </c>
       <c r="J193" s="9" t="n"/>
+      <c r="K193" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="30" customHeight="1" s="16">
       <c r="A194" s="9" t="inlineStr">
@@ -13135,6 +14101,11 @@
         </is>
       </c>
       <c r="J194" s="9" t="n"/>
+      <c r="K194" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="30" customHeight="1" s="16">
       <c r="A195" s="9" t="inlineStr">
@@ -13183,6 +14154,11 @@
         </is>
       </c>
       <c r="J195" s="9" t="n"/>
+      <c r="K195" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="30" customHeight="1" s="16">
       <c r="A196" s="9" t="inlineStr">
@@ -13231,6 +14207,11 @@
         </is>
       </c>
       <c r="J196" s="9" t="n"/>
+      <c r="K196" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="30" customHeight="1" s="16">
       <c r="A197" s="9" t="inlineStr">
@@ -13279,6 +14260,11 @@
         </is>
       </c>
       <c r="J197" s="9" t="n"/>
+      <c r="K197" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="30" customHeight="1" s="16">
       <c r="A198" s="9" t="inlineStr">
@@ -13327,6 +14313,11 @@
         </is>
       </c>
       <c r="J198" s="9" t="n"/>
+      <c r="K198" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="199" s="16">
       <c r="A199" s="9" t="inlineStr">
@@ -13375,6 +14366,11 @@
         </is>
       </c>
       <c r="J199" s="9" t="n"/>
+      <c r="K199" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="200" s="16">
       <c r="A200" s="9" t="inlineStr">
@@ -13423,6 +14419,11 @@
         </is>
       </c>
       <c r="J200" s="9" t="n"/>
+      <c r="K200" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="201" s="16">
       <c r="A201" s="9" t="inlineStr">
@@ -13471,6 +14472,11 @@
         </is>
       </c>
       <c r="J201" s="9" t="n"/>
+      <c r="K201" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="30" customHeight="1" s="16">
       <c r="A202" s="10" t="inlineStr">
@@ -13519,6 +14525,11 @@
         </is>
       </c>
       <c r="J202" s="10" t="n"/>
+      <c r="K202" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="30" customHeight="1" s="16">
       <c r="A203" s="10" t="inlineStr">
@@ -13567,6 +14578,11 @@
         </is>
       </c>
       <c r="J203" s="10" t="n"/>
+      <c r="K203" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="30" customHeight="1" s="16">
       <c r="A204" s="10" t="inlineStr">
@@ -13615,6 +14631,11 @@
         </is>
       </c>
       <c r="J204" s="10" t="n"/>
+      <c r="K204" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="30" customHeight="1" s="16">
       <c r="A205" s="10" t="inlineStr">
@@ -13663,6 +14684,11 @@
         </is>
       </c>
       <c r="J205" s="10" t="n"/>
+      <c r="K205" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="30" customHeight="1" s="16">
       <c r="A206" s="10" t="inlineStr">
@@ -13711,6 +14737,11 @@
         </is>
       </c>
       <c r="J206" s="10" t="n"/>
+      <c r="K206" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="30" customHeight="1" s="16">
       <c r="A207" s="10" t="inlineStr">
@@ -13759,6 +14790,11 @@
         </is>
       </c>
       <c r="J207" s="10" t="n"/>
+      <c r="K207" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="30" customHeight="1" s="16">
       <c r="A208" s="10" t="inlineStr">
@@ -13807,6 +14843,11 @@
         </is>
       </c>
       <c r="J208" s="10" t="n"/>
+      <c r="K208" s="10" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="30" customHeight="1" s="16">
       <c r="A209" s="10" t="inlineStr">
@@ -13855,6 +14896,11 @@
         </is>
       </c>
       <c r="J209" s="10" t="n"/>
+      <c r="K209" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="30" customHeight="1" s="16">
       <c r="A210" s="10" t="inlineStr">
@@ -13903,6 +14949,11 @@
         </is>
       </c>
       <c r="J210" s="10" t="n"/>
+      <c r="K210" s="10" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="30" customHeight="1" s="16">
       <c r="A211" s="10" t="inlineStr">
@@ -13951,6 +15002,11 @@
         </is>
       </c>
       <c r="J211" s="10" t="n"/>
+      <c r="K211" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="30" customHeight="1" s="16">
       <c r="A212" s="10" t="inlineStr">
@@ -13999,6 +15055,11 @@
         </is>
       </c>
       <c r="J212" s="10" t="n"/>
+      <c r="K212" s="10" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="30" customHeight="1" s="16">
       <c r="A213" s="10" t="inlineStr">
@@ -14047,6 +15108,11 @@
         </is>
       </c>
       <c r="J213" s="10" t="n"/>
+      <c r="K213" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="30" customHeight="1" s="16">
       <c r="A214" s="10" t="inlineStr">
@@ -14095,6 +15161,11 @@
         </is>
       </c>
       <c r="J214" s="10" t="n"/>
+      <c r="K214" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="30" customHeight="1" s="16">
       <c r="A215" s="10" t="inlineStr">
@@ -14143,6 +15214,11 @@
         </is>
       </c>
       <c r="J215" s="10" t="n"/>
+      <c r="K215" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="30" customHeight="1" s="16">
       <c r="A216" s="10" t="inlineStr">
@@ -14191,6 +15267,11 @@
         </is>
       </c>
       <c r="J216" s="10" t="n"/>
+      <c r="K216" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="30" customHeight="1" s="16">
       <c r="A217" s="10" t="inlineStr">
@@ -14239,6 +15320,11 @@
         </is>
       </c>
       <c r="J217" s="10" t="n"/>
+      <c r="K217" s="10" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="30" customHeight="1" s="16">
       <c r="A218" s="10" t="inlineStr">
@@ -14287,6 +15373,11 @@
         </is>
       </c>
       <c r="J218" s="10" t="n"/>
+      <c r="K218" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="30" customHeight="1" s="16">
       <c r="A219" s="9" t="inlineStr">
@@ -14335,6 +15426,11 @@
         </is>
       </c>
       <c r="J219" s="9" t="n"/>
+      <c r="K219" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="30" customHeight="1" s="16">
       <c r="A220" s="9" t="inlineStr">
@@ -14383,6 +15479,11 @@
         </is>
       </c>
       <c r="J220" s="9" t="n"/>
+      <c r="K220" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="30" customHeight="1" s="16">
       <c r="A221" s="9" t="inlineStr">
@@ -14431,6 +15532,11 @@
         </is>
       </c>
       <c r="J221" s="9" t="n"/>
+      <c r="K221" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="30" customHeight="1" s="16">
       <c r="A222" s="9" t="inlineStr">
@@ -14479,6 +15585,11 @@
         </is>
       </c>
       <c r="J222" s="9" t="n"/>
+      <c r="K222" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="30" customHeight="1" s="16">
       <c r="A223" s="9" t="inlineStr">
@@ -14527,6 +15638,11 @@
         </is>
       </c>
       <c r="J223" s="9" t="n"/>
+      <c r="K223" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="30" customHeight="1" s="16">
       <c r="A224" s="9" t="inlineStr">
@@ -14575,6 +15691,11 @@
         </is>
       </c>
       <c r="J224" s="9" t="n"/>
+      <c r="K224" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="30" customHeight="1" s="16">
       <c r="A225" s="9" t="inlineStr">
@@ -14623,6 +15744,11 @@
         </is>
       </c>
       <c r="J225" s="9" t="n"/>
+      <c r="K225" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="30" customHeight="1" s="16">
       <c r="A226" s="9" t="inlineStr">
@@ -14671,6 +15797,11 @@
         </is>
       </c>
       <c r="J226" s="9" t="n"/>
+      <c r="K226" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="30" customHeight="1" s="16">
       <c r="A227" s="9" t="inlineStr">
@@ -14719,6 +15850,11 @@
         </is>
       </c>
       <c r="J227" s="9" t="n"/>
+      <c r="K227" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="30" customHeight="1" s="16">
       <c r="A228" s="9" t="inlineStr">
@@ -14767,6 +15903,11 @@
         </is>
       </c>
       <c r="J228" s="9" t="n"/>
+      <c r="K228" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="30" customHeight="1" s="16">
       <c r="A229" s="9" t="inlineStr">
@@ -14815,6 +15956,11 @@
         </is>
       </c>
       <c r="J229" s="9" t="n"/>
+      <c r="K229" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="30" customHeight="1" s="16">
       <c r="A230" s="9" t="inlineStr">
@@ -14863,6 +16009,11 @@
         </is>
       </c>
       <c r="J230" s="9" t="n"/>
+      <c r="K230" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="30" customHeight="1" s="16">
       <c r="A231" s="9" t="inlineStr">
@@ -14911,6 +16062,11 @@
         </is>
       </c>
       <c r="J231" s="9" t="n"/>
+      <c r="K231" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="30" customHeight="1" s="16">
       <c r="A232" s="9" t="inlineStr">
@@ -14959,6 +16115,11 @@
         </is>
       </c>
       <c r="J232" s="9" t="n"/>
+      <c r="K232" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="30" customHeight="1" s="16">
       <c r="A233" s="9" t="inlineStr">
@@ -15007,6 +16168,11 @@
         </is>
       </c>
       <c r="J233" s="9" t="n"/>
+      <c r="K233" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="30" customHeight="1" s="16">
       <c r="A234" s="9" t="inlineStr">
@@ -15055,6 +16221,11 @@
         </is>
       </c>
       <c r="J234" s="9" t="n"/>
+      <c r="K234" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="45" customHeight="1" s="16">
       <c r="A235" s="9" t="inlineStr">
@@ -15103,6 +16274,11 @@
         </is>
       </c>
       <c r="J235" s="9" t="n"/>
+      <c r="K235" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="45" customHeight="1" s="16">
       <c r="A236" s="9" t="inlineStr">
@@ -15151,6 +16327,11 @@
         </is>
       </c>
       <c r="J236" s="9" t="n"/>
+      <c r="K236" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="45" customHeight="1" s="16">
       <c r="A237" s="9" t="inlineStr">
@@ -15199,6 +16380,11 @@
         </is>
       </c>
       <c r="J237" s="9" t="n"/>
+      <c r="K237" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="45" customHeight="1" s="16">
       <c r="A238" s="9" t="inlineStr">
@@ -15247,6 +16433,11 @@
         </is>
       </c>
       <c r="J238" s="9" t="n"/>
+      <c r="K238" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="45" customHeight="1" s="16">
       <c r="A239" s="9" t="inlineStr">
@@ -15295,6 +16486,11 @@
         </is>
       </c>
       <c r="J239" s="9" t="n"/>
+      <c r="K239" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="45" customHeight="1" s="16">
       <c r="A240" s="9" t="inlineStr">
@@ -15343,6 +16539,11 @@
         </is>
       </c>
       <c r="J240" s="9" t="n"/>
+      <c r="K240" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="45" customHeight="1" s="16">
       <c r="A241" s="9" t="inlineStr">
@@ -15391,6 +16592,11 @@
         </is>
       </c>
       <c r="J241" s="9" t="n"/>
+      <c r="K241" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="30" customHeight="1" s="16">
       <c r="A242" s="9" t="inlineStr">
@@ -15439,6 +16645,11 @@
         </is>
       </c>
       <c r="J242" s="9" t="n"/>
+      <c r="K242" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="30" customHeight="1" s="16">
       <c r="A243" s="9" t="inlineStr">
@@ -15487,6 +16698,11 @@
         </is>
       </c>
       <c r="J243" s="9" t="n"/>
+      <c r="K243" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="30" customHeight="1" s="16">
       <c r="A244" s="9" t="inlineStr">
@@ -15535,6 +16751,11 @@
         </is>
       </c>
       <c r="J244" s="9" t="n"/>
+      <c r="K244" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="30" customHeight="1" s="16">
       <c r="A245" s="9" t="inlineStr">
@@ -15583,6 +16804,11 @@
         </is>
       </c>
       <c r="J245" s="9" t="n"/>
+      <c r="K245" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="30" customHeight="1" s="16">
       <c r="A246" s="9" t="inlineStr">
@@ -15631,6 +16857,11 @@
         </is>
       </c>
       <c r="J246" s="9" t="n"/>
+      <c r="K246" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="30" customHeight="1" s="16">
       <c r="A247" s="9" t="inlineStr">
@@ -15679,6 +16910,11 @@
         </is>
       </c>
       <c r="J247" s="9" t="n"/>
+      <c r="K247" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="30" customHeight="1" s="16">
       <c r="A248" s="9" t="inlineStr">
@@ -15727,6 +16963,11 @@
         </is>
       </c>
       <c r="J248" s="9" t="n"/>
+      <c r="K248" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="30" customHeight="1" s="16">
       <c r="A249" s="9" t="inlineStr">
@@ -15775,6 +17016,11 @@
         </is>
       </c>
       <c r="J249" s="9" t="n"/>
+      <c r="K249" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="30" customHeight="1" s="16">
       <c r="A250" s="9" t="inlineStr">
@@ -15823,6 +17069,11 @@
         </is>
       </c>
       <c r="J250" s="9" t="n"/>
+      <c r="K250" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="45" customHeight="1" s="16">
       <c r="A251" s="9" t="inlineStr">
@@ -15871,6 +17122,11 @@
         </is>
       </c>
       <c r="J251" s="9" t="n"/>
+      <c r="K251" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="45" customHeight="1" s="16">
       <c r="A252" s="9" t="inlineStr">
@@ -15919,6 +17175,11 @@
         </is>
       </c>
       <c r="J252" s="9" t="n"/>
+      <c r="K252" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="45" customHeight="1" s="16">
       <c r="A253" s="9" t="inlineStr">
@@ -15967,6 +17228,11 @@
         </is>
       </c>
       <c r="J253" s="9" t="n"/>
+      <c r="K253" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="30" customHeight="1" s="16">
       <c r="A254" s="9" t="inlineStr">
@@ -16015,6 +17281,11 @@
         </is>
       </c>
       <c r="J254" s="9" t="n"/>
+      <c r="K254" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="30" customHeight="1" s="16">
       <c r="A255" s="9" t="inlineStr">
@@ -16063,6 +17334,11 @@
         </is>
       </c>
       <c r="J255" s="9" t="n"/>
+      <c r="K255" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="30" customHeight="1" s="16">
       <c r="A256" s="9" t="inlineStr">
@@ -16111,6 +17387,11 @@
         </is>
       </c>
       <c r="J256" s="9" t="n"/>
+      <c r="K256" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="30" customHeight="1" s="16">
       <c r="A257" s="9" t="inlineStr">
@@ -16159,6 +17440,11 @@
         </is>
       </c>
       <c r="J257" s="9" t="n"/>
+      <c r="K257" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="30" customHeight="1" s="16">
       <c r="A258" s="9" t="inlineStr">
@@ -16207,6 +17493,11 @@
         </is>
       </c>
       <c r="J258" s="9" t="n"/>
+      <c r="K258" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="30" customHeight="1" s="16">
       <c r="A259" s="9" t="inlineStr">
@@ -16255,6 +17546,11 @@
         </is>
       </c>
       <c r="J259" s="9" t="n"/>
+      <c r="K259" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="30" customHeight="1" s="16">
       <c r="A260" s="9" t="inlineStr">
@@ -16303,6 +17599,11 @@
         </is>
       </c>
       <c r="J260" s="9" t="n"/>
+      <c r="K260" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="30" customHeight="1" s="16">
       <c r="A261" s="9" t="inlineStr">
@@ -16351,6 +17652,11 @@
         </is>
       </c>
       <c r="J261" s="9" t="n"/>
+      <c r="K261" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="30" customHeight="1" s="16">
       <c r="A262" s="9" t="inlineStr">
@@ -16399,6 +17705,11 @@
         </is>
       </c>
       <c r="J262" s="9" t="n"/>
+      <c r="K262" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="30" customHeight="1" s="16">
       <c r="A263" s="9" t="inlineStr">
@@ -16447,6 +17758,11 @@
         </is>
       </c>
       <c r="J263" s="9" t="n"/>
+      <c r="K263" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="30" customHeight="1" s="16">
       <c r="A264" s="9" t="inlineStr">
@@ -16495,6 +17811,11 @@
         </is>
       </c>
       <c r="J264" s="9" t="n"/>
+      <c r="K264" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="30" customHeight="1" s="16">
       <c r="A265" s="9" t="inlineStr">
@@ -16543,6 +17864,11 @@
         </is>
       </c>
       <c r="J265" s="9" t="n"/>
+      <c r="K265" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="30" customHeight="1" s="16">
       <c r="A266" s="9" t="inlineStr">
@@ -16591,6 +17917,11 @@
         </is>
       </c>
       <c r="J266" s="9" t="n"/>
+      <c r="K266" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="30" customHeight="1" s="16">
       <c r="A267" s="9" t="inlineStr">
@@ -16639,6 +17970,11 @@
         </is>
       </c>
       <c r="J267" s="9" t="n"/>
+      <c r="K267" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="30" customHeight="1" s="16">
       <c r="A268" s="9" t="inlineStr">
@@ -16687,6 +18023,11 @@
         </is>
       </c>
       <c r="J268" s="9" t="n"/>
+      <c r="K268" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="30" customHeight="1" s="16">
       <c r="A269" s="9" t="inlineStr">
@@ -16735,6 +18076,11 @@
         </is>
       </c>
       <c r="J269" s="9" t="n"/>
+      <c r="K269" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="30" customHeight="1" s="16">
       <c r="A270" s="9" t="inlineStr">
@@ -16783,6 +18129,11 @@
         </is>
       </c>
       <c r="J270" s="9" t="n"/>
+      <c r="K270" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="30" customHeight="1" s="16">
       <c r="A271" s="9" t="inlineStr">
@@ -16831,6 +18182,11 @@
         </is>
       </c>
       <c r="J271" s="9" t="n"/>
+      <c r="K271" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="272" s="16">
       <c r="A272" s="9" t="inlineStr">
@@ -16879,6 +18235,11 @@
         </is>
       </c>
       <c r="J272" s="9" t="n"/>
+      <c r="K272" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="30" customHeight="1" s="16">
       <c r="A273" s="9" t="inlineStr">
@@ -16927,6 +18288,11 @@
         </is>
       </c>
       <c r="J273" s="9" t="n"/>
+      <c r="K273" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="30" customHeight="1" s="16">
       <c r="A274" s="9" t="inlineStr">
@@ -16975,6 +18341,11 @@
         </is>
       </c>
       <c r="J274" s="9" t="n"/>
+      <c r="K274" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="30" customHeight="1" s="16">
       <c r="A275" s="9" t="inlineStr">
@@ -17023,6 +18394,11 @@
         </is>
       </c>
       <c r="J275" s="9" t="n"/>
+      <c r="K275" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="75" customHeight="1" s="16">
       <c r="A276" s="9" t="inlineStr">
@@ -17071,6 +18447,11 @@
         </is>
       </c>
       <c r="J276" s="9" t="n"/>
+      <c r="K276" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="75" customHeight="1" s="16">
       <c r="A277" s="9" t="inlineStr">
@@ -17119,6 +18500,11 @@
         </is>
       </c>
       <c r="J277" s="9" t="n"/>
+      <c r="K277" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="45" customHeight="1" s="16">
       <c r="A278" s="9" t="inlineStr">
@@ -17167,6 +18553,11 @@
         </is>
       </c>
       <c r="J278" s="9" t="n"/>
+      <c r="K278" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="45" customHeight="1" s="16">
       <c r="A279" s="9" t="inlineStr">
@@ -17215,6 +18606,11 @@
         </is>
       </c>
       <c r="J279" s="9" t="n"/>
+      <c r="K279" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="45" customHeight="1" s="16">
       <c r="A280" s="9" t="inlineStr">
@@ -17263,6 +18659,11 @@
         </is>
       </c>
       <c r="J280" s="9" t="n"/>
+      <c r="K280" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="45" customHeight="1" s="16">
       <c r="A281" s="9" t="inlineStr">
@@ -17311,6 +18712,11 @@
         </is>
       </c>
       <c r="J281" s="9" t="n"/>
+      <c r="K281" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="45" customHeight="1" s="16">
       <c r="A282" s="9" t="inlineStr">
@@ -17359,6 +18765,11 @@
         </is>
       </c>
       <c r="J282" s="9" t="n"/>
+      <c r="K282" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="45" customHeight="1" s="16">
       <c r="A283" s="9" t="inlineStr">
@@ -17407,6 +18818,11 @@
         </is>
       </c>
       <c r="J283" s="9" t="n"/>
+      <c r="K283" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="30" customHeight="1" s="16">
       <c r="A284" s="9" t="inlineStr">
@@ -17455,6 +18871,11 @@
         </is>
       </c>
       <c r="J284" s="9" t="n"/>
+      <c r="K284" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="30" customHeight="1" s="16">
       <c r="A285" s="9" t="inlineStr">
@@ -17503,6 +18924,11 @@
         </is>
       </c>
       <c r="J285" s="9" t="n"/>
+      <c r="K285" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="30" customHeight="1" s="16">
       <c r="A286" s="9" t="inlineStr">
@@ -17551,6 +18977,11 @@
         </is>
       </c>
       <c r="J286" s="9" t="n"/>
+      <c r="K286" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="30" customHeight="1" s="16">
       <c r="A287" s="9" t="inlineStr">
@@ -17599,6 +19030,11 @@
         </is>
       </c>
       <c r="J287" s="9" t="n"/>
+      <c r="K287" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="30" customHeight="1" s="16">
       <c r="A288" s="9" t="inlineStr">
@@ -17647,6 +19083,11 @@
         </is>
       </c>
       <c r="J288" s="12" t="n"/>
+      <c r="K288" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="30" customHeight="1" s="16">
       <c r="A289" s="9" t="inlineStr">
@@ -17695,6 +19136,11 @@
         </is>
       </c>
       <c r="J289" s="12" t="n"/>
+      <c r="K289" s="12" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="30" customHeight="1" s="16">
       <c r="A290" s="11" t="inlineStr">
@@ -17743,6 +19189,11 @@
         </is>
       </c>
       <c r="J290" s="11" t="n"/>
+      <c r="K290" s="11" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="30" customHeight="1" s="16">
       <c r="A291" s="9" t="inlineStr">
@@ -17791,6 +19242,11 @@
         </is>
       </c>
       <c r="J291" s="12" t="n"/>
+      <c r="K291" s="12" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="30" customHeight="1" s="16">
       <c r="A292" s="9" t="inlineStr">
@@ -17839,6 +19295,11 @@
         </is>
       </c>
       <c r="J292" s="12" t="n"/>
+      <c r="K292" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="30" customHeight="1" s="16">
       <c r="A293" s="9" t="inlineStr">
@@ -17887,6 +19348,11 @@
         </is>
       </c>
       <c r="J293" s="9" t="n"/>
+      <c r="K293" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="30" customHeight="1" s="16">
       <c r="A294" s="9" t="inlineStr">
@@ -17935,6 +19401,11 @@
         </is>
       </c>
       <c r="J294" s="9" t="n"/>
+      <c r="K294" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="30" customHeight="1" s="16">
       <c r="A295" s="9" t="inlineStr">
@@ -17983,6 +19454,11 @@
         </is>
       </c>
       <c r="J295" s="9" t="n"/>
+      <c r="K295" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="30" customHeight="1" s="16">
       <c r="A296" s="9" t="inlineStr">
@@ -18031,6 +19507,11 @@
         </is>
       </c>
       <c r="J296" s="9" t="n"/>
+      <c r="K296" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="30" customHeight="1" s="16">
       <c r="A297" s="9" t="inlineStr">
@@ -18079,6 +19560,11 @@
         </is>
       </c>
       <c r="J297" s="9" t="n"/>
+      <c r="K297" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="30" customHeight="1" s="16">
       <c r="A298" s="9" t="inlineStr">
@@ -18127,6 +19613,11 @@
         </is>
       </c>
       <c r="J298" s="9" t="n"/>
+      <c r="K298" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="30" customHeight="1" s="16">
       <c r="A299" s="9" t="inlineStr">
@@ -18175,6 +19666,11 @@
         </is>
       </c>
       <c r="J299" s="9" t="n"/>
+      <c r="K299" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="30" customHeight="1" s="16">
       <c r="A300" s="9" t="inlineStr">
@@ -18223,6 +19719,11 @@
         </is>
       </c>
       <c r="J300" s="9" t="n"/>
+      <c r="K300" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="30" customHeight="1" s="16">
       <c r="A301" s="9" t="inlineStr">
@@ -18271,6 +19772,11 @@
         </is>
       </c>
       <c r="J301" s="9" t="n"/>
+      <c r="K301" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="30" customHeight="1" s="16">
       <c r="A302" s="9" t="inlineStr">
@@ -18319,6 +19825,11 @@
         </is>
       </c>
       <c r="J302" s="9" t="n"/>
+      <c r="K302" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="30" customHeight="1" s="16">
       <c r="A303" s="9" t="inlineStr">
@@ -18367,6 +19878,11 @@
         </is>
       </c>
       <c r="J303" s="9" t="n"/>
+      <c r="K303" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="30" customHeight="1" s="16">
       <c r="A304" s="9" t="inlineStr">
@@ -18415,6 +19931,11 @@
         </is>
       </c>
       <c r="J304" s="9" t="n"/>
+      <c r="K304" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="30" customHeight="1" s="16">
       <c r="A305" s="9" t="inlineStr">
@@ -18463,6 +19984,11 @@
         </is>
       </c>
       <c r="J305" s="9" t="n"/>
+      <c r="K305" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="30" customHeight="1" s="16">
       <c r="A306" s="9" t="inlineStr">
@@ -18511,6 +20037,11 @@
         </is>
       </c>
       <c r="J306" s="9" t="n"/>
+      <c r="K306" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="30" customHeight="1" s="16">
       <c r="A307" s="9" t="inlineStr">
@@ -18559,6 +20090,11 @@
         </is>
       </c>
       <c r="J307" s="9" t="n"/>
+      <c r="K307" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="30" customHeight="1" s="16">
       <c r="A308" s="9" t="inlineStr">
@@ -18607,6 +20143,11 @@
         </is>
       </c>
       <c r="J308" s="9" t="n"/>
+      <c r="K308" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="30" customHeight="1" s="16">
       <c r="A309" s="9" t="inlineStr">
@@ -18655,6 +20196,11 @@
         </is>
       </c>
       <c r="J309" s="9" t="n"/>
+      <c r="K309" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="30" customHeight="1" s="16">
       <c r="A310" s="9" t="inlineStr">
@@ -18703,6 +20249,11 @@
         </is>
       </c>
       <c r="J310" s="9" t="n"/>
+      <c r="K310" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="30" customHeight="1" s="16">
       <c r="A311" s="9" t="inlineStr">
@@ -18751,6 +20302,11 @@
         </is>
       </c>
       <c r="J311" s="9" t="n"/>
+      <c r="K311" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="30" customHeight="1" s="16">
       <c r="A312" s="9" t="inlineStr">
@@ -18799,6 +20355,11 @@
         </is>
       </c>
       <c r="J312" s="9" t="n"/>
+      <c r="K312" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="313" s="16">
       <c r="A313" s="9" t="inlineStr">
@@ -18847,6 +20408,11 @@
         </is>
       </c>
       <c r="J313" s="9" t="n"/>
+      <c r="K313" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="314" s="16">
       <c r="A314" s="9" t="inlineStr">
@@ -18895,6 +20461,11 @@
         </is>
       </c>
       <c r="J314" s="9" t="n"/>
+      <c r="K314" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="315" s="16">
       <c r="A315" s="9" t="inlineStr">
@@ -18943,6 +20514,11 @@
         </is>
       </c>
       <c r="J315" s="9" t="n"/>
+      <c r="K315" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="30" customHeight="1" s="16">
       <c r="A316" s="9" t="inlineStr">
@@ -18991,6 +20567,11 @@
         </is>
       </c>
       <c r="J316" s="9" t="n"/>
+      <c r="K316" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="30" customHeight="1" s="16">
       <c r="A317" s="9" t="inlineStr">
@@ -19039,6 +20620,11 @@
         </is>
       </c>
       <c r="J317" s="9" t="n"/>
+      <c r="K317" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="318" s="16">
       <c r="A318" s="9" t="inlineStr">
@@ -19087,6 +20673,11 @@
         </is>
       </c>
       <c r="J318" s="9" t="n"/>
+      <c r="K318" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="30" customHeight="1" s="16">
       <c r="A319" s="9" t="inlineStr">
@@ -19135,6 +20726,11 @@
         </is>
       </c>
       <c r="J319" s="9" t="n"/>
+      <c r="K319" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="30" customHeight="1" s="16">
       <c r="A320" s="9" t="inlineStr">
@@ -19183,6 +20779,11 @@
         </is>
       </c>
       <c r="J320" s="9" t="n"/>
+      <c r="K320" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="30" customHeight="1" s="16">
       <c r="A321" s="9" t="inlineStr">
@@ -19231,6 +20832,11 @@
         </is>
       </c>
       <c r="J321" s="9" t="n"/>
+      <c r="K321" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="30" customHeight="1" s="16">
       <c r="A322" s="9" t="inlineStr">
@@ -19279,6 +20885,11 @@
         </is>
       </c>
       <c r="J322" s="9" t="n"/>
+      <c r="K322" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="30" customHeight="1" s="16">
       <c r="A323" s="9" t="inlineStr">
@@ -19327,6 +20938,11 @@
         </is>
       </c>
       <c r="J323" s="9" t="n"/>
+      <c r="K323" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="30" customHeight="1" s="16">
       <c r="A324" s="9" t="inlineStr">
@@ -19375,6 +20991,11 @@
         </is>
       </c>
       <c r="J324" s="9" t="n"/>
+      <c r="K324" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="30" customHeight="1" s="16">
       <c r="A325" s="9" t="inlineStr">
@@ -19423,6 +21044,11 @@
         </is>
       </c>
       <c r="J325" s="9" t="n"/>
+      <c r="K325" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="30" customHeight="1" s="16">
       <c r="A326" s="9" t="inlineStr">
@@ -19471,6 +21097,11 @@
         </is>
       </c>
       <c r="J326" s="9" t="n"/>
+      <c r="K326" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="30" customHeight="1" s="16">
       <c r="A327" s="9" t="inlineStr">
@@ -19519,6 +21150,11 @@
         </is>
       </c>
       <c r="J327" s="9" t="n"/>
+      <c r="K327" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="30" customHeight="1" s="16">
       <c r="A328" s="9" t="inlineStr">
@@ -19567,6 +21203,11 @@
         </is>
       </c>
       <c r="J328" s="9" t="n"/>
+      <c r="K328" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="30" customHeight="1" s="16">
       <c r="A329" s="9" t="inlineStr">
@@ -19615,6 +21256,11 @@
         </is>
       </c>
       <c r="J329" s="9" t="n"/>
+      <c r="K329" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="30" customHeight="1" s="16">
       <c r="A330" s="9" t="inlineStr">
@@ -19663,6 +21309,11 @@
         </is>
       </c>
       <c r="J330" s="9" t="n"/>
+      <c r="K330" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="30" customHeight="1" s="16">
       <c r="A331" s="9" t="inlineStr">
@@ -19711,6 +21362,11 @@
         </is>
       </c>
       <c r="J331" s="9" t="n"/>
+      <c r="K331" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="30" customHeight="1" s="16">
       <c r="A332" s="9" t="inlineStr">
@@ -19759,6 +21415,11 @@
         </is>
       </c>
       <c r="J332" s="9" t="n"/>
+      <c r="K332" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="30" customHeight="1" s="16">
       <c r="A333" s="9" t="inlineStr">
@@ -19807,6 +21468,11 @@
         </is>
       </c>
       <c r="J333" s="9" t="n"/>
+      <c r="K333" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="30" customHeight="1" s="16">
       <c r="A334" s="9" t="inlineStr">
@@ -19855,6 +21521,11 @@
         </is>
       </c>
       <c r="J334" s="9" t="n"/>
+      <c r="K334" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="30" customHeight="1" s="16">
       <c r="A335" s="9" t="inlineStr">
@@ -19903,6 +21574,11 @@
         </is>
       </c>
       <c r="J335" s="9" t="n"/>
+      <c r="K335" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="30" customHeight="1" s="16">
       <c r="A336" s="9" t="inlineStr">
@@ -19951,6 +21627,11 @@
         </is>
       </c>
       <c r="J336" s="9" t="n"/>
+      <c r="K336" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="30" customHeight="1" s="16">
       <c r="A337" s="9" t="inlineStr">
@@ -19999,6 +21680,11 @@
         </is>
       </c>
       <c r="J337" s="9" t="n"/>
+      <c r="K337" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="30" customHeight="1" s="16">
       <c r="A338" s="9" t="inlineStr">
@@ -20047,6 +21733,11 @@
         </is>
       </c>
       <c r="J338" s="9" t="n"/>
+      <c r="K338" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="30" customHeight="1" s="16">
       <c r="A339" s="9" t="inlineStr">
@@ -20095,6 +21786,11 @@
         </is>
       </c>
       <c r="J339" s="9" t="n"/>
+      <c r="K339" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="30" customHeight="1" s="16">
       <c r="A340" s="9" t="inlineStr">
@@ -20143,6 +21839,11 @@
         </is>
       </c>
       <c r="J340" s="9" t="n"/>
+      <c r="K340" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="30" customHeight="1" s="16">
       <c r="A341" s="9" t="inlineStr">
@@ -20191,6 +21892,11 @@
         </is>
       </c>
       <c r="J341" s="9" t="n"/>
+      <c r="K341" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="30" customHeight="1" s="16">
       <c r="A342" s="9" t="inlineStr">
@@ -20239,6 +21945,11 @@
         </is>
       </c>
       <c r="J342" s="12" t="n"/>
+      <c r="K342" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="30" customHeight="1" s="16">
       <c r="A343" s="9" t="inlineStr">
@@ -20287,6 +21998,11 @@
         </is>
       </c>
       <c r="J343" s="9" t="n"/>
+      <c r="K343" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="30" customHeight="1" s="16">
       <c r="A344" s="9" t="inlineStr">
@@ -20335,6 +22051,11 @@
         </is>
       </c>
       <c r="J344" s="9" t="n"/>
+      <c r="K344" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="30" customHeight="1" s="16">
       <c r="A345" s="9" t="inlineStr">
@@ -20383,6 +22104,11 @@
         </is>
       </c>
       <c r="J345" s="9" t="n"/>
+      <c r="K345" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="30" customHeight="1" s="16">
       <c r="A346" s="9" t="inlineStr">
@@ -20431,6 +22157,11 @@
         </is>
       </c>
       <c r="J346" s="9" t="n"/>
+      <c r="K346" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="30" customHeight="1" s="16">
       <c r="A347" s="9" t="inlineStr">
@@ -20479,6 +22210,11 @@
         </is>
       </c>
       <c r="J347" s="9" t="n"/>
+      <c r="K347" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="30" customHeight="1" s="16">
       <c r="A348" s="9" t="inlineStr">
@@ -20527,6 +22263,11 @@
         </is>
       </c>
       <c r="J348" s="9" t="n"/>
+      <c r="K348" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="30" customHeight="1" s="16">
       <c r="A349" s="9" t="inlineStr">
@@ -20575,6 +22316,11 @@
         </is>
       </c>
       <c r="J349" s="9" t="n"/>
+      <c r="K349" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="30" customHeight="1" s="16">
       <c r="A350" s="9" t="inlineStr">
@@ -20623,6 +22369,11 @@
         </is>
       </c>
       <c r="J350" s="9" t="n"/>
+      <c r="K350" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="30" customHeight="1" s="16">
       <c r="A351" s="9" t="inlineStr">
@@ -20671,6 +22422,11 @@
         </is>
       </c>
       <c r="J351" s="9" t="n"/>
+      <c r="K351" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="30" customHeight="1" s="16">
       <c r="A352" s="9" t="inlineStr">
@@ -20719,6 +22475,11 @@
         </is>
       </c>
       <c r="J352" s="9" t="n"/>
+      <c r="K352" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="30" customHeight="1" s="16">
       <c r="A353" s="9" t="inlineStr">
@@ -20767,6 +22528,11 @@
         </is>
       </c>
       <c r="J353" s="9" t="n"/>
+      <c r="K353" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="30" customHeight="1" s="16">
       <c r="A354" s="9" t="inlineStr">
@@ -20815,6 +22581,11 @@
         </is>
       </c>
       <c r="J354" s="9" t="n"/>
+      <c r="K354" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="30" customHeight="1" s="16">
       <c r="A355" s="9" t="inlineStr">
@@ -20863,6 +22634,11 @@
         </is>
       </c>
       <c r="J355" s="9" t="n"/>
+      <c r="K355" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="30" customHeight="1" s="16">
       <c r="A356" s="9" t="inlineStr">
@@ -20911,6 +22687,11 @@
         </is>
       </c>
       <c r="J356" s="9" t="n"/>
+      <c r="K356" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="30" customHeight="1" s="16">
       <c r="A357" s="9" t="inlineStr">
@@ -20959,6 +22740,11 @@
         </is>
       </c>
       <c r="J357" s="9" t="n"/>
+      <c r="K357" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="30" customHeight="1" s="16">
       <c r="A358" s="9" t="inlineStr">
@@ -21007,6 +22793,11 @@
         </is>
       </c>
       <c r="J358" s="9" t="n"/>
+      <c r="K358" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="45" customHeight="1" s="16">
       <c r="A359" s="10" t="inlineStr">
@@ -21055,6 +22846,11 @@
         </is>
       </c>
       <c r="J359" s="10" t="n"/>
+      <c r="K359" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="30" customHeight="1" s="16">
       <c r="A360" s="10" t="inlineStr">
@@ -21103,6 +22899,11 @@
         </is>
       </c>
       <c r="J360" s="10" t="n"/>
+      <c r="K360" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="30" customHeight="1" s="16">
       <c r="A361" s="10" t="inlineStr">
@@ -21151,6 +22952,11 @@
         </is>
       </c>
       <c r="J361" s="10" t="n"/>
+      <c r="K361" s="10" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="30" customHeight="1" s="16">
       <c r="A362" s="10" t="inlineStr">
@@ -21199,6 +23005,11 @@
         </is>
       </c>
       <c r="J362" s="10" t="n"/>
+      <c r="K362" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="30" customHeight="1" s="16">
       <c r="A363" s="10" t="inlineStr">
@@ -21247,6 +23058,11 @@
         </is>
       </c>
       <c r="J363" s="10" t="n"/>
+      <c r="K363" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="30" customHeight="1" s="16">
       <c r="A364" s="10" t="inlineStr">
@@ -21295,6 +23111,11 @@
         </is>
       </c>
       <c r="J364" s="10" t="n"/>
+      <c r="K364" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="30" customHeight="1" s="16">
       <c r="A365" s="10" t="inlineStr">
@@ -21343,6 +23164,11 @@
         </is>
       </c>
       <c r="J365" s="10" t="n"/>
+      <c r="K365" s="10" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="30" customHeight="1" s="16">
       <c r="A366" s="10" t="inlineStr">
@@ -21391,6 +23217,11 @@
         </is>
       </c>
       <c r="J366" s="10" t="n"/>
+      <c r="K366" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="30" customHeight="1" s="16">
       <c r="A367" s="10" t="inlineStr">
@@ -21439,6 +23270,11 @@
         </is>
       </c>
       <c r="J367" s="10" t="n"/>
+      <c r="K367" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="30" customHeight="1" s="16">
       <c r="A368" s="10" t="inlineStr">
@@ -21487,6 +23323,11 @@
         </is>
       </c>
       <c r="J368" s="10" t="n"/>
+      <c r="K368" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="30" customHeight="1" s="16">
       <c r="A369" s="10" t="inlineStr">
@@ -21535,6 +23376,11 @@
         </is>
       </c>
       <c r="J369" s="10" t="n"/>
+      <c r="K369" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="30" customHeight="1" s="16">
       <c r="A370" s="10" t="inlineStr">
@@ -21583,6 +23429,11 @@
         </is>
       </c>
       <c r="J370" s="10" t="n"/>
+      <c r="K370" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="30" customHeight="1" s="16">
       <c r="A371" s="10" t="inlineStr">
@@ -21631,6 +23482,11 @@
         </is>
       </c>
       <c r="J371" s="10" t="n"/>
+      <c r="K371" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="30" customHeight="1" s="16">
       <c r="A372" s="10" t="inlineStr">
@@ -21679,6 +23535,11 @@
         </is>
       </c>
       <c r="J372" s="10" t="n"/>
+      <c r="K372" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="30" customHeight="1" s="16">
       <c r="A373" s="10" t="inlineStr">
@@ -21727,6 +23588,11 @@
         </is>
       </c>
       <c r="J373" s="10" t="n"/>
+      <c r="K373" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="30" customHeight="1" s="16">
       <c r="A374" s="10" t="inlineStr">
@@ -21775,6 +23641,11 @@
         </is>
       </c>
       <c r="J374" s="10" t="n"/>
+      <c r="K374" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="30" customHeight="1" s="16">
       <c r="A375" s="10" t="inlineStr">
@@ -21823,6 +23694,11 @@
         </is>
       </c>
       <c r="J375" s="10" t="n"/>
+      <c r="K375" s="10" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="30" customHeight="1" s="16">
       <c r="A376" s="10" t="inlineStr">
@@ -21871,6 +23747,11 @@
         </is>
       </c>
       <c r="J376" s="10" t="n"/>
+      <c r="K376" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="30" customHeight="1" s="16">
       <c r="A377" s="10" t="inlineStr">
@@ -21919,6 +23800,11 @@
         </is>
       </c>
       <c r="J377" s="10" t="n"/>
+      <c r="K377" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="30" customHeight="1" s="16">
       <c r="A378" s="10" t="inlineStr">
@@ -21967,6 +23853,11 @@
         </is>
       </c>
       <c r="J378" s="10" t="n"/>
+      <c r="K378" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="30" customHeight="1" s="16">
       <c r="A379" s="10" t="inlineStr">
@@ -22015,6 +23906,11 @@
         </is>
       </c>
       <c r="J379" s="10" t="n"/>
+      <c r="K379" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="30" customHeight="1" s="16">
       <c r="A380" s="10" t="inlineStr">
@@ -22063,6 +23959,11 @@
         </is>
       </c>
       <c r="J380" s="10" t="n"/>
+      <c r="K380" s="10" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="30" customHeight="1" s="16">
       <c r="A381" s="10" t="inlineStr">
@@ -22111,6 +24012,11 @@
         </is>
       </c>
       <c r="J381" s="10" t="n"/>
+      <c r="K381" s="10" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="30" customHeight="1" s="16">
       <c r="A382" s="10" t="inlineStr">
@@ -22159,6 +24065,11 @@
         </is>
       </c>
       <c r="J382" s="10" t="n"/>
+      <c r="K382" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="30" customHeight="1" s="16">
       <c r="A383" s="10" t="inlineStr">
@@ -22207,6 +24118,11 @@
         </is>
       </c>
       <c r="J383" s="10" t="n"/>
+      <c r="K383" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="30" customHeight="1" s="16">
       <c r="A384" s="10" t="inlineStr">
@@ -22255,6 +24171,11 @@
         </is>
       </c>
       <c r="J384" s="10" t="n"/>
+      <c r="K384" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="30" customHeight="1" s="16">
       <c r="A385" s="10" t="inlineStr">
@@ -22303,6 +24224,11 @@
         </is>
       </c>
       <c r="J385" s="10" t="n"/>
+      <c r="K385" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="30" customHeight="1" s="16">
       <c r="A386" s="10" t="inlineStr">
@@ -22351,6 +24277,11 @@
         </is>
       </c>
       <c r="J386" s="10" t="n"/>
+      <c r="K386" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="30" customHeight="1" s="16">
       <c r="A387" s="10" t="inlineStr">
@@ -22399,6 +24330,11 @@
         </is>
       </c>
       <c r="J387" s="10" t="n"/>
+      <c r="K387" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="30" customHeight="1" s="16">
       <c r="A388" s="9" t="inlineStr">
@@ -22447,6 +24383,11 @@
         </is>
       </c>
       <c r="J388" s="9" t="n"/>
+      <c r="K388" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="30" customHeight="1" s="16">
       <c r="A389" s="9" t="inlineStr">
@@ -22495,6 +24436,11 @@
         </is>
       </c>
       <c r="J389" s="9" t="n"/>
+      <c r="K389" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="30" customHeight="1" s="16">
       <c r="A390" s="9" t="inlineStr">
@@ -22543,6 +24489,11 @@
         </is>
       </c>
       <c r="J390" s="9" t="n"/>
+      <c r="K390" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="30" customHeight="1" s="16">
       <c r="A391" s="9" t="inlineStr">
@@ -22591,6 +24542,11 @@
         </is>
       </c>
       <c r="J391" s="9" t="n"/>
+      <c r="K391" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="30" customHeight="1" s="16">
       <c r="A392" s="9" t="inlineStr">
@@ -22639,6 +24595,11 @@
         </is>
       </c>
       <c r="J392" s="9" t="n"/>
+      <c r="K392" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="30" customHeight="1" s="16">
       <c r="A393" s="9" t="inlineStr">
@@ -22687,6 +24648,11 @@
         </is>
       </c>
       <c r="J393" s="9" t="n"/>
+      <c r="K393" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="30" customHeight="1" s="16">
       <c r="A394" s="9" t="inlineStr">
@@ -22735,6 +24701,11 @@
         </is>
       </c>
       <c r="J394" s="9" t="n"/>
+      <c r="K394" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="30" customHeight="1" s="16">
       <c r="A395" s="9" t="inlineStr">
@@ -22783,6 +24754,11 @@
         </is>
       </c>
       <c r="J395" s="9" t="n"/>
+      <c r="K395" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="30" customHeight="1" s="16">
       <c r="A396" s="9" t="inlineStr">
@@ -22831,6 +24807,11 @@
         </is>
       </c>
       <c r="J396" s="9" t="n"/>
+      <c r="K396" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="30" customHeight="1" s="16">
       <c r="A397" s="9" t="inlineStr">
@@ -22879,6 +24860,11 @@
         </is>
       </c>
       <c r="J397" s="9" t="n"/>
+      <c r="K397" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="30" customHeight="1" s="16">
       <c r="A398" s="9" t="inlineStr">
@@ -22927,6 +24913,11 @@
         </is>
       </c>
       <c r="J398" s="9" t="n"/>
+      <c r="K398" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="30" customHeight="1" s="16">
       <c r="A399" s="9" t="inlineStr">
@@ -22975,6 +24966,11 @@
         </is>
       </c>
       <c r="J399" s="9" t="n"/>
+      <c r="K399" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="30" customHeight="1" s="16">
       <c r="A400" s="9" t="inlineStr">
@@ -23023,6 +25019,11 @@
         </is>
       </c>
       <c r="J400" s="9" t="n"/>
+      <c r="K400" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="30" customHeight="1" s="16">
       <c r="A401" s="9" t="inlineStr">
@@ -23071,6 +25072,11 @@
         </is>
       </c>
       <c r="J401" s="12" t="n"/>
+      <c r="K401" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="402" s="16">
       <c r="A402" s="9" t="inlineStr">
@@ -23119,6 +25125,11 @@
         </is>
       </c>
       <c r="J402" s="12" t="n"/>
+      <c r="K402" s="12" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="30" customHeight="1" s="16">
       <c r="A403" s="9" t="inlineStr">
@@ -23167,6 +25178,11 @@
         </is>
       </c>
       <c r="J403" s="9" t="n"/>
+      <c r="K403" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="404" s="16">
       <c r="A404" s="9" t="inlineStr">
@@ -23215,6 +25231,11 @@
         </is>
       </c>
       <c r="J404" s="12" t="n"/>
+      <c r="K404" s="12" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="405" s="16">
       <c r="A405" s="9" t="inlineStr">
@@ -23263,6 +25284,11 @@
         </is>
       </c>
       <c r="J405" s="12" t="n"/>
+      <c r="K405" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="30" customHeight="1" s="16">
       <c r="A406" s="9" t="inlineStr">
@@ -23311,6 +25337,11 @@
         </is>
       </c>
       <c r="J406" s="9" t="n"/>
+      <c r="K406" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="30" customHeight="1" s="16">
       <c r="A407" s="9" t="inlineStr">
@@ -23359,6 +25390,11 @@
         </is>
       </c>
       <c r="J407" s="9" t="n"/>
+      <c r="K407" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="30" customHeight="1" s="16">
       <c r="A408" s="9" t="inlineStr">
@@ -23407,6 +25443,11 @@
         </is>
       </c>
       <c r="J408" s="9" t="n"/>
+      <c r="K408" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="30" customHeight="1" s="16">
       <c r="A409" s="9" t="inlineStr">
@@ -23455,6 +25496,11 @@
         </is>
       </c>
       <c r="J409" s="9" t="n"/>
+      <c r="K409" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="30" customHeight="1" s="16">
       <c r="A410" s="9" t="inlineStr">
@@ -23503,6 +25549,11 @@
         </is>
       </c>
       <c r="J410" s="9" t="n"/>
+      <c r="K410" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="30" customHeight="1" s="16">
       <c r="A411" s="9" t="inlineStr">
@@ -23551,6 +25602,11 @@
         </is>
       </c>
       <c r="J411" s="9" t="n"/>
+      <c r="K411" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="30" customHeight="1" s="16">
       <c r="A412" s="9" t="inlineStr">
@@ -23599,6 +25655,11 @@
         </is>
       </c>
       <c r="J412" s="9" t="n"/>
+      <c r="K412" s="9" t="inlineStr">
+        <is>
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="30" customHeight="1" s="16">
       <c r="A413" s="9" t="inlineStr">
@@ -23647,6 +25708,11 @@
         </is>
       </c>
       <c r="J413" s="9" t="n"/>
+      <c r="K413" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="30" customHeight="1" s="16">
       <c r="A414" s="9" t="inlineStr">
@@ -23695,6 +25761,11 @@
         </is>
       </c>
       <c r="J414" s="9" t="n"/>
+      <c r="K414" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="30" customHeight="1" s="16">
       <c r="A415" s="9" t="inlineStr">
@@ -23743,6 +25814,11 @@
         </is>
       </c>
       <c r="J415" s="9" t="n"/>
+      <c r="K415" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="30" customHeight="1" s="16">
       <c r="A416" s="9" t="inlineStr">
@@ -23791,6 +25867,11 @@
         </is>
       </c>
       <c r="J416" s="9" t="n"/>
+      <c r="K416" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="30" customHeight="1" s="16">
       <c r="A417" s="9" t="inlineStr">
@@ -23839,6 +25920,11 @@
         </is>
       </c>
       <c r="J417" s="9" t="n"/>
+      <c r="K417" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="30" customHeight="1" s="16">
       <c r="A418" s="9" t="inlineStr">
@@ -23887,6 +25973,11 @@
         </is>
       </c>
       <c r="J418" s="9" t="n"/>
+      <c r="K418" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="30" customHeight="1" s="16">
       <c r="A419" s="9" t="inlineStr">
@@ -23935,6 +26026,11 @@
         </is>
       </c>
       <c r="J419" s="9" t="n"/>
+      <c r="K419" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="30" customHeight="1" s="16">
       <c r="A420" s="9" t="inlineStr">
@@ -23983,6 +26079,11 @@
         </is>
       </c>
       <c r="J420" s="9" t="n"/>
+      <c r="K420" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="30" customHeight="1" s="16">
       <c r="A421" s="9" t="inlineStr">
@@ -24031,6 +26132,11 @@
         </is>
       </c>
       <c r="J421" s="9" t="n"/>
+      <c r="K421" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="30" customHeight="1" s="16">
       <c r="A422" s="9" t="inlineStr">
@@ -24079,6 +26185,11 @@
         </is>
       </c>
       <c r="J422" s="9" t="n"/>
+      <c r="K422" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="30" customHeight="1" s="16">
       <c r="A423" s="9" t="inlineStr">
@@ -24127,6 +26238,11 @@
         </is>
       </c>
       <c r="J423" s="9" t="n"/>
+      <c r="K423" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="30" customHeight="1" s="16">
       <c r="A424" s="9" t="inlineStr">
@@ -24175,6 +26291,11 @@
         </is>
       </c>
       <c r="J424" s="9" t="n"/>
+      <c r="K424" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="30" customHeight="1" s="16">
       <c r="A425" s="9" t="inlineStr">
@@ -24223,6 +26344,11 @@
         </is>
       </c>
       <c r="J425" s="9" t="n"/>
+      <c r="K425" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="30" customHeight="1" s="16">
       <c r="A426" s="9" t="inlineStr">
@@ -24271,6 +26397,11 @@
         </is>
       </c>
       <c r="J426" s="9" t="n"/>
+      <c r="K426" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="30" customHeight="1" s="16">
       <c r="A427" s="9" t="inlineStr">
@@ -24319,6 +26450,11 @@
         </is>
       </c>
       <c r="J427" s="9" t="n"/>
+      <c r="K427" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="30" customHeight="1" s="16">
       <c r="A428" s="9" t="inlineStr">
@@ -24367,6 +26503,11 @@
         </is>
       </c>
       <c r="J428" s="9" t="n"/>
+      <c r="K428" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="30" customHeight="1" s="16">
       <c r="A429" s="9" t="inlineStr">
@@ -24415,6 +26556,11 @@
         </is>
       </c>
       <c r="J429" s="9" t="n"/>
+      <c r="K429" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="30" customHeight="1" s="16">
       <c r="A430" s="9" t="inlineStr">
@@ -24463,6 +26609,11 @@
         </is>
       </c>
       <c r="J430" s="9" t="n"/>
+      <c r="K430" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="30" customHeight="1" s="16">
       <c r="A431" s="9" t="inlineStr">
@@ -24511,6 +26662,11 @@
         </is>
       </c>
       <c r="J431" s="9" t="n"/>
+      <c r="K431" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="30" customHeight="1" s="16">
       <c r="A432" s="9" t="inlineStr">
@@ -24559,6 +26715,11 @@
         </is>
       </c>
       <c r="J432" s="9" t="n"/>
+      <c r="K432" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="30" customHeight="1" s="16">
       <c r="A433" s="9" t="inlineStr">
@@ -24607,6 +26768,11 @@
         </is>
       </c>
       <c r="J433" s="9" t="n"/>
+      <c r="K433" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="30" customHeight="1" s="16">
       <c r="A434" s="9" t="inlineStr">
@@ -24655,6 +26821,11 @@
         </is>
       </c>
       <c r="J434" s="9" t="n"/>
+      <c r="K434" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="30" customHeight="1" s="16">
       <c r="A435" s="9" t="inlineStr">
@@ -24703,6 +26874,11 @@
         </is>
       </c>
       <c r="J435" s="9" t="n"/>
+      <c r="K435" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="30" customHeight="1" s="16">
       <c r="A436" s="9" t="inlineStr">
@@ -24751,6 +26927,11 @@
         </is>
       </c>
       <c r="J436" s="9" t="n"/>
+      <c r="K436" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="30" customHeight="1" s="16">
       <c r="A437" s="9" t="inlineStr">
@@ -24799,6 +26980,11 @@
         </is>
       </c>
       <c r="J437" s="9" t="n"/>
+      <c r="K437" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="30" customHeight="1" s="16">
       <c r="A438" s="9" t="inlineStr">
@@ -24847,6 +27033,11 @@
         </is>
       </c>
       <c r="J438" s="9" t="n"/>
+      <c r="K438" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="30" customHeight="1" s="16">
       <c r="A439" s="9" t="inlineStr">
@@ -24895,6 +27086,11 @@
         </is>
       </c>
       <c r="J439" s="9" t="n"/>
+      <c r="K439" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="30" customHeight="1" s="16">
       <c r="A440" s="9" t="inlineStr">
@@ -24943,6 +27139,11 @@
         </is>
       </c>
       <c r="J440" s="9" t="n"/>
+      <c r="K440" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="30" customHeight="1" s="16">
       <c r="A441" s="9" t="inlineStr">
@@ -24991,6 +27192,11 @@
         </is>
       </c>
       <c r="J441" s="9" t="n"/>
+      <c r="K441" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="30" customHeight="1" s="16">
       <c r="A442" s="9" t="inlineStr">
@@ -25039,6 +27245,11 @@
         </is>
       </c>
       <c r="J442" s="9" t="n"/>
+      <c r="K442" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="443" ht="45" customHeight="1" s="16">
       <c r="A443" s="9" t="inlineStr">
@@ -25087,6 +27298,11 @@
         </is>
       </c>
       <c r="J443" s="9" t="n"/>
+      <c r="K443" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="444" ht="30" customHeight="1" s="16">
       <c r="A444" s="9" t="inlineStr">
@@ -25135,6 +27351,11 @@
         </is>
       </c>
       <c r="J444" s="9" t="n"/>
+      <c r="K444" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="30" customHeight="1" s="16">
       <c r="A445" s="9" t="inlineStr">
@@ -25183,6 +27404,11 @@
         </is>
       </c>
       <c r="J445" s="9" t="n"/>
+      <c r="K445" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="30" customHeight="1" s="16">
       <c r="A446" s="9" t="inlineStr">
@@ -25231,6 +27457,11 @@
         </is>
       </c>
       <c r="J446" s="9" t="n"/>
+      <c r="K446" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="447" ht="30" customHeight="1" s="16">
       <c r="A447" s="9" t="inlineStr">
@@ -25279,6 +27510,11 @@
         </is>
       </c>
       <c r="J447" s="9" t="n"/>
+      <c r="K447" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="30" customHeight="1" s="16">
       <c r="A448" s="9" t="inlineStr">
@@ -25327,6 +27563,11 @@
         </is>
       </c>
       <c r="J448" s="9" t="n"/>
+      <c r="K448" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="30" customHeight="1" s="16">
       <c r="A449" s="9" t="inlineStr">
@@ -25375,6 +27616,11 @@
         </is>
       </c>
       <c r="J449" s="9" t="n"/>
+      <c r="K449" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="450" ht="30" customHeight="1" s="16">
       <c r="A450" s="9" t="inlineStr">
@@ -25423,6 +27669,11 @@
         </is>
       </c>
       <c r="J450" s="9" t="n"/>
+      <c r="K450" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="30" customHeight="1" s="16">
       <c r="A451" s="9" t="inlineStr">
@@ -25471,6 +27722,11 @@
         </is>
       </c>
       <c r="J451" s="9" t="n"/>
+      <c r="K451" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="452" ht="30" customHeight="1" s="16">
       <c r="A452" s="9" t="inlineStr">
@@ -25519,6 +27775,11 @@
         </is>
       </c>
       <c r="J452" s="9" t="n"/>
+      <c r="K452" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="30" customHeight="1" s="16">
       <c r="A453" s="9" t="inlineStr">
@@ -25567,6 +27828,11 @@
         </is>
       </c>
       <c r="J453" s="9" t="n"/>
+      <c r="K453" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="30" customHeight="1" s="16">
       <c r="A454" s="9" t="inlineStr">
@@ -25615,6 +27881,11 @@
         </is>
       </c>
       <c r="J454" s="9" t="n"/>
+      <c r="K454" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="30" customHeight="1" s="16">
       <c r="A455" s="9" t="inlineStr">
@@ -25663,6 +27934,11 @@
         </is>
       </c>
       <c r="J455" s="9" t="n"/>
+      <c r="K455" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="30" customHeight="1" s="16">
       <c r="A456" s="9" t="inlineStr">
@@ -25711,6 +27987,11 @@
         </is>
       </c>
       <c r="J456" s="9" t="n"/>
+      <c r="K456" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="30" customHeight="1" s="16">
       <c r="A457" s="9" t="inlineStr">
@@ -25759,6 +28040,11 @@
         </is>
       </c>
       <c r="J457" s="9" t="n"/>
+      <c r="K457" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="30" customHeight="1" s="16">
       <c r="A458" s="9" t="inlineStr">
@@ -25807,6 +28093,11 @@
         </is>
       </c>
       <c r="J458" s="9" t="n"/>
+      <c r="K458" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="459" ht="30" customHeight="1" s="16">
       <c r="A459" s="9" t="inlineStr">
@@ -25855,6 +28146,11 @@
         </is>
       </c>
       <c r="J459" s="9" t="n"/>
+      <c r="K459" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="460" ht="30" customHeight="1" s="16">
       <c r="A460" s="9" t="inlineStr">
@@ -25903,6 +28199,11 @@
         </is>
       </c>
       <c r="J460" s="9" t="n"/>
+      <c r="K460" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="461" ht="30" customHeight="1" s="16">
       <c r="A461" s="9" t="inlineStr">
@@ -25951,6 +28252,11 @@
         </is>
       </c>
       <c r="J461" s="9" t="n"/>
+      <c r="K461" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="45" customHeight="1" s="16">
       <c r="A462" s="9" t="inlineStr">
@@ -25999,6 +28305,11 @@
         </is>
       </c>
       <c r="J462" s="9" t="n"/>
+      <c r="K462" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="463" ht="45" customHeight="1" s="16">
       <c r="A463" s="9" t="inlineStr">
@@ -26047,6 +28358,11 @@
         </is>
       </c>
       <c r="J463" s="9" t="n"/>
+      <c r="K463" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="30" customHeight="1" s="16">
       <c r="A464" s="9" t="inlineStr">
@@ -26095,6 +28411,11 @@
         </is>
       </c>
       <c r="J464" s="9" t="n"/>
+      <c r="K464" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="465" ht="30" customHeight="1" s="16">
       <c r="A465" s="9" t="inlineStr">
@@ -26143,6 +28464,11 @@
         </is>
       </c>
       <c r="J465" s="9" t="n"/>
+      <c r="K465" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="466" ht="30" customHeight="1" s="16">
       <c r="A466" s="9" t="inlineStr">
@@ -26191,6 +28517,11 @@
         </is>
       </c>
       <c r="J466" s="9" t="n"/>
+      <c r="K466" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="30" customHeight="1" s="16">
       <c r="A467" s="9" t="inlineStr">
@@ -26239,6 +28570,11 @@
         </is>
       </c>
       <c r="J467" s="9" t="n"/>
+      <c r="K467" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="468" ht="45" customHeight="1" s="16">
       <c r="A468" s="9" t="inlineStr">
@@ -26287,6 +28623,11 @@
         </is>
       </c>
       <c r="J468" s="9" t="n"/>
+      <c r="K468" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="469" ht="30" customHeight="1" s="16">
       <c r="A469" s="9" t="inlineStr">
@@ -26335,6 +28676,11 @@
         </is>
       </c>
       <c r="J469" s="9" t="n"/>
+      <c r="K469" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="470" ht="30" customHeight="1" s="16">
       <c r="A470" s="9" t="inlineStr">
@@ -26383,6 +28729,11 @@
         </is>
       </c>
       <c r="J470" s="9" t="n"/>
+      <c r="K470" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="471" ht="30" customHeight="1" s="16">
       <c r="A471" s="9" t="inlineStr">
@@ -26431,6 +28782,11 @@
         </is>
       </c>
       <c r="J471" s="9" t="n"/>
+      <c r="K471" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="472" ht="45" customHeight="1" s="16">
       <c r="A472" s="9" t="inlineStr">
@@ -26479,6 +28835,11 @@
         </is>
       </c>
       <c r="J472" s="9" t="n"/>
+      <c r="K472" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="30" customHeight="1" s="16">
       <c r="A473" s="9" t="inlineStr">
@@ -26527,6 +28888,11 @@
         </is>
       </c>
       <c r="J473" s="9" t="n"/>
+      <c r="K473" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="30" customHeight="1" s="16">
       <c r="A474" s="9" t="inlineStr">
@@ -26575,6 +28941,11 @@
         </is>
       </c>
       <c r="J474" s="9" t="n"/>
+      <c r="K474" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="30" customHeight="1" s="16">
       <c r="A475" s="9" t="inlineStr">
@@ -26623,6 +28994,11 @@
         </is>
       </c>
       <c r="J475" s="9" t="n"/>
+      <c r="K475" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="30" customHeight="1" s="16">
       <c r="A476" s="10" t="inlineStr">
@@ -26671,6 +29047,11 @@
         </is>
       </c>
       <c r="J476" s="10" t="n"/>
+      <c r="K476" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="30" customHeight="1" s="16">
       <c r="A477" s="10" t="inlineStr">
@@ -26719,6 +29100,11 @@
         </is>
       </c>
       <c r="J477" s="10" t="n"/>
+      <c r="K477" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="30" customHeight="1" s="16">
       <c r="A478" s="10" t="inlineStr">
@@ -26767,6 +29153,11 @@
         </is>
       </c>
       <c r="J478" s="10" t="n"/>
+      <c r="K478" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="30" customHeight="1" s="16">
       <c r="A479" s="10" t="inlineStr">
@@ -26815,6 +29206,11 @@
         </is>
       </c>
       <c r="J479" s="10" t="n"/>
+      <c r="K479" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="30" customHeight="1" s="16">
       <c r="A480" s="10" t="inlineStr">
@@ -26863,6 +29259,11 @@
         </is>
       </c>
       <c r="J480" s="10" t="n"/>
+      <c r="K480" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="30" customHeight="1" s="16">
       <c r="A481" s="10" t="inlineStr">
@@ -26911,6 +29312,11 @@
         </is>
       </c>
       <c r="J481" s="10" t="n"/>
+      <c r="K481" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="30" customHeight="1" s="16">
       <c r="A482" s="10" t="inlineStr">
@@ -26959,6 +29365,11 @@
         </is>
       </c>
       <c r="J482" s="10" t="n"/>
+      <c r="K482" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="483" ht="30" customHeight="1" s="16">
       <c r="A483" s="10" t="inlineStr">
@@ -27007,6 +29418,11 @@
         </is>
       </c>
       <c r="J483" s="10" t="n"/>
+      <c r="K483" s="10" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="30" customHeight="1" s="16">
       <c r="A484" s="10" t="inlineStr">
@@ -27055,6 +29471,11 @@
         </is>
       </c>
       <c r="J484" s="10" t="n"/>
+      <c r="K484" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="30" customHeight="1" s="16">
       <c r="A485" s="10" t="inlineStr">
@@ -27103,6 +29524,11 @@
         </is>
       </c>
       <c r="J485" s="10" t="n"/>
+      <c r="K485" s="10" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="30" customHeight="1" s="16">
       <c r="A486" s="10" t="inlineStr">
@@ -27151,6 +29577,11 @@
         </is>
       </c>
       <c r="J486" s="10" t="n"/>
+      <c r="K486" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="487" ht="30" customHeight="1" s="16">
       <c r="A487" s="10" t="inlineStr">
@@ -27199,6 +29630,11 @@
         </is>
       </c>
       <c r="J487" s="10" t="n"/>
+      <c r="K487" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="488" ht="30" customHeight="1" s="16">
       <c r="A488" s="10" t="inlineStr">
@@ -27247,6 +29683,11 @@
         </is>
       </c>
       <c r="J488" s="10" t="n"/>
+      <c r="K488" s="10" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="489" ht="30" customHeight="1" s="16">
       <c r="A489" s="10" t="inlineStr">
@@ -27295,6 +29736,11 @@
         </is>
       </c>
       <c r="J489" s="10" t="n"/>
+      <c r="K489" s="10" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="30" customHeight="1" s="16">
       <c r="A490" s="10" t="inlineStr">
@@ -27343,6 +29789,11 @@
         </is>
       </c>
       <c r="J490" s="10" t="n"/>
+      <c r="K490" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="30" customHeight="1" s="16">
       <c r="A491" s="10" t="inlineStr">
@@ -27391,6 +29842,11 @@
         </is>
       </c>
       <c r="J491" s="10" t="n"/>
+      <c r="K491" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="45" customHeight="1" s="16">
       <c r="A492" s="10" t="inlineStr">
@@ -27439,6 +29895,11 @@
         </is>
       </c>
       <c r="J492" s="10" t="n"/>
+      <c r="K492" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="493" ht="45" customHeight="1" s="16">
       <c r="A493" s="10" t="inlineStr">
@@ -27487,6 +29948,11 @@
         </is>
       </c>
       <c r="J493" s="10" t="n"/>
+      <c r="K493" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="494" ht="30" customHeight="1" s="16">
       <c r="A494" s="9" t="inlineStr">
@@ -27535,6 +30001,11 @@
         </is>
       </c>
       <c r="J494" s="9" t="n"/>
+      <c r="K494" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="495" ht="30" customHeight="1" s="16">
       <c r="A495" s="9" t="inlineStr">
@@ -27583,6 +30054,11 @@
         </is>
       </c>
       <c r="J495" s="9" t="n"/>
+      <c r="K495" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="496" ht="30" customHeight="1" s="16">
       <c r="A496" s="9" t="inlineStr">
@@ -27631,6 +30107,11 @@
         </is>
       </c>
       <c r="J496" s="9" t="n"/>
+      <c r="K496" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="497" ht="30" customHeight="1" s="16">
       <c r="A497" s="9" t="inlineStr">
@@ -27679,6 +30160,11 @@
         </is>
       </c>
       <c r="J497" s="9" t="n"/>
+      <c r="K497" s="9" t="inlineStr">
+        <is>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="30" customHeight="1" s="16">
       <c r="A498" s="9" t="inlineStr">
@@ -27727,6 +30213,11 @@
         </is>
       </c>
       <c r="J498" s="9" t="n"/>
+      <c r="K498" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="30" customHeight="1" s="16">
       <c r="A499" s="9" t="inlineStr">
@@ -27775,6 +30266,11 @@
         </is>
       </c>
       <c r="J499" s="9" t="n"/>
+      <c r="K499" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="30" customHeight="1" s="16">
       <c r="A500" s="9" t="inlineStr">
@@ -27823,6 +30319,11 @@
         </is>
       </c>
       <c r="J500" s="9" t="n"/>
+      <c r="K500" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="501" ht="30" customHeight="1" s="16">
       <c r="A501" s="9" t="inlineStr">
@@ -27871,6 +30372,11 @@
         </is>
       </c>
       <c r="J501" s="9" t="n"/>
+      <c r="K501" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="502" ht="30" customHeight="1" s="16">
       <c r="A502" s="9" t="inlineStr">
@@ -27919,6 +30425,11 @@
         </is>
       </c>
       <c r="J502" s="9" t="n"/>
+      <c r="K502" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="503" ht="30" customHeight="1" s="16">
       <c r="A503" s="9" t="inlineStr">
@@ -27967,6 +30478,11 @@
         </is>
       </c>
       <c r="J503" s="9" t="n"/>
+      <c r="K503" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="504" ht="30" customHeight="1" s="16">
       <c r="A504" s="9" t="inlineStr">
@@ -28015,6 +30531,11 @@
         </is>
       </c>
       <c r="J504" s="9" t="n"/>
+      <c r="K504" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="505" ht="30" customHeight="1" s="16">
       <c r="A505" s="9" t="inlineStr">
@@ -28063,6 +30584,11 @@
         </is>
       </c>
       <c r="J505" s="9" t="n"/>
+      <c r="K505" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="60" customHeight="1" s="16">
       <c r="A506" s="9" t="inlineStr">
@@ -28111,6 +30637,11 @@
         </is>
       </c>
       <c r="J506" s="9" t="n"/>
+      <c r="K506" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="60" customHeight="1" s="16">
       <c r="A507" s="9" t="inlineStr">
@@ -28159,6 +30690,11 @@
         </is>
       </c>
       <c r="J507" s="9" t="n"/>
+      <c r="K507" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="60" customHeight="1" s="16">
       <c r="A508" s="9" t="inlineStr">
@@ -28207,6 +30743,11 @@
         </is>
       </c>
       <c r="J508" s="9" t="n"/>
+      <c r="K508" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="60" customHeight="1" s="16">
       <c r="A509" s="9" t="inlineStr">
@@ -28255,6 +30796,11 @@
         </is>
       </c>
       <c r="J509" s="9" t="n"/>
+      <c r="K509" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="60" customHeight="1" s="16">
       <c r="A510" s="9" t="inlineStr">
@@ -28303,6 +30849,11 @@
         </is>
       </c>
       <c r="J510" s="9" t="n"/>
+      <c r="K510" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="511" ht="60" customHeight="1" s="16">
       <c r="A511" s="9" t="inlineStr">
@@ -28351,6 +30902,11 @@
         </is>
       </c>
       <c r="J511" s="9" t="n"/>
+      <c r="K511" s="9" t="inlineStr">
+        <is>
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="60" customHeight="1" s="16">
       <c r="A512" s="9" t="inlineStr">
@@ -28399,6 +30955,11 @@
         </is>
       </c>
       <c r="J512" s="9" t="n"/>
+      <c r="K512" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="513" ht="60" customHeight="1" s="16">
       <c r="A513" s="9" t="inlineStr">
@@ -28447,6 +31008,11 @@
         </is>
       </c>
       <c r="J513" s="9" t="n"/>
+      <c r="K513" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="30" customHeight="1" s="16">
       <c r="A514" s="9" t="inlineStr">
@@ -28495,6 +31061,11 @@
         </is>
       </c>
       <c r="J514" s="9" t="n"/>
+      <c r="K514" s="9" t="inlineStr">
+        <is>
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="515" ht="30" customHeight="1" s="16">
       <c r="A515" s="9" t="inlineStr">
@@ -28543,6 +31114,11 @@
         </is>
       </c>
       <c r="J515" s="9" t="n"/>
+      <c r="K515" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="30" customHeight="1" s="16">
       <c r="A516" s="9" t="inlineStr">
@@ -28591,6 +31167,11 @@
         </is>
       </c>
       <c r="J516" s="9" t="n"/>
+      <c r="K516" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="517" ht="30" customHeight="1" s="16">
       <c r="A517" s="9" t="inlineStr">
@@ -28639,6 +31220,11 @@
         </is>
       </c>
       <c r="J517" s="9" t="n"/>
+      <c r="K517" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="30" customHeight="1" s="16">
       <c r="A518" s="9" t="inlineStr">
@@ -28687,6 +31273,11 @@
         </is>
       </c>
       <c r="J518" s="9" t="n"/>
+      <c r="K518" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="519" ht="30" customHeight="1" s="16">
       <c r="A519" s="9" t="inlineStr">
@@ -28735,6 +31326,11 @@
         </is>
       </c>
       <c r="J519" s="9" t="n"/>
+      <c r="K519" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="520" ht="30" customHeight="1" s="16">
       <c r="A520" s="9" t="inlineStr">
@@ -28783,6 +31379,11 @@
         </is>
       </c>
       <c r="J520" s="9" t="n"/>
+      <c r="K520" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="521" ht="30" customHeight="1" s="16">
       <c r="A521" s="9" t="inlineStr">
@@ -28831,6 +31432,11 @@
         </is>
       </c>
       <c r="J521" s="9" t="n"/>
+      <c r="K521" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="30" customHeight="1" s="16">
       <c r="A522" s="9" t="inlineStr">
@@ -28879,6 +31485,11 @@
         </is>
       </c>
       <c r="J522" s="9" t="n"/>
+      <c r="K522" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="523" ht="30" customHeight="1" s="16">
       <c r="A523" s="9" t="inlineStr">
@@ -28927,6 +31538,11 @@
         </is>
       </c>
       <c r="J523" s="9" t="n"/>
+      <c r="K523" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="30" customHeight="1" s="16">
       <c r="A524" s="9" t="inlineStr">
@@ -28975,6 +31591,11 @@
         </is>
       </c>
       <c r="J524" s="9" t="n"/>
+      <c r="K524" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="525" ht="30" customHeight="1" s="16">
       <c r="A525" s="9" t="inlineStr">
@@ -29023,6 +31644,11 @@
         </is>
       </c>
       <c r="J525" s="9" t="n"/>
+      <c r="K525" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="526" ht="30" customHeight="1" s="16">
       <c r="A526" s="9" t="inlineStr">
@@ -29071,6 +31697,11 @@
         </is>
       </c>
       <c r="J526" s="9" t="n"/>
+      <c r="K526" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="527" ht="30" customHeight="1" s="16">
       <c r="A527" s="9" t="inlineStr">
@@ -29119,6 +31750,11 @@
         </is>
       </c>
       <c r="J527" s="9" t="n"/>
+      <c r="K527" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="30" customHeight="1" s="16">
       <c r="A528" s="9" t="inlineStr">
@@ -29167,6 +31803,11 @@
         </is>
       </c>
       <c r="J528" s="9" t="n"/>
+      <c r="K528" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="30" customHeight="1" s="16">
       <c r="A529" s="9" t="inlineStr">
@@ -29215,6 +31856,11 @@
         </is>
       </c>
       <c r="J529" s="9" t="n"/>
+      <c r="K529" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="530" ht="30" customHeight="1" s="16">
       <c r="A530" s="9" t="inlineStr">
@@ -29263,6 +31909,11 @@
         </is>
       </c>
       <c r="J530" s="9" t="n"/>
+      <c r="K530" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="531" ht="30" customHeight="1" s="16">
       <c r="A531" s="9" t="inlineStr">
@@ -29311,6 +31962,11 @@
         </is>
       </c>
       <c r="J531" s="9" t="n"/>
+      <c r="K531" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="532" s="16">
       <c r="A532" s="9" t="inlineStr">
@@ -29359,6 +32015,11 @@
         </is>
       </c>
       <c r="J532" s="9" t="n"/>
+      <c r="K532" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="533" ht="30" customHeight="1" s="16">
       <c r="A533" s="9" t="inlineStr">
@@ -29407,6 +32068,11 @@
         </is>
       </c>
       <c r="J533" s="9" t="n"/>
+      <c r="K533" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="30" customHeight="1" s="16">
       <c r="A534" s="9" t="inlineStr">
@@ -29455,6 +32121,11 @@
         </is>
       </c>
       <c r="J534" s="9" t="n"/>
+      <c r="K534" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="535" ht="30" customHeight="1" s="16">
       <c r="A535" s="9" t="inlineStr">
@@ -29503,6 +32174,11 @@
         </is>
       </c>
       <c r="J535" s="9" t="n"/>
+      <c r="K535" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="536" ht="30" customHeight="1" s="16">
       <c r="A536" s="9" t="inlineStr">
@@ -29551,6 +32227,11 @@
         </is>
       </c>
       <c r="J536" s="9" t="n"/>
+      <c r="K536" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="537" ht="30" customHeight="1" s="16">
       <c r="A537" s="9" t="inlineStr">
@@ -29599,6 +32280,11 @@
         </is>
       </c>
       <c r="J537" s="9" t="n"/>
+      <c r="K537" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="30" customHeight="1" s="16">
       <c r="A538" s="9" t="inlineStr">
@@ -29647,6 +32333,11 @@
         </is>
       </c>
       <c r="J538" s="9" t="n"/>
+      <c r="K538" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="539" ht="30" customHeight="1" s="16">
       <c r="A539" s="9" t="inlineStr">
@@ -29695,6 +32386,11 @@
         </is>
       </c>
       <c r="J539" s="9" t="n"/>
+      <c r="K539" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="540" ht="30" customHeight="1" s="16">
       <c r="A540" s="9" t="inlineStr">
@@ -29743,6 +32439,11 @@
         </is>
       </c>
       <c r="J540" s="9" t="n"/>
+      <c r="K540" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="541" ht="30" customHeight="1" s="16">
       <c r="A541" s="9" t="inlineStr">
@@ -29791,6 +32492,11 @@
         </is>
       </c>
       <c r="J541" s="9" t="n"/>
+      <c r="K541" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="542" ht="30" customHeight="1" s="16">
       <c r="A542" s="9" t="inlineStr">
@@ -29839,6 +32545,11 @@
         </is>
       </c>
       <c r="J542" s="9" t="n"/>
+      <c r="K542" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="543" ht="30" customHeight="1" s="16">
       <c r="A543" s="9" t="inlineStr">
@@ -29887,6 +32598,11 @@
         </is>
       </c>
       <c r="J543" s="9" t="n"/>
+      <c r="K543" s="9" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="544" ht="30" customHeight="1" s="16">
       <c r="A544" s="9" t="inlineStr">
@@ -29935,6 +32651,11 @@
         </is>
       </c>
       <c r="J544" s="9" t="n"/>
+      <c r="K544" s="9" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="545" ht="30" customHeight="1" s="16">
       <c r="A545" s="9" t="inlineStr">
@@ -29983,6 +32704,11 @@
         </is>
       </c>
       <c r="J545" s="9" t="n"/>
+      <c r="K545" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
     </row>
     <row r="546" ht="30" customHeight="1" s="16">
       <c r="A546" s="9" t="inlineStr">
@@ -30031,6 +32757,11 @@
         </is>
       </c>
       <c r="J546" s="9" t="n"/>
+      <c r="K546" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="547" ht="30" customHeight="1" s="16">
       <c r="A547" s="9" t="inlineStr">
@@ -30079,6 +32810,11 @@
         </is>
       </c>
       <c r="J547" s="9" t="n"/>
+      <c r="K547" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="548" ht="30" customHeight="1" s="16">
       <c r="A548" s="9" t="inlineStr">
@@ -30127,6 +32863,11 @@
         </is>
       </c>
       <c r="J548" s="9" t="n"/>
+      <c r="K548" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="549" ht="30" customHeight="1" s="16">
       <c r="A549" s="9" t="inlineStr">
@@ -30175,6 +32916,11 @@
         </is>
       </c>
       <c r="J549" s="9" t="n"/>
+      <c r="K549" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="550" ht="30" customHeight="1" s="16">
       <c r="A550" s="9" t="inlineStr">
@@ -30223,6 +32969,11 @@
         </is>
       </c>
       <c r="J550" s="9" t="n"/>
+      <c r="K550" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="551" ht="30" customHeight="1" s="16">
       <c r="A551" s="9" t="inlineStr">
@@ -30271,6 +33022,11 @@
         </is>
       </c>
       <c r="J551" s="9" t="n"/>
+      <c r="K551" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="552" ht="60" customHeight="1" s="16">
       <c r="A552" s="9" t="inlineStr">
@@ -30319,6 +33075,11 @@
         </is>
       </c>
       <c r="J552" s="9" t="n"/>
+      <c r="K552" s="9" t="inlineStr">
+        <is>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="553" ht="60" customHeight="1" s="16">
       <c r="A553" s="9" t="inlineStr">
@@ -30367,6 +33128,11 @@
         </is>
       </c>
       <c r="J553" s="9" t="n"/>
+      <c r="K553" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="554" ht="60" customHeight="1" s="16">
       <c r="A554" s="9" t="inlineStr">
@@ -30415,6 +33181,11 @@
         </is>
       </c>
       <c r="J554" s="9" t="n"/>
+      <c r="K554" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="555" ht="60" customHeight="1" s="16">
       <c r="A555" s="9" t="inlineStr">
@@ -30463,6 +33234,11 @@
         </is>
       </c>
       <c r="J555" s="9" t="n"/>
+      <c r="K555" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
     </row>
     <row r="556" ht="60" customHeight="1" s="16">
       <c r="A556" s="9" t="inlineStr">
@@ -30511,6 +33287,11 @@
         </is>
       </c>
       <c r="J556" s="9" t="n"/>
+      <c r="K556" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="557" ht="30" customHeight="1" s="16">
       <c r="A557" s="9" t="inlineStr">
@@ -30559,6 +33340,11 @@
         </is>
       </c>
       <c r="J557" s="9" t="n"/>
+      <c r="K557" s="9" t="inlineStr">
+        <is>
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
     </row>
     <row r="558" ht="60" customHeight="1" s="16">
       <c r="A558" s="9" t="inlineStr">
@@ -30607,6 +33393,11 @@
         </is>
       </c>
       <c r="J558" s="9" t="n"/>
+      <c r="K558" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
     </row>
     <row r="559" ht="60" customHeight="1" s="16">
       <c r="A559" s="9" t="inlineStr">
@@ -30655,9 +33446,14 @@
         </is>
       </c>
       <c r="J559" s="9" t="n"/>
+      <c r="K559" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J559">
+  <autoFilter ref="A1:K559">
     <sortState ref="A2:J528">
       <sortCondition ref="A1:A528"/>
     </sortState>

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$7:$I$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'list'!$A$1:$K$559</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'list'!$A$1:$K$552</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Little choice: 4 distinct units, each offered as standard or Advanced (Adv) version (Adv needs a 75+ mark in the prerequisite - take the standard version); terms inferred from previous years</t>
+          <t>Little choice (at minimum); Terms partly inferred from previous years</t>
         </is>
       </c>
     </row>
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Standard and Advanced (Adv) versions listed - Adv needs a 75+ mark in the prerequisite; terms inferred from previous years</t>
+          <t>Terms partly inferred from previous years</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="16" min="1" max="1"/>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="E360" s="10" t="inlineStr">
         <is>
-          <t>GEOS2921 Environmental and Resource Management (Adv) (6 CP)</t>
+          <t>GEOS2121 Environmental and Resource Management (6 cp)</t>
         </is>
       </c>
       <c r="F360" s="10" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="E361" s="10" t="inlineStr">
         <is>
-          <t>GEOS2923 The Geography of Cities and Regions (6 cp)</t>
+          <t>GEOS2123 The Geography of Cities and Regions (6 cp)</t>
         </is>
       </c>
       <c r="F361" s="10" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="E362" s="10" t="inlineStr">
         <is>
-          <t>GEOS3909 Coastal Environments and Processes (Adv) (6 CP)</t>
+          <t>GEOS3009 Coastal Environments and Processes (6 cp)</t>
         </is>
       </c>
       <c r="F362" s="10" t="inlineStr">
@@ -23034,7 +23034,7 @@
       </c>
       <c r="E363" s="10" t="inlineStr">
         <is>
-          <t>GEOS3920 Urban Citizenship and Sustainability (Adv) (6 CP)</t>
+          <t>GEOS3520 Urban Citizenship and Sustainability (6 cp)</t>
         </is>
       </c>
       <c r="F363" s="10" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="B364" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C364" s="10" t="inlineStr">
@@ -23087,12 +23087,12 @@
       </c>
       <c r="E364" s="10" t="inlineStr">
         <is>
-          <t>GEOS2121 Environmental and Resource Management (6 cp)</t>
+          <t>GEOS1001 Earth, Environment and Society (6 cp)</t>
         </is>
       </c>
       <c r="F364" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G364" s="10" t="inlineStr">
@@ -23125,12 +23125,12 @@
       </c>
       <c r="B365" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C365" s="10" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D365" s="10" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="E365" s="10" t="inlineStr">
         <is>
-          <t>GEOS2123 The Geography of Cities and Regions (6 cp)</t>
+          <t>GEOS2121 Environmental and Resource Management (6 cp)</t>
         </is>
       </c>
       <c r="F365" s="10" t="inlineStr">
@@ -23166,7 +23166,7 @@
       <c r="J365" s="10" t="n"/>
       <c r="K365" s="10" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -23178,12 +23178,12 @@
       </c>
       <c r="B366" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C366" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D366" s="10" t="inlineStr">
@@ -23219,7 +23219,7 @@
       <c r="J366" s="10" t="n"/>
       <c r="K366" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B367" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C367" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D367" s="10" t="inlineStr">
@@ -23272,7 +23272,7 @@
       <c r="J367" s="10" t="n"/>
       <c r="K367" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -23289,7 +23289,7 @@
       </c>
       <c r="C368" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D368" s="10" t="inlineStr">
@@ -23299,12 +23299,12 @@
       </c>
       <c r="E368" s="10" t="inlineStr">
         <is>
-          <t>GEOS1001 Earth, Environment and Society (6 cp)</t>
+          <t>GEOS2115 Oceans, Coasts and Climate Change (6 cp)</t>
         </is>
       </c>
       <c r="F368" s="10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G368" s="10" t="inlineStr">
@@ -23325,24 +23325,24 @@
       <c r="J368" s="10" t="n"/>
       <c r="K368" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="369" ht="30" customHeight="1" s="16">
       <c r="A369" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B369" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C369" s="10" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D369" s="10" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E369" s="10" t="inlineStr">
         <is>
-          <t>GEOS2921 Environmental and Resource Management (Adv) (6 CP)</t>
+          <t>KGA171 Global Geographies of Change</t>
         </is>
       </c>
       <c r="F369" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G369" s="10" t="inlineStr">
@@ -23378,24 +23378,24 @@
       <c r="J369" s="10" t="n"/>
       <c r="K369" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="370" ht="30" customHeight="1" s="16">
       <c r="A370" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B370" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C370" s="10" t="inlineStr">
         <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D370" s="10" t="inlineStr">
@@ -23405,12 +23405,12 @@
       </c>
       <c r="E370" s="10" t="inlineStr">
         <is>
-          <t>GEOS3909 Coastal Environments and Processes (Adv) (6 CP)</t>
+          <t>KGA205 Geographies of Economy, Politics and Culture</t>
         </is>
       </c>
       <c r="F370" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G370" s="10" t="inlineStr">
@@ -23431,24 +23431,24 @@
       <c r="J370" s="10" t="n"/>
       <c r="K370" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="371" ht="30" customHeight="1" s="16">
       <c r="A371" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B371" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C371" s="10" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D371" s="10" t="inlineStr">
@@ -23458,12 +23458,12 @@
       </c>
       <c r="E371" s="10" t="inlineStr">
         <is>
-          <t>GEOS3920 Urban Citizenship and Sustainability (Adv) (6 CP)</t>
+          <t>KGA207 Systems Thinking (12.5% weight (UTAS standard, per handbook))</t>
         </is>
       </c>
       <c r="F371" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G371" s="10" t="inlineStr">
@@ -23484,24 +23484,24 @@
       <c r="J371" s="10" t="n"/>
       <c r="K371" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
     <row r="372" ht="30" customHeight="1" s="16">
       <c r="A372" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B372" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C372" s="10" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D372" s="10" t="inlineStr">
@@ -23511,12 +23511,12 @@
       </c>
       <c r="E372" s="10" t="inlineStr">
         <is>
-          <t>GEOS2121 Environmental and Resource Management (6 cp)</t>
+          <t>KGA327 Geoheritage and Geotourism (12.5% weight (UTAS standard))</t>
         </is>
       </c>
       <c r="F372" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G372" s="10" t="inlineStr">
@@ -23537,24 +23537,24 @@
       <c r="J372" s="10" t="n"/>
       <c r="K372" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
     <row r="373" ht="30" customHeight="1" s="16">
       <c r="A373" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B373" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C373" s="10" t="inlineStr">
         <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
         </is>
       </c>
       <c r="D373" s="10" t="inlineStr">
@@ -23564,12 +23564,12 @@
       </c>
       <c r="E373" s="10" t="inlineStr">
         <is>
-          <t>GEOS3009 Coastal Environments and Processes (6 cp)</t>
+          <t>KGG213 Remote Sensing: From Data to Information (12.5% weight (UTAS standard, per handbook))</t>
         </is>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G373" s="10" t="inlineStr">
@@ -23590,14 +23590,14 @@
       <c r="J373" s="10" t="n"/>
       <c r="K373" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
         </is>
       </c>
     </row>
     <row r="374" ht="30" customHeight="1" s="16">
       <c r="A374" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B374" s="10" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="C374" s="10" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D374" s="10" t="inlineStr">
@@ -23617,12 +23617,12 @@
       </c>
       <c r="E374" s="10" t="inlineStr">
         <is>
-          <t>GEOS3520 Urban Citizenship and Sustainability (6 cp)</t>
+          <t>KGA204 Earth, Climate and Life</t>
         </is>
       </c>
       <c r="F374" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G374" s="10" t="inlineStr">
@@ -23643,14 +23643,14 @@
       <c r="J374" s="10" t="n"/>
       <c r="K374" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="375" ht="30" customHeight="1" s="16">
       <c r="A375" s="10" t="inlineStr">
         <is>
-          <t>University of Sydney — Australia</t>
+          <t>University of Tasmania — Australia</t>
         </is>
       </c>
       <c r="B375" s="10" t="inlineStr">
@@ -23660,7 +23660,7 @@
       </c>
       <c r="C375" s="10" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D375" s="10" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="E375" s="10" t="inlineStr">
         <is>
-          <t>GEOS2115 Oceans, Coasts and Climate Change (6 cp)</t>
+          <t>KGG213 Remote Sensing: From Data to Information (12.5% weight (UTAS standard, per handbook))</t>
         </is>
       </c>
       <c r="F375" s="10" t="inlineStr">
@@ -23696,7 +23696,7 @@
       <c r="J375" s="10" t="n"/>
       <c r="K375" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -23708,12 +23708,12 @@
       </c>
       <c r="B376" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C376" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D376" s="10" t="inlineStr">
@@ -23723,12 +23723,12 @@
       </c>
       <c r="E376" s="10" t="inlineStr">
         <is>
-          <t>KGA171 Global Geographies of Change</t>
+          <t>KGG301 3D Geospatial Data Capture and Analytics (12.5% weight (UTAS standard))</t>
         </is>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G376" s="10" t="inlineStr">
@@ -23749,7 +23749,7 @@
       <c r="J376" s="10" t="n"/>
       <c r="K376" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="C377" s="10" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D377" s="10" t="inlineStr">
@@ -23776,12 +23776,12 @@
       </c>
       <c r="E377" s="10" t="inlineStr">
         <is>
-          <t>KGA205 Geographies of Economy, Politics and Culture</t>
+          <t>KGA301 Change Agents for Sustainability (12.5% weight (UTAS standard))</t>
         </is>
       </c>
       <c r="F377" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G377" s="10" t="inlineStr">
@@ -23802,7 +23802,7 @@
       <c r="J377" s="10" t="n"/>
       <c r="K377" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -23814,12 +23814,12 @@
       </c>
       <c r="B378" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C378" s="10" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D378" s="10" t="inlineStr">
@@ -23829,12 +23829,12 @@
       </c>
       <c r="E378" s="10" t="inlineStr">
         <is>
-          <t>KGA207 Systems Thinking (12.5% weight (UTAS standard, per handbook))</t>
+          <t>KGA301 Change Agents for Sustainability (12.5% weight (UTAS standard))</t>
         </is>
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G378" s="10" t="inlineStr">
@@ -23855,7 +23855,7 @@
       <c r="J378" s="10" t="n"/>
       <c r="K378" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -23867,12 +23867,12 @@
       </c>
       <c r="B379" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C379" s="10" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D379" s="10" t="inlineStr">
@@ -23882,12 +23882,12 @@
       </c>
       <c r="E379" s="10" t="inlineStr">
         <is>
-          <t>KGA327 Geoheritage and Geotourism (12.5% weight (UTAS standard))</t>
+          <t>KGA207 Systems Thinking (12.5%)</t>
         </is>
       </c>
       <c r="F379" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G379" s="10" t="inlineStr">
@@ -23908,7 +23908,7 @@
       <c r="J379" s="10" t="n"/>
       <c r="K379" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -23920,12 +23920,12 @@
       </c>
       <c r="B380" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C380" s="10" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D380" s="10" t="inlineStr">
@@ -23935,12 +23935,12 @@
       </c>
       <c r="E380" s="10" t="inlineStr">
         <is>
-          <t>KGG213 Remote Sensing: From Data to Information (12.5% weight (UTAS standard, per handbook))</t>
+          <t>KGA327 Geoheritage and Geotourism (12.5%)</t>
         </is>
       </c>
       <c r="F380" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G380" s="10" t="inlineStr">
@@ -23961,385 +23961,385 @@
       <c r="J380" s="10" t="n"/>
       <c r="K380" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
     <row r="381" ht="30" customHeight="1" s="16">
-      <c r="A381" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B381" s="10" t="inlineStr">
+      <c r="A381" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney (UTS) — Australia</t>
+        </is>
+      </c>
+      <c r="B381" s="9" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C381" s="10" t="inlineStr">
+      <c r="C381" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D381" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E381" s="9" t="inlineStr">
+        <is>
+          <t>91120 GIS and Remote Sensing</t>
+        </is>
+      </c>
+      <c r="F381" s="9" t="inlineStr">
+        <is>
+          <t>Upper-level undergraduate</t>
+        </is>
+      </c>
+      <c r="G381" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H381" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I381" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J381" s="9" t="n"/>
+      <c r="K381" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="30" customHeight="1" s="16">
+      <c r="A382" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney (UTS) — Australia</t>
+        </is>
+      </c>
+      <c r="B382" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C382" s="9" t="inlineStr">
+        <is>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D382" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E382" s="9" t="inlineStr">
+        <is>
+          <t>91145 Environmental Protection and Management</t>
+        </is>
+      </c>
+      <c r="F382" s="9" t="inlineStr">
+        <is>
+          <t>Upper-level undergraduate</t>
+        </is>
+      </c>
+      <c r="G382" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H382" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I382" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J382" s="9" t="n"/>
+      <c r="K382" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="30" customHeight="1" s="16">
+      <c r="A383" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney (UTS) — Australia</t>
+        </is>
+      </c>
+      <c r="B383" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C383" s="9" t="inlineStr">
+        <is>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D383" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E383" s="9" t="inlineStr">
+        <is>
+          <t>91154 Ecology</t>
+        </is>
+      </c>
+      <c r="F383" s="9" t="inlineStr">
+        <is>
+          <t>Upper-level undergraduate</t>
+        </is>
+      </c>
+      <c r="G383" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H383" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I383" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J383" s="9" t="n"/>
+      <c r="K383" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="30" customHeight="1" s="16">
+      <c r="A384" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney (UTS) — Australia</t>
+        </is>
+      </c>
+      <c r="B384" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C384" s="9" t="inlineStr">
         <is>
           <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
-      <c r="D381" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E381" s="10" t="inlineStr">
-        <is>
-          <t>KGA204 Earth, Climate and Life</t>
-        </is>
-      </c>
-      <c r="F381" s="10" t="inlineStr">
+      <c r="D384" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E384" s="9" t="inlineStr">
+        <is>
+          <t>91156 Ocean Systems and Climate Change</t>
+        </is>
+      </c>
+      <c r="F384" s="9" t="inlineStr">
+        <is>
+          <t>Upper-level undergraduate</t>
+        </is>
+      </c>
+      <c r="G384" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H384" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I384" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J384" s="9" t="n"/>
+      <c r="K384" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="30" customHeight="1" s="16">
+      <c r="A385" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney (UTS) — Australia</t>
+        </is>
+      </c>
+      <c r="B385" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C385" s="9" t="inlineStr">
+        <is>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D385" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E385" s="9" t="inlineStr">
+        <is>
+          <t>91309 Biodiversity Conservation</t>
+        </is>
+      </c>
+      <c r="F385" s="9" t="inlineStr">
+        <is>
+          <t>Upper-level undergraduate</t>
+        </is>
+      </c>
+      <c r="G385" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H385" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I385" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J385" s="9" t="n"/>
+      <c r="K385" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="30" customHeight="1" s="16">
+      <c r="A386" s="9" t="inlineStr">
+        <is>
+          <t>University of Texas at Dallas — USA</t>
+        </is>
+      </c>
+      <c r="B386" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C386" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D386" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E386" s="9" t="inlineStr">
+        <is>
+          <t>GISC2307 Digital Earth (3)</t>
+        </is>
+      </c>
+      <c r="F386" s="9" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G381" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H381" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I381" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J381" s="10" t="n"/>
-      <c r="K381" s="10" t="inlineStr">
-        <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="382" ht="30" customHeight="1" s="16">
-      <c r="A382" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B382" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C382" s="10" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D382" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E382" s="10" t="inlineStr">
-        <is>
-          <t>KGG213 Remote Sensing: From Data to Information (12.5% weight (UTAS standard, per handbook))</t>
-        </is>
-      </c>
-      <c r="F382" s="10" t="inlineStr">
+      <c r="G386" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H386" s="9" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="I386" s="12" t="inlineStr">
+        <is>
+          <t>Semester 1</t>
+        </is>
+      </c>
+      <c r="J386" s="9" t="n"/>
+      <c r="K386" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="30" customHeight="1" s="16">
+      <c r="A387" s="9" t="inlineStr">
+        <is>
+          <t>University of Texas at Dallas — USA</t>
+        </is>
+      </c>
+      <c r="B387" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C387" s="9" t="inlineStr">
+        <is>
+          <t>SOES220 CITIES AND REGIONS</t>
+        </is>
+      </c>
+      <c r="D387" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E387" s="9" t="inlineStr">
+        <is>
+          <t>GEOG2303 World Regional Geography (3)</t>
+        </is>
+      </c>
+      <c r="F387" s="9" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G382" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H382" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I382" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J382" s="10" t="n"/>
-      <c r="K382" s="10" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="383" ht="30" customHeight="1" s="16">
-      <c r="A383" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B383" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C383" s="10" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D383" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E383" s="10" t="inlineStr">
-        <is>
-          <t>KGG301 3D Geospatial Data Capture and Analytics (12.5% weight (UTAS standard))</t>
-        </is>
-      </c>
-      <c r="F383" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G383" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H383" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I383" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J383" s="10" t="n"/>
-      <c r="K383" s="10" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="384" ht="30" customHeight="1" s="16">
-      <c r="A384" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B384" s="10" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C384" s="10" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D384" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E384" s="10" t="inlineStr">
-        <is>
-          <t>KGA301 Change Agents for Sustainability (12.5% weight (UTAS standard))</t>
-        </is>
-      </c>
-      <c r="F384" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G384" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H384" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I384" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J384" s="10" t="n"/>
-      <c r="K384" s="10" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="385" ht="30" customHeight="1" s="16">
-      <c r="A385" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B385" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C385" s="10" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D385" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E385" s="10" t="inlineStr">
-        <is>
-          <t>KGA301 Change Agents for Sustainability (12.5% weight (UTAS standard))</t>
-        </is>
-      </c>
-      <c r="F385" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G385" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H385" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I385" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J385" s="10" t="n"/>
-      <c r="K385" s="10" t="inlineStr">
-        <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="386" ht="30" customHeight="1" s="16">
-      <c r="A386" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B386" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C386" s="10" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D386" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E386" s="10" t="inlineStr">
-        <is>
-          <t>KGA207 Systems Thinking (12.5%)</t>
-        </is>
-      </c>
-      <c r="F386" s="10" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G386" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H386" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I386" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J386" s="10" t="n"/>
-      <c r="K386" s="10" t="inlineStr">
-        <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="387" ht="30" customHeight="1" s="16">
-      <c r="A387" s="10" t="inlineStr">
-        <is>
-          <t>University of Tasmania — Australia</t>
-        </is>
-      </c>
-      <c r="B387" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C387" s="10" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D387" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E387" s="10" t="inlineStr">
-        <is>
-          <t>KGA327 Geoheritage and Geotourism (12.5%)</t>
-        </is>
-      </c>
-      <c r="F387" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G387" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H387" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I387" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J387" s="10" t="n"/>
-      <c r="K387" s="10" t="inlineStr">
-        <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+      <c r="G387" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H387" s="9" t="inlineStr">
+        <is>
+          <t>Fall 2026</t>
+        </is>
+      </c>
+      <c r="I387" s="12" t="inlineStr">
+        <is>
+          <t>Semester 1</t>
+        </is>
+      </c>
+      <c r="J387" s="9" t="n"/>
+      <c r="K387" s="9" t="inlineStr">
+        <is>
+          <t>ENVS230 Cities and Regions (same module)</t>
         </is>
       </c>
     </row>
     <row r="388" ht="30" customHeight="1" s="16">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>University of Technology Sydney (UTS) — Australia</t>
+          <t>University of Texas at Dallas — USA</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -24359,12 +24359,12 @@
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>91120 GIS and Remote Sensing</t>
+          <t>GISC4381 Spatial Data Science (3)</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G388" s="9" t="inlineStr">
@@ -24374,12 +24374,12 @@
       </c>
       <c r="H388" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I388" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J388" s="9" t="n"/>
@@ -24392,17 +24392,17 @@
     <row r="389" ht="30" customHeight="1" s="16">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>University of Technology Sydney (UTS) — Australia</t>
+          <t>University of Texas at Dallas — USA</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C389" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
@@ -24412,12 +24412,12 @@
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>91145 Environmental Protection and Management</t>
+          <t>GEOG2302 The Global Environment (3)</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G389" s="9" t="inlineStr">
@@ -24427,25 +24427,25 @@
       </c>
       <c r="H389" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I389" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J389" s="9" t="n"/>
       <c r="K389" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="390" ht="30" customHeight="1" s="16">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>University of Technology Sydney (UTS) — Australia</t>
+          <t>University of Texas at Dallas — USA</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="C390" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
@@ -24465,12 +24465,12 @@
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>91154 Ecology</t>
+          <t>GEOS4430 Hydrogeology and Aqueous Geochemistry (4)</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G390" s="9" t="inlineStr">
@@ -24480,35 +24480,35 @@
       </c>
       <c r="H390" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I390" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J390" s="9" t="n"/>
       <c r="K390" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="391" ht="30" customHeight="1" s="16">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>University of Technology Sydney (UTS) — Australia</t>
+          <t>University of Texas at Dallas — USA</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C391" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
@@ -24518,12 +24518,12 @@
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>91156 Ocean Systems and Climate Change</t>
+          <t>GEOG3331 Smart and Sustainable Cities (3)</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G391" s="9" t="inlineStr">
@@ -24533,25 +24533,25 @@
       </c>
       <c r="H391" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I391" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J391" s="9" t="n"/>
       <c r="K391" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
     <row r="392" ht="30" customHeight="1" s="16">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>University of Technology Sydney (UTS) — Australia</t>
+          <t>University of Texas at Dallas — USA</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -24571,12 +24571,12 @@
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>91309 Biodiversity Conservation</t>
+          <t>GEOS2310 Environmental Geosciences (3)</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G392" s="9" t="inlineStr">
@@ -24586,12 +24586,12 @@
       </c>
       <c r="H392" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I392" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J392" s="9" t="n"/>
@@ -24609,12 +24609,12 @@
       </c>
       <c r="B393" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C393" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D393" s="9" t="inlineStr">
@@ -24624,12 +24624,12 @@
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>GISC2307 Digital Earth (3)</t>
+          <t>GEOG3372 Population and Development (3)</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G393" s="9" t="inlineStr">
@@ -24650,7 +24650,7 @@
       <c r="J393" s="9" t="n"/>
       <c r="K393" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -24667,7 +24667,7 @@
       </c>
       <c r="C394" s="9" t="inlineStr">
         <is>
-          <t>SOES220 CITIES AND REGIONS</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D394" s="9" t="inlineStr">
@@ -24677,12 +24677,12 @@
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>GEOG2303 World Regional Geography (3)</t>
+          <t>GISC3336 Fundamentals of Sustainability (3)</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G394" s="9" t="inlineStr">
@@ -24700,14 +24700,14 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J394" s="9" t="n"/>
-      <c r="K394" s="9" t="inlineStr">
-        <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="395" ht="30" customHeight="1" s="16">
+      <c r="J394" s="12" t="n"/>
+      <c r="K394" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" s="16">
       <c r="A395" s="9" t="inlineStr">
         <is>
           <t>University of Texas at Dallas — USA</t>
@@ -24715,12 +24715,12 @@
       </c>
       <c r="B395" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C395" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
         </is>
       </c>
       <c r="D395" s="9" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>GISC4381 Spatial Data Science (3)</t>
+          <t>GISC4384 Health and Environmental GIS (3)</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
@@ -24753,10 +24753,10 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J395" s="9" t="n"/>
-      <c r="K395" s="9" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+      <c r="J395" s="12" t="n"/>
+      <c r="K395" s="12" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
         </is>
       </c>
     </row>
@@ -24768,12 +24768,12 @@
       </c>
       <c r="B396" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C396" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D396" s="9" t="inlineStr">
@@ -24809,11 +24809,11 @@
       <c r="J396" s="9" t="n"/>
       <c r="K396" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="397" ht="30" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" s="16">
       <c r="A397" s="9" t="inlineStr">
         <is>
           <t>University of Texas at Dallas — USA</t>
@@ -24826,7 +24826,7 @@
       </c>
       <c r="C397" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D397" s="9" t="inlineStr">
@@ -24836,12 +24836,12 @@
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>GEOS4430 Hydrogeology and Aqueous Geochemistry (4)</t>
+          <t>GISC3336 Fundamentals of Sustainability (3)</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G397" s="9" t="inlineStr">
@@ -24859,14 +24859,14 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J397" s="9" t="n"/>
-      <c r="K397" s="9" t="inlineStr">
-        <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="398" ht="30" customHeight="1" s="16">
+      <c r="J397" s="12" t="n"/>
+      <c r="K397" s="12" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" s="16">
       <c r="A398" s="9" t="inlineStr">
         <is>
           <t>University of Texas at Dallas — USA</t>
@@ -24874,12 +24874,12 @@
       </c>
       <c r="B398" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C398" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
@@ -24889,7 +24889,7 @@
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>GEOG3331 Smart and Sustainable Cities (3)</t>
+          <t>GISC4384 Health and Environmental GIS (3)</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
@@ -24912,17 +24912,17 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J398" s="9" t="n"/>
-      <c r="K398" s="9" t="inlineStr">
-        <is>
-          <t>ENVS205 People and Place (closest)</t>
+      <c r="J398" s="12" t="n"/>
+      <c r="K398" s="12" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="399" ht="30" customHeight="1" s="16">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -24942,12 +24942,12 @@
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>GEOS2310 Environmental Geosciences (3)</t>
+          <t>GGR112H5 Physical Geography</t>
         </is>
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G399" s="9" t="inlineStr">
@@ -24975,17 +24975,17 @@
     <row r="400" ht="30" customHeight="1" s="16">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C400" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D400" s="9" t="inlineStr">
@@ -24995,12 +24995,12 @@
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>GEOG3372 Population and Development (3)</t>
+          <t>GGR217H5 Fundamentals of Hydrology</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G400" s="9" t="inlineStr">
@@ -25021,24 +25021,24 @@
       <c r="J400" s="9" t="n"/>
       <c r="K400" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="401" ht="30" customHeight="1" s="16">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C401" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D401" s="9" t="inlineStr">
@@ -25048,12 +25048,12 @@
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>GISC3336 Fundamentals of Sustainability (3)</t>
+          <t>GGR227H5 Ecosystems and Environmental Change</t>
         </is>
       </c>
       <c r="F401" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G401" s="9" t="inlineStr">
@@ -25071,27 +25071,27 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J401" s="12" t="n"/>
-      <c r="K401" s="12" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="402" s="16">
+      <c r="J401" s="9" t="n"/>
+      <c r="K401" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="30" customHeight="1" s="16">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C402" s="9" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D402" s="9" t="inlineStr">
@@ -25101,12 +25101,12 @@
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>GISC4384 Health and Environmental GIS (3)</t>
+          <t>GGR278H5 Introduction to GIScience</t>
         </is>
       </c>
       <c r="F402" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G402" s="9" t="inlineStr">
@@ -25124,17 +25124,17 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J402" s="12" t="n"/>
-      <c r="K402" s="12" t="inlineStr">
-        <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+      <c r="J402" s="9" t="n"/>
+      <c r="K402" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="403" ht="30" customHeight="1" s="16">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="C403" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D403" s="9" t="inlineStr">
@@ -25154,12 +25154,12 @@
       </c>
       <c r="E403" s="9" t="inlineStr">
         <is>
-          <t>GEOG2302 The Global Environment (3)</t>
+          <t>GGR337H5 Environmental Remote Sensing</t>
         </is>
       </c>
       <c r="F403" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G403" s="9" t="inlineStr">
@@ -25180,14 +25180,14 @@
       <c r="J403" s="9" t="n"/>
       <c r="K403" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="404" s="16">
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="30" customHeight="1" s="16">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="C404" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D404" s="9" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>GISC3336 Fundamentals of Sustainability (3)</t>
+          <t>GGR384H5 Climatology of Canadian Landscapes</t>
         </is>
       </c>
       <c r="F404" s="9" t="inlineStr">
@@ -25230,17 +25230,17 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J404" s="12" t="n"/>
-      <c r="K404" s="12" t="inlineStr">
-        <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="405" s="16">
+      <c r="J404" s="9" t="n"/>
+      <c r="K404" s="9" t="inlineStr">
+        <is>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="30" customHeight="1" s="16">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas — USA</t>
+          <t>University of Toronto - Mississauga Campus — Canada</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -25250,7 +25250,7 @@
       </c>
       <c r="C405" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES267 PHYSICAL GEOGRAPHY FIELD SKILLS</t>
         </is>
       </c>
       <c r="D405" s="9" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="E405" s="9" t="inlineStr">
         <is>
-          <t>GISC4384 Health and Environmental GIS (3)</t>
+          <t>GGR379H5 Field Methods in Physical Geography</t>
         </is>
       </c>
       <c r="F405" s="9" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="G405" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H405" s="9" t="inlineStr">
@@ -25283,10 +25283,10 @@
           <t>Semester 1</t>
         </is>
       </c>
-      <c r="J405" s="12" t="n"/>
-      <c r="K405" s="12" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+      <c r="J405" s="9" t="n"/>
+      <c r="K405" s="9" t="inlineStr">
+        <is>
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
         </is>
       </c>
     </row>
@@ -25298,12 +25298,12 @@
       </c>
       <c r="B406" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C406" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES220 CITIES AND REGIONS</t>
         </is>
       </c>
       <c r="D406" s="9" t="inlineStr">
@@ -25313,12 +25313,12 @@
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>GGR112H5 Physical Geography</t>
+          <t>GGR202H5 Geography of Canada (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F406" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G406" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       <c r="J406" s="9" t="n"/>
       <c r="K406" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS230 Cities and Regions (same module)</t>
         </is>
       </c>
     </row>
@@ -25351,12 +25351,12 @@
       </c>
       <c r="B407" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C407" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D407" s="9" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="E407" s="9" t="inlineStr">
         <is>
-          <t>GGR217H5 Fundamentals of Hydrology</t>
+          <t>GGR252H5 Retail Geography (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F407" s="9" t="inlineStr">
@@ -25392,7 +25392,7 @@
       <c r="J407" s="9" t="n"/>
       <c r="K407" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -25404,12 +25404,12 @@
       </c>
       <c r="B408" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C408" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D408" s="9" t="inlineStr">
@@ -25419,12 +25419,12 @@
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>GGR227H5 Ecosystems and Environmental Change</t>
+          <t>GGR301H5 Pandemics, Inequality, and Health: Exploring the Nexus of Health Disparities in Crisis (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G408" s="9" t="inlineStr">
@@ -25445,7 +25445,7 @@
       <c r="J408" s="9" t="n"/>
       <c r="K408" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -25457,12 +25457,12 @@
       </c>
       <c r="B409" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C409" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D409" s="9" t="inlineStr">
@@ -25472,12 +25472,12 @@
       </c>
       <c r="E409" s="9" t="inlineStr">
         <is>
-          <t>GGR278H5 Introduction to GIScience</t>
+          <t>GGR318H5 Political Geography (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F409" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G409" s="9" t="inlineStr">
@@ -25498,7 +25498,7 @@
       <c r="J409" s="9" t="n"/>
       <c r="K409" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -25510,12 +25510,12 @@
       </c>
       <c r="B410" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C410" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D410" s="9" t="inlineStr">
@@ -25525,12 +25525,12 @@
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>GGR337H5 Environmental Remote Sensing</t>
+          <t>GGR209H5 Economic Geography</t>
         </is>
       </c>
       <c r="F410" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G410" s="9" t="inlineStr">
@@ -25551,7 +25551,7 @@
       <c r="J410" s="9" t="n"/>
       <c r="K410" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -25563,12 +25563,12 @@
       </c>
       <c r="B411" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C411" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D411" s="9" t="inlineStr">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="E411" s="9" t="inlineStr">
         <is>
-          <t>GGR384H5 Climatology of Canadian Landscapes</t>
+          <t>GGR313H5 Gender and the City</t>
         </is>
       </c>
       <c r="F411" s="9" t="inlineStr">
@@ -25604,7 +25604,7 @@
       <c r="J411" s="9" t="n"/>
       <c r="K411" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
@@ -25616,12 +25616,12 @@
       </c>
       <c r="B412" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C412" s="9" t="inlineStr">
         <is>
-          <t>SOES267 PHYSICAL GEOGRAPHY FIELD SKILLS</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D412" s="9" t="inlineStr">
@@ -25631,12 +25631,12 @@
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>GGR379H5 Field Methods in Physical Geography</t>
+          <t>GGR277H5 Social Research Methods in Geography</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G412" s="9" t="inlineStr">
@@ -25657,24 +25657,24 @@
       <c r="J412" s="9" t="n"/>
       <c r="K412" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+          <t>ENVS225 Exploring the Social World (same module)</t>
         </is>
       </c>
     </row>
     <row r="413" ht="30" customHeight="1" s="16">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C413" s="9" t="inlineStr">
         <is>
-          <t>SOES220 CITIES AND REGIONS</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D413" s="9" t="inlineStr">
@@ -25684,12 +25684,12 @@
       </c>
       <c r="E413" s="9" t="inlineStr">
         <is>
-          <t>GGR202H5 Geography of Canada (0.5 credit (half course))</t>
+          <t>EESA01H3 Introduction to Environmental Science</t>
         </is>
       </c>
       <c r="F413" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G413" s="9" t="inlineStr">
@@ -25710,24 +25710,24 @@
       <c r="J413" s="9" t="n"/>
       <c r="K413" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
     <row r="414" ht="30" customHeight="1" s="16">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C414" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D414" s="9" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="E414" s="9" t="inlineStr">
         <is>
-          <t>GGR252H5 Retail Geography (0.5 credit (half course))</t>
+          <t>EESB02H3 Principles of Geomorphology</t>
         </is>
       </c>
       <c r="F414" s="9" t="inlineStr">
@@ -25763,24 +25763,24 @@
       <c r="J414" s="9" t="n"/>
       <c r="K414" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
     <row r="415" ht="30" customHeight="1" s="16">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C415" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D415" s="9" t="inlineStr">
@@ -25790,12 +25790,12 @@
       </c>
       <c r="E415" s="9" t="inlineStr">
         <is>
-          <t>GGR301H5 Pandemics, Inequality, and Health: Exploring the Nexus of Health Disparities in Crisis (0.5 credit (half course))</t>
+          <t>EESB04H3 Principles of Hydrology</t>
         </is>
       </c>
       <c r="F415" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G415" s="9" t="inlineStr">
@@ -25816,14 +25816,14 @@
       <c r="J415" s="9" t="n"/>
       <c r="K415" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="416" ht="30" customHeight="1" s="16">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="C416" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D416" s="9" t="inlineStr">
@@ -25843,12 +25843,12 @@
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>GGR318H5 Political Geography (0.5 credit (half course))</t>
+          <t>GGRA02H3 Introduction to Human Geography: Imagining Better Worlds</t>
         </is>
       </c>
       <c r="F416" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G416" s="9" t="inlineStr">
@@ -25869,14 +25869,14 @@
       <c r="J416" s="9" t="n"/>
       <c r="K416" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="417" ht="30" customHeight="1" s="16">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="C417" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D417" s="9" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="E417" s="9" t="inlineStr">
         <is>
-          <t>GGR209H5 Economic Geography</t>
+          <t>GGRB02H3 Geographic Thought: Critical Perspectives on Key Concepts in Human Geography</t>
         </is>
       </c>
       <c r="F417" s="9" t="inlineStr">
@@ -25922,14 +25922,14 @@
       <c r="J417" s="9" t="n"/>
       <c r="K417" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="418" ht="30" customHeight="1" s="16">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -25939,7 +25939,7 @@
       </c>
       <c r="C418" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D418" s="9" t="inlineStr">
@@ -25949,12 +25949,12 @@
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>GGR313H5 Gender and the City</t>
+          <t>GGRB21H3 Political Ecology: Nature, Society and Environmental Change</t>
         </is>
       </c>
       <c r="F418" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G418" s="9" t="inlineStr">
@@ -25975,14 +25975,14 @@
       <c r="J418" s="9" t="n"/>
       <c r="K418" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="419" ht="30" customHeight="1" s="16">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Mississauga Campus — Canada</t>
+          <t>University of Toronto - Scarborough Campus — Canada</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="C419" s="9" t="inlineStr">
         <is>
-          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
         </is>
       </c>
       <c r="D419" s="9" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>GGR277H5 Social Research Methods in Geography</t>
+          <t>GGRB30H3 GIS Principles and Applied Mapping</t>
         </is>
       </c>
       <c r="F419" s="9" t="inlineStr">
@@ -26012,7 +26012,7 @@
       </c>
       <c r="G419" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
@@ -26028,7 +26028,7 @@
       <c r="J419" s="9" t="n"/>
       <c r="K419" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
         </is>
       </c>
     </row>
@@ -26040,12 +26040,12 @@
       </c>
       <c r="B420" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C420" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D420" s="9" t="inlineStr">
@@ -26055,12 +26055,12 @@
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>EESA01H3 Introduction to Environmental Science</t>
+          <t>GGRB18H3 Whose Land? Indigenous-Canada-Land Relations</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G420" s="9" t="inlineStr">
@@ -26081,7 +26081,7 @@
       <c r="J420" s="9" t="n"/>
       <c r="K420" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -26093,12 +26093,12 @@
       </c>
       <c r="B421" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C421" s="9" t="inlineStr">
         <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D421" s="9" t="inlineStr">
@@ -26108,12 +26108,12 @@
       </c>
       <c r="E421" s="9" t="inlineStr">
         <is>
-          <t>EESB02H3 Principles of Geomorphology</t>
+          <t>GGRC13H3 Urban Political Geography</t>
         </is>
       </c>
       <c r="F421" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G421" s="9" t="inlineStr">
@@ -26134,7 +26134,7 @@
       <c r="J421" s="9" t="n"/>
       <c r="K421" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
@@ -26146,12 +26146,12 @@
       </c>
       <c r="B422" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C422" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D422" s="9" t="inlineStr">
@@ -26161,12 +26161,12 @@
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>EESB04H3 Principles of Hydrology</t>
+          <t>GGRC44H3 Environmental Conservation and Sustainable Development</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G422" s="9" t="inlineStr">
@@ -26187,7 +26187,7 @@
       <c r="J422" s="9" t="n"/>
       <c r="K422" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26199,12 +26199,12 @@
       </c>
       <c r="B423" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C423" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D423" s="9" t="inlineStr">
@@ -26214,12 +26214,12 @@
       </c>
       <c r="E423" s="9" t="inlineStr">
         <is>
-          <t>GGRA02H3 Introduction to Human Geography: Imagining Better Worlds</t>
+          <t>GGRB30H3 GIS Principles and Applied Mapping</t>
         </is>
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G423" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
       <c r="J423" s="9" t="n"/>
       <c r="K423" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -26252,12 +26252,12 @@
       </c>
       <c r="B424" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C424" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D424" s="9" t="inlineStr">
@@ -26267,12 +26267,12 @@
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>GGRB02H3 Geographic Thought: Critical Perspectives on Key Concepts in Human Geography</t>
+          <t>GGRC30H3 Advanced GIS</t>
         </is>
       </c>
       <c r="F424" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G424" s="9" t="inlineStr">
@@ -26293,14 +26293,14 @@
       <c r="J424" s="9" t="n"/>
       <c r="K424" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="425" ht="30" customHeight="1" s="16">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="C425" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
         </is>
       </c>
       <c r="D425" s="9" t="inlineStr">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="E425" s="9" t="inlineStr">
         <is>
-          <t>GGRB21H3 Political Ecology: Nature, Society and Environmental Change</t>
+          <t>GGR217H1 Urban Landscapes and Planning (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F425" s="9" t="inlineStr">
@@ -26346,14 +26346,14 @@
       <c r="J425" s="9" t="n"/>
       <c r="K425" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
         </is>
       </c>
     </row>
     <row r="426" ht="30" customHeight="1" s="16">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C426" s="9" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D426" s="9" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>GGRB30H3 GIS Principles and Applied Mapping</t>
+          <t>GGR221H1 New Economic Spaces (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F426" s="9" t="inlineStr">
@@ -26399,14 +26399,14 @@
       <c r="J426" s="9" t="n"/>
       <c r="K426" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="427" ht="30" customHeight="1" s="16">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="E427" s="9" t="inlineStr">
         <is>
-          <t>GGRB18H3 Whose Land? Indigenous-Canada-Land Relations</t>
+          <t>GGR251H1 Geography of Innovation (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F427" s="9" t="inlineStr">
@@ -26459,7 +26459,7 @@
     <row r="428" ht="30" customHeight="1" s="16">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -26479,12 +26479,12 @@
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>GGRC13H3 Urban Political Geography</t>
+          <t>GGR259H1 Urban Growth and Decline (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G428" s="9" t="inlineStr">
@@ -26512,7 +26512,7 @@
     <row r="429" ht="30" customHeight="1" s="16">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -26522,7 +26522,7 @@
       </c>
       <c r="C429" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D429" s="9" t="inlineStr">
@@ -26532,17 +26532,17 @@
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>GGRC44H3 Environmental Conservation and Sustainable Development</t>
+          <t>GGR270H1 Introductory Analytical Methods (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G429" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H429" s="9" t="inlineStr">
@@ -26558,24 +26558,24 @@
       <c r="J429" s="9" t="n"/>
       <c r="K429" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS225 Exploring the Social World (same module)</t>
         </is>
       </c>
     </row>
     <row r="430" ht="30" customHeight="1" s="16">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C430" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
         </is>
       </c>
       <c r="D430" s="9" t="inlineStr">
@@ -26585,12 +26585,12 @@
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>GGRB30H3 GIS Principles and Applied Mapping</t>
+          <t>GGR315H1 Environmental Remote Sensing (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F430" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G430" s="9" t="inlineStr">
@@ -26611,24 +26611,24 @@
       <c r="J430" s="9" t="n"/>
       <c r="K430" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
         </is>
       </c>
     </row>
     <row r="431" ht="30" customHeight="1" s="16">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - Scarborough Campus — Canada</t>
+          <t>University of Toronto - St. George Campus — Canada</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C431" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D431" s="9" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="E431" s="9" t="inlineStr">
         <is>
-          <t>GGRC30H3 Advanced GIS</t>
+          <t>GGR334H1 Water Resource Management (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F431" s="9" t="inlineStr">
@@ -26664,7 +26664,7 @@
       <c r="J431" s="9" t="n"/>
       <c r="K431" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="C432" s="9" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D432" s="9" t="inlineStr">
@@ -26691,12 +26691,12 @@
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>GGR217H1 Urban Landscapes and Planning (0.5 credit (half course))</t>
+          <t>GGR336H1 Urban Historical Geography of North America</t>
         </is>
       </c>
       <c r="F432" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G432" s="9" t="inlineStr">
@@ -26717,7 +26717,7 @@
       <c r="J432" s="9" t="n"/>
       <c r="K432" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="C433" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D433" s="9" t="inlineStr">
@@ -26744,12 +26744,12 @@
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>GGR221H1 New Economic Spaces (0.5 credit (half course))</t>
+          <t>GGR340H1 Health Geography (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G433" s="9" t="inlineStr">
@@ -26770,7 +26770,7 @@
       <c r="J433" s="9" t="n"/>
       <c r="K433" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -26782,12 +26782,12 @@
       </c>
       <c r="B434" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C434" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D434" s="9" t="inlineStr">
@@ -26797,7 +26797,7 @@
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>GGR251H1 Geography of Innovation (0.5 credit (half course))</t>
+          <t>GGR217H1 Urban Landscapes and Planning (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F434" s="9" t="inlineStr">
@@ -26823,7 +26823,7 @@
       <c r="J434" s="9" t="n"/>
       <c r="K434" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
@@ -26835,12 +26835,12 @@
       </c>
       <c r="B435" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C435" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
         </is>
       </c>
       <c r="D435" s="9" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="E435" s="9" t="inlineStr">
         <is>
-          <t>GGR259H1 Urban Growth and Decline (0.5 credit (half course))</t>
+          <t>GGR270H1 Introductory Analytical Methods (0.5 credit (half course))</t>
         </is>
       </c>
       <c r="F435" s="9" t="inlineStr">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="G435" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H435" s="9" t="inlineStr">
@@ -26876,11 +26876,11 @@
       <c r="J435" s="9" t="n"/>
       <c r="K435" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="436" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="45" customHeight="1" s="16">
       <c r="A436" s="9" t="inlineStr">
         <is>
           <t>University of Toronto - St. George Campus — Canada</t>
@@ -26888,12 +26888,12 @@
       </c>
       <c r="B436" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C436" s="9" t="inlineStr">
         <is>
-          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D436" s="9" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="E436" s="9" t="inlineStr">
         <is>
-          <t>GGR270H1 Introductory Analytical Methods (0.5 credit (half course))</t>
+          <t>GGR272H1 Geographic Information and Mapping I</t>
         </is>
       </c>
       <c r="F436" s="9" t="inlineStr">
@@ -26913,7 +26913,7 @@
       </c>
       <c r="G436" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H436" s="9" t="inlineStr">
@@ -26929,7 +26929,7 @@
       <c r="J436" s="9" t="n"/>
       <c r="K436" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -26941,12 +26941,12 @@
       </c>
       <c r="B437" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C437" s="9" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D437" s="9" t="inlineStr">
@@ -26982,7 +26982,7 @@
       <c r="J437" s="9" t="n"/>
       <c r="K437" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="B438" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C438" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D438" s="9" t="inlineStr">
@@ -27035,7 +27035,7 @@
       <c r="J438" s="9" t="n"/>
       <c r="K438" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
@@ -27047,12 +27047,12 @@
       </c>
       <c r="B439" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C439" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D439" s="9" t="inlineStr">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="E439" s="9" t="inlineStr">
         <is>
-          <t>GGR336H1 Urban Historical Geography of North America</t>
+          <t>GGR373H1 Advanced Geographic Information Systems</t>
         </is>
       </c>
       <c r="F439" s="9" t="inlineStr">
@@ -27088,14 +27088,14 @@
       <c r="J439" s="9" t="n"/>
       <c r="K439" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="440" ht="30" customHeight="1" s="16">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -27115,12 +27115,12 @@
       </c>
       <c r="E440" s="9" t="inlineStr">
         <is>
-          <t>GGR340H1 Health Geography (0.5 credit (half course))</t>
+          <t>GEOG101A Environment, Society and Sustainability</t>
         </is>
       </c>
       <c r="F440" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G440" s="9" t="inlineStr">
@@ -27148,17 +27148,17 @@
     <row r="441" ht="30" customHeight="1" s="16">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C441" s="9" t="inlineStr">
         <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D441" s="9" t="inlineStr">
@@ -27168,12 +27168,12 @@
       </c>
       <c r="E441" s="9" t="inlineStr">
         <is>
-          <t>GGR217H1 Urban Landscapes and Planning (0.5 credit (half course))</t>
+          <t>GEOG101B Space, Place and Society</t>
         </is>
       </c>
       <c r="F441" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G441" s="9" t="inlineStr">
@@ -27194,14 +27194,14 @@
       <c r="J441" s="9" t="n"/>
       <c r="K441" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
     <row r="442" ht="30" customHeight="1" s="16">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -27211,7 +27211,7 @@
       </c>
       <c r="C442" s="9" t="inlineStr">
         <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D442" s="9" t="inlineStr">
@@ -27221,17 +27221,17 @@
       </c>
       <c r="E442" s="9" t="inlineStr">
         <is>
-          <t>GGR270H1 Introductory Analytical Methods (0.5 credit (half course))</t>
+          <t>GEOG103 Intro to Physical Geography</t>
         </is>
       </c>
       <c r="F442" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G442" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H442" s="9" t="inlineStr">
@@ -27247,14 +27247,14 @@
       <c r="J442" s="9" t="n"/>
       <c r="K442" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="443" ht="45" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="30" customHeight="1" s="16">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -27274,12 +27274,12 @@
       </c>
       <c r="E443" s="9" t="inlineStr">
         <is>
-          <t>GGR272H1 Geographic Information and Mapping I</t>
+          <t>GEOG104 Our Digital Earth</t>
         </is>
       </c>
       <c r="F443" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G443" s="9" t="inlineStr">
@@ -27307,7 +27307,7 @@
     <row r="444" ht="30" customHeight="1" s="16">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -27327,12 +27327,12 @@
       </c>
       <c r="E444" s="9" t="inlineStr">
         <is>
-          <t>GGR315H1 Environmental Remote Sensing (0.5 credit (half course))</t>
+          <t>GEOG222 Intro to Maps and GIS</t>
         </is>
       </c>
       <c r="F444" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G444" s="9" t="inlineStr">
@@ -27360,7 +27360,7 @@
     <row r="445" ht="30" customHeight="1" s="16">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="C445" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
         </is>
       </c>
       <c r="D445" s="9" t="inlineStr">
@@ -27380,17 +27380,17 @@
       </c>
       <c r="E445" s="9" t="inlineStr">
         <is>
-          <t>GGR334H1 Water Resource Management (0.5 credit (half course))</t>
+          <t>GEOG226 Intro to Quantitative Methods in Geography</t>
         </is>
       </c>
       <c r="F445" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G445" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H445" s="9" t="inlineStr">
@@ -27406,14 +27406,14 @@
       <c r="J445" s="9" t="n"/>
       <c r="K445" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="446" ht="30" customHeight="1" s="16">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>University of Toronto - St. George Campus — Canada</t>
+          <t>University of Victoria (UVic) — Canada</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -27433,12 +27433,12 @@
       </c>
       <c r="E446" s="9" t="inlineStr">
         <is>
-          <t>GGR373H1 Advanced Geographic Information Systems</t>
+          <t>GEOG228 Intro to Remote Sensing</t>
         </is>
       </c>
       <c r="F446" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G446" s="9" t="inlineStr">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="C447" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D447" s="9" t="inlineStr">
@@ -27486,17 +27486,17 @@
       </c>
       <c r="E447" s="9" t="inlineStr">
         <is>
-          <t>GEOG101A Environment, Society and Sustainability</t>
+          <t>GEOG227 Qualitative Research Methods in Geography (1.5 units)</t>
         </is>
       </c>
       <c r="F447" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G447" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H447" s="9" t="inlineStr">
@@ -27512,7 +27512,7 @@
       <c r="J447" s="9" t="n"/>
       <c r="K447" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS225 Exploring the Social World (same module)</t>
         </is>
       </c>
     </row>
@@ -27529,7 +27529,7 @@
       </c>
       <c r="C448" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES220 CITIES AND REGIONS</t>
         </is>
       </c>
       <c r="D448" s="9" t="inlineStr">
@@ -27539,12 +27539,12 @@
       </c>
       <c r="E448" s="9" t="inlineStr">
         <is>
-          <t>GEOG101B Space, Place and Society</t>
+          <t>GEOG306 Geography of Canada (1.5 units)</t>
         </is>
       </c>
       <c r="F448" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G448" s="9" t="inlineStr">
@@ -27565,7 +27565,7 @@
       <c r="J448" s="9" t="n"/>
       <c r="K448" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS230 Cities and Regions (same module)</t>
         </is>
       </c>
     </row>
@@ -27577,12 +27577,12 @@
       </c>
       <c r="B449" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C449" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D449" s="9" t="inlineStr">
@@ -27592,12 +27592,12 @@
       </c>
       <c r="E449" s="9" t="inlineStr">
         <is>
-          <t>GEOG103 Intro to Physical Geography</t>
+          <t>GEOG310 Global Migration (1.5 units)</t>
         </is>
       </c>
       <c r="F449" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G449" s="9" t="inlineStr">
@@ -27618,7 +27618,7 @@
       <c r="J449" s="9" t="n"/>
       <c r="K449" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -27630,12 +27630,12 @@
       </c>
       <c r="B450" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C450" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D450" s="9" t="inlineStr">
@@ -27645,12 +27645,12 @@
       </c>
       <c r="E450" s="9" t="inlineStr">
         <is>
-          <t>GEOG104 Our Digital Earth</t>
+          <t>GEOG318 Indigenous Geographies (1.5 units)</t>
         </is>
       </c>
       <c r="F450" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G450" s="9" t="inlineStr">
@@ -27671,7 +27671,7 @@
       <c r="J450" s="9" t="n"/>
       <c r="K450" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -27683,12 +27683,12 @@
       </c>
       <c r="B451" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C451" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D451" s="9" t="inlineStr">
@@ -27698,12 +27698,12 @@
       </c>
       <c r="E451" s="9" t="inlineStr">
         <is>
-          <t>GEOG222 Intro to Maps and GIS</t>
+          <t>GEOG333 Contemporary Challenges in Global Development (1.5 units)</t>
         </is>
       </c>
       <c r="F451" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G451" s="9" t="inlineStr">
@@ -27724,7 +27724,7 @@
       <c r="J451" s="9" t="n"/>
       <c r="K451" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -27736,12 +27736,12 @@
       </c>
       <c r="B452" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C452" s="9" t="inlineStr">
         <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D452" s="9" t="inlineStr">
@@ -27751,17 +27751,17 @@
       </c>
       <c r="E452" s="9" t="inlineStr">
         <is>
-          <t>GEOG226 Intro to Quantitative Methods in Geography</t>
+          <t>GEOG340 Cities and Planning (1.5 units)</t>
         </is>
       </c>
       <c r="F452" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G452" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H452" s="9" t="inlineStr">
@@ -27777,7 +27777,7 @@
       <c r="J452" s="9" t="n"/>
       <c r="K452" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
@@ -27789,12 +27789,12 @@
       </c>
       <c r="B453" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C453" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D453" s="9" t="inlineStr">
@@ -27804,12 +27804,12 @@
       </c>
       <c r="E453" s="9" t="inlineStr">
         <is>
-          <t>GEOG228 Intro to Remote Sensing</t>
+          <t>GEOG386 Contemporary Geopolitics (1.5 units)</t>
         </is>
       </c>
       <c r="F453" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G453" s="9" t="inlineStr">
@@ -27830,14 +27830,14 @@
       <c r="J453" s="9" t="n"/>
       <c r="K453" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="454" ht="30" customHeight="1" s="16">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="C454" s="9" t="inlineStr">
         <is>
-          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D454" s="9" t="inlineStr">
@@ -27857,7 +27857,7 @@
       </c>
       <c r="E454" s="9" t="inlineStr">
         <is>
-          <t>GEOG227 Qualitative Research Methods in Geography (1.5 units)</t>
+          <t>GEOG202 Economy and Development: Spaces of Global Transformation</t>
         </is>
       </c>
       <c r="F454" s="9" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="G454" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H454" s="9" t="inlineStr">
@@ -27883,24 +27883,24 @@
       <c r="J454" s="9" t="n"/>
       <c r="K454" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="455" ht="30" customHeight="1" s="16">
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="45" customHeight="1" s="16">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C455" s="9" t="inlineStr">
         <is>
-          <t>SOES220 CITIES AND REGIONS</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D455" s="9" t="inlineStr">
@@ -27910,12 +27910,12 @@
       </c>
       <c r="E455" s="9" t="inlineStr">
         <is>
-          <t>GEOG306 Geography of Canada (1.5 units)</t>
+          <t>GDS187 Geospatial Data Science</t>
         </is>
       </c>
       <c r="F455" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G455" s="9" t="inlineStr">
@@ -27936,14 +27936,14 @@
       <c r="J455" s="9" t="n"/>
       <c r="K455" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="456" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="45" customHeight="1" s="16">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -27953,7 +27953,7 @@
       </c>
       <c r="C456" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D456" s="9" t="inlineStr">
@@ -27963,17 +27963,17 @@
       </c>
       <c r="E456" s="9" t="inlineStr">
         <is>
-          <t>GEOG310 Global Migration (1.5 units)</t>
+          <t>ENVS278 Applied Statistics for Environmental Research (0.5 units)</t>
         </is>
       </c>
       <c r="F456" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G456" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H456" s="9" t="inlineStr">
@@ -27989,24 +27989,24 @@
       <c r="J456" s="9" t="n"/>
       <c r="K456" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS225 Exploring the Social World (same module)</t>
         </is>
       </c>
     </row>
     <row r="457" ht="30" customHeight="1" s="16">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C457" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
         </is>
       </c>
       <c r="D457" s="9" t="inlineStr">
@@ -28016,17 +28016,17 @@
       </c>
       <c r="E457" s="9" t="inlineStr">
         <is>
-          <t>GEOG318 Indigenous Geographies (1.5 units)</t>
+          <t>ENVS278 Applied Statistics for Environmental Research (0.5 units)</t>
         </is>
       </c>
       <c r="F457" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G457" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H457" s="9" t="inlineStr">
@@ -28042,14 +28042,14 @@
       <c r="J457" s="9" t="n"/>
       <c r="K457" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="458" ht="30" customHeight="1" s="16">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="C458" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
         </is>
       </c>
       <c r="D458" s="9" t="inlineStr">
@@ -28069,12 +28069,12 @@
       </c>
       <c r="E458" s="9" t="inlineStr">
         <is>
-          <t>GEOG333 Contemporary Challenges in Global Development (1.5 units)</t>
+          <t>GEOG271 Earth from Space Using Remote Sensing</t>
         </is>
       </c>
       <c r="F458" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G458" s="9" t="inlineStr">
@@ -28095,14 +28095,14 @@
       <c r="J458" s="9" t="n"/>
       <c r="K458" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
         </is>
       </c>
     </row>
     <row r="459" ht="30" customHeight="1" s="16">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C459" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES220 CITIES AND REGIONS</t>
         </is>
       </c>
       <c r="D459" s="9" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E459" s="9" t="inlineStr">
         <is>
-          <t>GEOG340 Cities and Planning (1.5 units)</t>
+          <t>GEOG293 Approaches to Research in Human Geography</t>
         </is>
       </c>
       <c r="F459" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G459" s="9" t="inlineStr">
@@ -28148,14 +28148,14 @@
       <c r="J459" s="9" t="n"/>
       <c r="K459" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS230 Cities and Regions (same module)</t>
         </is>
       </c>
     </row>
     <row r="460" ht="30" customHeight="1" s="16">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>University of Victoria (UVic) — Canada</t>
+          <t>University of Waterloo — Canada</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -28165,7 +28165,7 @@
       </c>
       <c r="C460" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D460" s="9" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="E460" s="9" t="inlineStr">
         <is>
-          <t>GEOG386 Contemporary Geopolitics (1.5 units)</t>
+          <t>GEOG325 Geographies of Health</t>
         </is>
       </c>
       <c r="F460" s="9" t="inlineStr">
@@ -28201,11 +28201,11 @@
       <c r="J460" s="9" t="n"/>
       <c r="K460" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="461" ht="30" customHeight="1" s="16">
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="45" customHeight="1" s="16">
       <c r="A461" s="9" t="inlineStr">
         <is>
           <t>University of Waterloo — Canada</t>
@@ -28218,7 +28218,7 @@
       </c>
       <c r="C461" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D461" s="9" t="inlineStr">
@@ -28228,12 +28228,12 @@
       </c>
       <c r="E461" s="9" t="inlineStr">
         <is>
-          <t>GEOG202 Economy and Development: Spaces of Global Transformation</t>
+          <t>GEOG356 Natural Resources Management</t>
         </is>
       </c>
       <c r="F461" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G461" s="9" t="inlineStr">
@@ -28254,11 +28254,11 @@
       <c r="J461" s="9" t="n"/>
       <c r="K461" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="462" ht="45" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="30" customHeight="1" s="16">
       <c r="A462" s="9" t="inlineStr">
         <is>
           <t>University of Waterloo — Canada</t>
@@ -28271,7 +28271,7 @@
       </c>
       <c r="C462" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D462" s="9" t="inlineStr">
@@ -28281,12 +28281,12 @@
       </c>
       <c r="E462" s="9" t="inlineStr">
         <is>
-          <t>GDS187 Geospatial Data Science</t>
+          <t>GEOG205 Landscape Dynamics</t>
         </is>
       </c>
       <c r="F462" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G462" s="9" t="inlineStr">
@@ -28307,11 +28307,11 @@
       <c r="J462" s="9" t="n"/>
       <c r="K462" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="463" ht="45" customHeight="1" s="16">
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="30" customHeight="1" s="16">
       <c r="A463" s="9" t="inlineStr">
         <is>
           <t>University of Waterloo — Canada</t>
@@ -28319,12 +28319,12 @@
       </c>
       <c r="B463" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C463" s="9" t="inlineStr">
         <is>
-          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D463" s="9" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="E463" s="9" t="inlineStr">
         <is>
-          <t>ENVS278 Applied Statistics for Environmental Research (0.5 units)</t>
+          <t>GEOG207 Climate Change Fundamentals</t>
         </is>
       </c>
       <c r="F463" s="9" t="inlineStr">
@@ -28344,7 +28344,7 @@
       </c>
       <c r="G463" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H463" s="9" t="inlineStr">
@@ -28360,7 +28360,7 @@
       <c r="J463" s="9" t="n"/>
       <c r="K463" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="C464" s="9" t="inlineStr">
         <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D464" s="9" t="inlineStr">
@@ -28387,7 +28387,7 @@
       </c>
       <c r="E464" s="9" t="inlineStr">
         <is>
-          <t>ENVS278 Applied Statistics for Environmental Research (0.5 units)</t>
+          <t>GEOG271 Earth from Space Using Remote Sensing</t>
         </is>
       </c>
       <c r="F464" s="9" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="G464" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H464" s="9" t="inlineStr">
@@ -28413,11 +28413,11 @@
       <c r="J464" s="9" t="n"/>
       <c r="K464" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="465" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="45" customHeight="1" s="16">
       <c r="A465" s="9" t="inlineStr">
         <is>
           <t>University of Waterloo — Canada</t>
@@ -28425,12 +28425,12 @@
       </c>
       <c r="B465" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C465" s="9" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D465" s="9" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E465" s="9" t="inlineStr">
         <is>
-          <t>GEOG271 Earth from Space Using Remote Sensing</t>
+          <t>GEOG305 Fluvial Geomorphology</t>
         </is>
       </c>
       <c r="F465" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G465" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
       <c r="J465" s="9" t="n"/>
       <c r="K465" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
@@ -28478,12 +28478,12 @@
       </c>
       <c r="B466" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C466" s="9" t="inlineStr">
         <is>
-          <t>SOES220 CITIES AND REGIONS</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D466" s="9" t="inlineStr">
@@ -28493,12 +28493,12 @@
       </c>
       <c r="E466" s="9" t="inlineStr">
         <is>
-          <t>GEOG293 Approaches to Research in Human Geography</t>
+          <t>GEOG356 Natural Resources Management</t>
         </is>
       </c>
       <c r="F466" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G466" s="9" t="inlineStr">
@@ -28519,7 +28519,7 @@
       <c r="J466" s="9" t="n"/>
       <c r="K466" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -28531,12 +28531,12 @@
       </c>
       <c r="B467" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C467" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D467" s="9" t="inlineStr">
@@ -28546,12 +28546,12 @@
       </c>
       <c r="E467" s="9" t="inlineStr">
         <is>
-          <t>GEOG325 Geographies of Health</t>
+          <t>GDS181 Designing Effective Maps</t>
         </is>
       </c>
       <c r="F467" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G467" s="9" t="inlineStr">
@@ -28572,11 +28572,11 @@
       <c r="J467" s="9" t="n"/>
       <c r="K467" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="468" ht="45" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="30" customHeight="1" s="16">
       <c r="A468" s="9" t="inlineStr">
         <is>
           <t>University of Waterloo — Canada</t>
@@ -28599,12 +28599,12 @@
       </c>
       <c r="E468" s="9" t="inlineStr">
         <is>
-          <t>GEOG356 Natural Resources Management</t>
+          <t>GEOG101 Changing Human Environments</t>
         </is>
       </c>
       <c r="F468" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G468" s="9" t="inlineStr">
@@ -28630,373 +28630,373 @@
       </c>
     </row>
     <row r="469" ht="30" customHeight="1" s="16">
-      <c r="A469" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B469" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C469" s="9" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D469" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E469" s="9" t="inlineStr">
-        <is>
-          <t>GEOG205 Landscape Dynamics</t>
-        </is>
-      </c>
-      <c r="F469" s="9" t="inlineStr">
+      <c r="A469" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B469" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C469" s="10" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D469" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E469" s="10" t="inlineStr">
+        <is>
+          <t>ENVT2222 Environmental and Human Health (6 points)</t>
+        </is>
+      </c>
+      <c r="F469" s="10" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G469" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H469" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I469" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J469" s="9" t="n"/>
-      <c r="K469" s="9" t="inlineStr">
-        <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+      <c r="G469" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H469" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I469" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J469" s="10" t="n"/>
+      <c r="K469" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="470" ht="30" customHeight="1" s="16">
-      <c r="A470" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B470" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C470" s="9" t="inlineStr">
-        <is>
-          <t>SOES280 HYDROCLIMATE</t>
-        </is>
-      </c>
-      <c r="D470" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E470" s="9" t="inlineStr">
-        <is>
-          <t>GEOG207 Climate Change Fundamentals</t>
-        </is>
-      </c>
-      <c r="F470" s="9" t="inlineStr">
+      <c r="A470" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B470" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C470" s="10" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D470" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E470" s="10" t="inlineStr">
+        <is>
+          <t>ENVT2250 Ecology (6 points)</t>
+        </is>
+      </c>
+      <c r="F470" s="10" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G470" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H470" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I470" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J470" s="9" t="n"/>
-      <c r="K470" s="9" t="inlineStr">
-        <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+      <c r="G470" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H470" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I470" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J470" s="10" t="n"/>
+      <c r="K470" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="471" ht="30" customHeight="1" s="16">
-      <c r="A471" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B471" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C471" s="9" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D471" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E471" s="9" t="inlineStr">
-        <is>
-          <t>GEOG271 Earth from Space Using Remote Sensing</t>
-        </is>
-      </c>
-      <c r="F471" s="9" t="inlineStr">
+      <c r="A471" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B471" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C471" s="10" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D471" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E471" s="10" t="inlineStr">
+        <is>
+          <t>ENVT3306 Coastal Conservation and Management (6 points)</t>
+        </is>
+      </c>
+      <c r="F471" s="10" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G471" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H471" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I471" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J471" s="10" t="n"/>
+      <c r="K471" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="30" customHeight="1" s="16">
+      <c r="A472" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B472" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C472" s="10" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D472" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E472" s="10" t="inlineStr">
+        <is>
+          <t>ENVT3361 Environmental Assessment (6 points)</t>
+        </is>
+      </c>
+      <c r="F472" s="10" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G472" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H472" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I472" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J472" s="10" t="n"/>
+      <c r="K472" s="10" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="30" customHeight="1" s="16">
+      <c r="A473" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B473" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C473" s="10" t="inlineStr">
+        <is>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+        </is>
+      </c>
+      <c r="D473" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E473" s="10" t="inlineStr">
+        <is>
+          <t>GEOG1106 Climate Change: Environment and Society</t>
+        </is>
+      </c>
+      <c r="F473" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G473" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H473" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I473" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J473" s="10" t="n"/>
+      <c r="K473" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="30" customHeight="1" s="16">
+      <c r="A474" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B474" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C474" s="10" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D474" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E474" s="10" t="inlineStr">
+        <is>
+          <t>GEOG1107 Global Human Inequality</t>
+        </is>
+      </c>
+      <c r="F474" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G474" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H474" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I474" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J474" s="10" t="n"/>
+      <c r="K474" s="10" t="inlineStr">
+        <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="30" customHeight="1" s="16">
+      <c r="A475" s="10" t="inlineStr">
+        <is>
+          <t>University of Western Australia — Australia</t>
+        </is>
+      </c>
+      <c r="B475" s="10" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C475" s="10" t="inlineStr">
+        <is>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+        </is>
+      </c>
+      <c r="D475" s="10" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E475" s="10" t="inlineStr">
+        <is>
+          <t>GEOG2206 Population Change: Debates and Controversies</t>
+        </is>
+      </c>
+      <c r="F475" s="10" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G471" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H471" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I471" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J471" s="9" t="n"/>
-      <c r="K471" s="9" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="472" ht="45" customHeight="1" s="16">
-      <c r="A472" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B472" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C472" s="9" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D472" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E472" s="9" t="inlineStr">
-        <is>
-          <t>GEOG305 Fluvial Geomorphology</t>
-        </is>
-      </c>
-      <c r="F472" s="9" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G472" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H472" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I472" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J472" s="9" t="n"/>
-      <c r="K472" s="9" t="inlineStr">
-        <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="473" ht="30" customHeight="1" s="16">
-      <c r="A473" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B473" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C473" s="9" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D473" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E473" s="9" t="inlineStr">
-        <is>
-          <t>GEOG356 Natural Resources Management</t>
-        </is>
-      </c>
-      <c r="F473" s="9" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G473" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H473" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I473" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J473" s="9" t="n"/>
-      <c r="K473" s="9" t="inlineStr">
-        <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="474" ht="30" customHeight="1" s="16">
-      <c r="A474" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B474" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C474" s="9" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D474" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E474" s="9" t="inlineStr">
-        <is>
-          <t>GDS181 Designing Effective Maps</t>
-        </is>
-      </c>
-      <c r="F474" s="9" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G474" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H474" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I474" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J474" s="9" t="n"/>
-      <c r="K474" s="9" t="inlineStr">
-        <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="475" ht="30" customHeight="1" s="16">
-      <c r="A475" s="9" t="inlineStr">
-        <is>
-          <t>University of Waterloo — Canada</t>
-        </is>
-      </c>
-      <c r="B475" s="9" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C475" s="9" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D475" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E475" s="9" t="inlineStr">
-        <is>
-          <t>GEOG101 Changing Human Environments</t>
-        </is>
-      </c>
-      <c r="F475" s="9" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G475" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H475" s="9" t="inlineStr">
-        <is>
-          <t>Fall 2026</t>
-        </is>
-      </c>
-      <c r="I475" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J475" s="9" t="n"/>
-      <c r="K475" s="9" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+      <c r="G475" s="10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H475" s="10" t="inlineStr">
+        <is>
+          <t>Semester 1 2027</t>
+        </is>
+      </c>
+      <c r="I475" s="13" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J475" s="10" t="n"/>
+      <c r="K475" s="10" t="inlineStr">
+        <is>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C476" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D476" s="10" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E476" s="10" t="inlineStr">
         <is>
-          <t>ENVT2222 Environmental and Human Health (6 points)</t>
+          <t>GEOG3308 Climate Change: Policy and Practice</t>
         </is>
       </c>
       <c r="F476" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G476" s="10" t="inlineStr">
@@ -29049,7 +29049,7 @@
       <c r="J476" s="10" t="n"/>
       <c r="K476" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
@@ -29066,7 +29066,7 @@
       </c>
       <c r="C477" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D477" s="10" t="inlineStr">
@@ -29076,12 +29076,12 @@
       </c>
       <c r="E477" s="10" t="inlineStr">
         <is>
-          <t>ENVT2250 Ecology (6 points)</t>
+          <t>GEOG3311 Geographies of Economic Development</t>
         </is>
       </c>
       <c r="F477" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G477" s="10" t="inlineStr">
@@ -29102,7 +29102,7 @@
       <c r="J477" s="10" t="n"/>
       <c r="K477" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -29114,12 +29114,12 @@
       </c>
       <c r="B478" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C478" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D478" s="10" t="inlineStr">
@@ -29129,12 +29129,12 @@
       </c>
       <c r="E478" s="10" t="inlineStr">
         <is>
-          <t>ENVT3306 Coastal Conservation and Management (6 points)</t>
+          <t>ENVT2220 The Climate System</t>
         </is>
       </c>
       <c r="F478" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G478" s="10" t="inlineStr">
@@ -29155,7 +29155,7 @@
       <c r="J478" s="10" t="n"/>
       <c r="K478" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
@@ -29167,12 +29167,12 @@
       </c>
       <c r="B479" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C479" s="10" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D479" s="10" t="inlineStr">
@@ -29182,12 +29182,12 @@
       </c>
       <c r="E479" s="10" t="inlineStr">
         <is>
-          <t>ENVT3361 Environmental Assessment (6 points)</t>
+          <t>ENVT2236 Soil Science (6 points)</t>
         </is>
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G479" s="10" t="inlineStr">
@@ -29208,7 +29208,7 @@
       <c r="J479" s="10" t="n"/>
       <c r="K479" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
@@ -29220,12 +29220,12 @@
       </c>
       <c r="B480" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C480" s="10" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D480" s="10" t="inlineStr">
@@ -29235,12 +29235,12 @@
       </c>
       <c r="E480" s="10" t="inlineStr">
         <is>
-          <t>GEOG1106 Climate Change: Environment and Society</t>
+          <t>ENVT2250 Ecology (6 points)</t>
         </is>
       </c>
       <c r="F480" s="10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G480" s="10" t="inlineStr">
@@ -29261,7 +29261,7 @@
       <c r="J480" s="10" t="n"/>
       <c r="K480" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
@@ -29273,12 +29273,12 @@
       </c>
       <c r="B481" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C481" s="10" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
       <c r="D481" s="10" t="inlineStr">
@@ -29288,12 +29288,12 @@
       </c>
       <c r="E481" s="10" t="inlineStr">
         <is>
-          <t>GEOG1107 Global Human Inequality</t>
+          <t>ENVT3306 Coastal Conservation and Management (6 points)</t>
         </is>
       </c>
       <c r="F481" s="10" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G481" s="10" t="inlineStr">
@@ -29314,7 +29314,7 @@
       <c r="J481" s="10" t="n"/>
       <c r="K481" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
@@ -29326,12 +29326,12 @@
       </c>
       <c r="B482" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C482" s="10" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D482" s="10" t="inlineStr">
@@ -29341,12 +29341,12 @@
       </c>
       <c r="E482" s="10" t="inlineStr">
         <is>
-          <t>GEOG2206 Population Change: Debates and Controversies</t>
+          <t>ENVT3361 Environmental Assessment (6 points)</t>
         </is>
       </c>
       <c r="F482" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G482" s="10" t="inlineStr">
@@ -29367,7 +29367,7 @@
       <c r="J482" s="10" t="n"/>
       <c r="K482" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -29379,12 +29379,12 @@
       </c>
       <c r="B483" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C483" s="10" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D483" s="10" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="E483" s="10" t="inlineStr">
         <is>
-          <t>GEOG3308 Climate Change: Policy and Practice</t>
+          <t>GEOG3300 Advanced Spatial Analysis</t>
         </is>
       </c>
       <c r="F483" s="10" t="inlineStr">
@@ -29420,7 +29420,7 @@
       <c r="J483" s="10" t="n"/>
       <c r="K483" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -29432,12 +29432,12 @@
       </c>
       <c r="B484" s="10" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C484" s="10" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D484" s="10" t="inlineStr">
@@ -29447,12 +29447,12 @@
       </c>
       <c r="E484" s="10" t="inlineStr">
         <is>
-          <t>GEOG3311 Geographies of Economic Development</t>
+          <t>GEOG2201 Geographic Information Systems</t>
         </is>
       </c>
       <c r="F484" s="10" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G484" s="10" t="inlineStr">
@@ -29473,24 +29473,24 @@
       <c r="J484" s="10" t="n"/>
       <c r="K484" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="485" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="45" customHeight="1" s="16">
       <c r="A485" s="10" t="inlineStr">
         <is>
-          <t>University of Western Australia — Australia</t>
+          <t>University of Wollongong — Australia</t>
         </is>
       </c>
       <c r="B485" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C485" s="10" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D485" s="10" t="inlineStr">
@@ -29500,12 +29500,12 @@
       </c>
       <c r="E485" s="10" t="inlineStr">
         <is>
-          <t>ENVT2220 The Climate System</t>
+          <t>EESC328 Dung, Death and Decay: Modern Methods in Geosciences and Archaeology (6 CP)</t>
         </is>
       </c>
       <c r="F485" s="10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G485" s="10" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H485" s="10" t="inlineStr">
         <is>
-          <t>Semester 1 2027</t>
+          <t>Autumn session 2027</t>
         </is>
       </c>
       <c r="I485" s="13" t="inlineStr">
@@ -29526,24 +29526,24 @@
       <c r="J485" s="10" t="n"/>
       <c r="K485" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="486" ht="30" customHeight="1" s="16">
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="45" customHeight="1" s="16">
       <c r="A486" s="10" t="inlineStr">
         <is>
-          <t>University of Western Australia — Australia</t>
+          <t>University of Wollongong — Australia</t>
         </is>
       </c>
       <c r="B486" s="10" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C486" s="10" t="inlineStr">
         <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D486" s="10" t="inlineStr">
@@ -29553,7 +29553,7 @@
       </c>
       <c r="E486" s="10" t="inlineStr">
         <is>
-          <t>ENVT2236 Soil Science (6 points)</t>
+          <t>GEOG221 Population, Migration, Inequality (6 CP)</t>
         </is>
       </c>
       <c r="F486" s="10" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="H486" s="10" t="inlineStr">
         <is>
-          <t>Semester 1 2027</t>
+          <t>Autumn session 2027</t>
         </is>
       </c>
       <c r="I486" s="13" t="inlineStr">
@@ -29579,378 +29579,378 @@
       <c r="J486" s="10" t="n"/>
       <c r="K486" s="10" t="inlineStr">
         <is>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="30" customHeight="1" s="16">
+      <c r="A487" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B487" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C487" s="9" t="inlineStr">
+        <is>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="D487" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E487" s="9" t="inlineStr">
+        <is>
+          <t>GEOG241 Just and Sustainable Cities? (6 CP)</t>
+        </is>
+      </c>
+      <c r="F487" s="9" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G487" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H487" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I487" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J487" s="9" t="n"/>
+      <c r="K487" s="9" t="inlineStr">
+        <is>
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="30" customHeight="1" s="16">
+      <c r="A488" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B488" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C488" s="9" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D488" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E488" s="9" t="inlineStr">
+        <is>
+          <t>GEOG354 Environmental Crime and Justice (6 CP)</t>
+        </is>
+      </c>
+      <c r="F488" s="9" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G488" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H488" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I488" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J488" s="9" t="n"/>
+      <c r="K488" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="30" customHeight="1" s="16">
+      <c r="A489" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B489" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C489" s="9" t="inlineStr">
+        <is>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D489" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E489" s="9" t="inlineStr">
+        <is>
+          <t>EESC203 Biogeography and Environmental Change (6 CP)</t>
+        </is>
+      </c>
+      <c r="F489" s="9" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G489" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H489" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I489" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J489" s="9" t="n"/>
+      <c r="K489" s="9" t="inlineStr">
+        <is>
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="30" customHeight="1" s="16">
+      <c r="A490" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B490" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C490" s="9" t="inlineStr">
+        <is>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+        </is>
+      </c>
+      <c r="D490" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E490" s="9" t="inlineStr">
+        <is>
+          <t>EESC323 River Processes (6 CP)</t>
+        </is>
+      </c>
+      <c r="F490" s="9" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G490" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H490" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I490" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J490" s="9" t="n"/>
+      <c r="K490" s="9" t="inlineStr">
+        <is>
           <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
         </is>
       </c>
     </row>
-    <row r="487" ht="30" customHeight="1" s="16">
-      <c r="A487" s="10" t="inlineStr">
-        <is>
-          <t>University of Western Australia — Australia</t>
-        </is>
-      </c>
-      <c r="B487" s="10" t="inlineStr">
+    <row r="491" ht="30" customHeight="1" s="16">
+      <c r="A491" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B491" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C491" s="9" t="inlineStr">
+        <is>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+        </is>
+      </c>
+      <c r="D491" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E491" s="9" t="inlineStr">
+        <is>
+          <t>SCII311 Applied Geospatial Analysis (6 CP)</t>
+        </is>
+      </c>
+      <c r="F491" s="9" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G491" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H491" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I491" s="12" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="J491" s="9" t="n"/>
+      <c r="K491" s="9" t="inlineStr">
+        <is>
+          <t>ENVS257 GIS for Human Geography (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="30" customHeight="1" s="16">
+      <c r="A492" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B492" s="9" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C487" s="10" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D487" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E487" s="10" t="inlineStr">
-        <is>
-          <t>ENVT2250 Ecology (6 points)</t>
-        </is>
-      </c>
-      <c r="F487" s="10" t="inlineStr">
+      <c r="C492" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D492" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E492" s="9" t="inlineStr">
+        <is>
+          <t>SCII205 Introductory Geospatial Analysis (6 CP)</t>
+        </is>
+      </c>
+      <c r="F492" s="9" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G487" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H487" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I487" s="13" t="inlineStr">
+      <c r="G492" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H492" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I492" s="12" t="inlineStr">
         <is>
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="J487" s="10" t="n"/>
-      <c r="K487" s="10" t="inlineStr">
-        <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="488" ht="30" customHeight="1" s="16">
-      <c r="A488" s="10" t="inlineStr">
-        <is>
-          <t>University of Western Australia — Australia</t>
-        </is>
-      </c>
-      <c r="B488" s="10" t="inlineStr">
+      <c r="J492" s="9" t="n"/>
+      <c r="K492" s="9" t="inlineStr">
+        <is>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="30" customHeight="1" s="16">
+      <c r="A493" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong — Australia</t>
+        </is>
+      </c>
+      <c r="B493" s="9" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C488" s="10" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D488" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E488" s="10" t="inlineStr">
-        <is>
-          <t>ENVT3306 Coastal Conservation and Management (6 points)</t>
-        </is>
-      </c>
-      <c r="F488" s="10" t="inlineStr">
+      <c r="C493" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D493" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E493" s="9" t="inlineStr">
+        <is>
+          <t>SCII311 Applied Geospatial Analysis (6 CP)</t>
+        </is>
+      </c>
+      <c r="F493" s="9" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G488" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H488" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I488" s="13" t="inlineStr">
+      <c r="G493" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H493" s="9" t="inlineStr">
+        <is>
+          <t>Autumn session 2027</t>
+        </is>
+      </c>
+      <c r="I493" s="12" t="inlineStr">
         <is>
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="J488" s="10" t="n"/>
-      <c r="K488" s="10" t="inlineStr">
-        <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="489" ht="30" customHeight="1" s="16">
-      <c r="A489" s="10" t="inlineStr">
-        <is>
-          <t>University of Western Australia — Australia</t>
-        </is>
-      </c>
-      <c r="B489" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C489" s="10" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D489" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E489" s="10" t="inlineStr">
-        <is>
-          <t>ENVT3361 Environmental Assessment (6 points)</t>
-        </is>
-      </c>
-      <c r="F489" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G489" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H489" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I489" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J489" s="10" t="n"/>
-      <c r="K489" s="10" t="inlineStr">
-        <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="490" ht="30" customHeight="1" s="16">
-      <c r="A490" s="10" t="inlineStr">
-        <is>
-          <t>University of Western Australia — Australia</t>
-        </is>
-      </c>
-      <c r="B490" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C490" s="10" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D490" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E490" s="10" t="inlineStr">
-        <is>
-          <t>GEOG3300 Advanced Spatial Analysis</t>
-        </is>
-      </c>
-      <c r="F490" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G490" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H490" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I490" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J490" s="10" t="n"/>
-      <c r="K490" s="10" t="inlineStr">
+      <c r="J493" s="9" t="n"/>
+      <c r="K493" s="9" t="inlineStr">
         <is>
           <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="491" ht="30" customHeight="1" s="16">
-      <c r="A491" s="10" t="inlineStr">
-        <is>
-          <t>University of Western Australia — Australia</t>
-        </is>
-      </c>
-      <c r="B491" s="10" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C491" s="10" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D491" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E491" s="10" t="inlineStr">
-        <is>
-          <t>GEOG2201 Geographic Information Systems</t>
-        </is>
-      </c>
-      <c r="F491" s="10" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G491" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H491" s="10" t="inlineStr">
-        <is>
-          <t>Semester 1 2027</t>
-        </is>
-      </c>
-      <c r="I491" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J491" s="10" t="n"/>
-      <c r="K491" s="10" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="492" ht="45" customHeight="1" s="16">
-      <c r="A492" s="10" t="inlineStr">
-        <is>
-          <t>University of Wollongong — Australia</t>
-        </is>
-      </c>
-      <c r="B492" s="10" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C492" s="10" t="inlineStr">
-        <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
-        </is>
-      </c>
-      <c r="D492" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E492" s="10" t="inlineStr">
-        <is>
-          <t>EESC328 Dung, Death and Decay: Modern Methods in Geosciences and Archaeology (6 CP)</t>
-        </is>
-      </c>
-      <c r="F492" s="10" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G492" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H492" s="10" t="inlineStr">
-        <is>
-          <t>Autumn session 2027</t>
-        </is>
-      </c>
-      <c r="I492" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J492" s="10" t="n"/>
-      <c r="K492" s="10" t="inlineStr">
-        <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="493" ht="45" customHeight="1" s="16">
-      <c r="A493" s="10" t="inlineStr">
-        <is>
-          <t>University of Wollongong — Australia</t>
-        </is>
-      </c>
-      <c r="B493" s="10" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C493" s="10" t="inlineStr">
-        <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
-        </is>
-      </c>
-      <c r="D493" s="10" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E493" s="10" t="inlineStr">
-        <is>
-          <t>GEOG221 Population, Migration, Inequality (6 CP)</t>
-        </is>
-      </c>
-      <c r="F493" s="10" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G493" s="10" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H493" s="10" t="inlineStr">
-        <is>
-          <t>Autumn session 2027</t>
-        </is>
-      </c>
-      <c r="I493" s="13" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J493" s="10" t="n"/>
-      <c r="K493" s="10" t="inlineStr">
-        <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -29962,12 +29962,12 @@
       </c>
       <c r="B494" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C494" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D494" s="9" t="inlineStr">
@@ -29977,7 +29977,7 @@
       </c>
       <c r="E494" s="9" t="inlineStr">
         <is>
-          <t>GEOG241 Just and Sustainable Cities? (6 CP)</t>
+          <t>BIOL251 Principles of Ecology (6 CP)</t>
         </is>
       </c>
       <c r="F494" s="9" t="inlineStr">
@@ -30003,7 +30003,7 @@
       <c r="J494" s="9" t="n"/>
       <c r="K494" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -30015,12 +30015,12 @@
       </c>
       <c r="B495" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C495" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D495" s="9" t="inlineStr">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="E495" s="9" t="inlineStr">
         <is>
-          <t>GEOG354 Environmental Crime and Justice (6 CP)</t>
+          <t>BIOL361 Conservation Biology (6 CP)</t>
         </is>
       </c>
       <c r="F495" s="9" t="inlineStr">
@@ -30056,14 +30056,14 @@
       <c r="J495" s="9" t="n"/>
       <c r="K495" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
     <row r="496" ht="30" customHeight="1" s="16">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="C496" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D496" s="9" t="inlineStr">
@@ -30083,12 +30083,12 @@
       </c>
       <c r="E496" s="9" t="inlineStr">
         <is>
-          <t>EESC203 Biogeography and Environmental Change (6 CP)</t>
+          <t>GEOS305 Introductory Atmospheric Science (20 points)</t>
         </is>
       </c>
       <c r="F496" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G496" s="9" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="H496" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I496" s="12" t="inlineStr">
@@ -30109,24 +30109,24 @@
       <c r="J496" s="9" t="n"/>
       <c r="K496" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="497" ht="30" customHeight="1" s="16">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C497" s="9" t="inlineStr">
         <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D497" s="9" t="inlineStr">
@@ -30136,12 +30136,12 @@
       </c>
       <c r="E497" s="9" t="inlineStr">
         <is>
-          <t>EESC323 River Processes (6 CP)</t>
+          <t>GEOG212 Worlds of Development (20 points)</t>
         </is>
       </c>
       <c r="F497" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G497" s="9" t="inlineStr">
@@ -30151,7 +30151,7 @@
       </c>
       <c r="H497" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I497" s="12" t="inlineStr">
@@ -30162,14 +30162,14 @@
       <c r="J497" s="9" t="n"/>
       <c r="K497" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="498" ht="30" customHeight="1" s="16">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -30179,7 +30179,7 @@
       </c>
       <c r="C498" s="9" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D498" s="9" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="E498" s="9" t="inlineStr">
         <is>
-          <t>SCII311 Applied Geospatial Analysis (6 CP)</t>
+          <t>GEOG306 Diverse Economies and Development: Shaping Ethical and Ecological Futures (20 points)</t>
         </is>
       </c>
       <c r="F498" s="9" t="inlineStr">
@@ -30204,7 +30204,7 @@
       </c>
       <c r="H498" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I498" s="12" t="inlineStr">
@@ -30215,24 +30215,24 @@
       <c r="J498" s="9" t="n"/>
       <c r="K498" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="499" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="60" customHeight="1" s="16">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C499" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D499" s="9" t="inlineStr">
@@ -30242,22 +30242,22 @@
       </c>
       <c r="E499" s="9" t="inlineStr">
         <is>
-          <t>SCII205 Introductory Geospatial Analysis (6 CP)</t>
+          <t>GEOG326 Research Project: Design and Methods (20 points)</t>
         </is>
       </c>
       <c r="F499" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G499" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H499" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I499" s="12" t="inlineStr">
@@ -30268,24 +30268,24 @@
       <c r="J499" s="9" t="n"/>
       <c r="K499" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="500" ht="30" customHeight="1" s="16">
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="60" customHeight="1" s="16">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C500" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D500" s="9" t="inlineStr">
@@ -30295,7 +30295,7 @@
       </c>
       <c r="E500" s="9" t="inlineStr">
         <is>
-          <t>SCII311 Applied Geospatial Analysis (6 CP)</t>
+          <t>GEOS308 Sustainable Resources and Infrastructure (20 points)</t>
         </is>
       </c>
       <c r="F500" s="9" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="H500" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I500" s="12" t="inlineStr">
@@ -30321,24 +30321,24 @@
       <c r="J500" s="9" t="n"/>
       <c r="K500" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="501" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="60" customHeight="1" s="16">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C501" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D501" s="9" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E501" s="9" t="inlineStr">
         <is>
-          <t>BIOL251 Principles of Ecology (6 CP)</t>
+          <t>INTP302 Global Politics of the Environment (20 points)</t>
         </is>
       </c>
       <c r="F501" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G501" s="9" t="inlineStr">
@@ -30363,7 +30363,7 @@
       </c>
       <c r="H501" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I501" s="12" t="inlineStr">
@@ -30374,24 +30374,24 @@
       <c r="J501" s="9" t="n"/>
       <c r="K501" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="502" ht="30" customHeight="1" s="16">
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="60" customHeight="1" s="16">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>University of Wollongong — Australia</t>
+          <t>Victoria University of Wellington — New Zealand</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C502" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D502" s="9" t="inlineStr">
@@ -30401,7 +30401,7 @@
       </c>
       <c r="E502" s="9" t="inlineStr">
         <is>
-          <t>BIOL361 Conservation Biology (6 CP)</t>
+          <t>PUBL307 Environmental Policy and Governance (20 points)</t>
         </is>
       </c>
       <c r="F502" s="9" t="inlineStr">
@@ -30416,7 +30416,7 @@
       </c>
       <c r="H502" s="9" t="inlineStr">
         <is>
-          <t>Autumn session 2027</t>
+          <t>Trimester 1 2027</t>
         </is>
       </c>
       <c r="I502" s="12" t="inlineStr">
@@ -30427,11 +30427,11 @@
       <c r="J502" s="9" t="n"/>
       <c r="K502" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="503" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (new module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="60" customHeight="1" s="16">
       <c r="A503" s="9" t="inlineStr">
         <is>
           <t>Victoria University of Wellington — New Zealand</t>
@@ -30439,12 +30439,12 @@
       </c>
       <c r="B503" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C503" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D503" s="9" t="inlineStr">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="E503" s="9" t="inlineStr">
         <is>
-          <t>GEOS305 Introductory Atmospheric Science (20 points)</t>
+          <t>ANTH319 Anthropology of Food and Eating (20 points)</t>
         </is>
       </c>
       <c r="F503" s="9" t="inlineStr">
@@ -30480,11 +30480,11 @@
       <c r="J503" s="9" t="n"/>
       <c r="K503" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="504" ht="30" customHeight="1" s="16">
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="60" customHeight="1" s="16">
       <c r="A504" s="9" t="inlineStr">
         <is>
           <t>Victoria University of Wellington — New Zealand</t>
@@ -30492,12 +30492,12 @@
       </c>
       <c r="B504" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C504" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES267 PHYSICAL GEOGRAPHY FIELD SKILLS</t>
         </is>
       </c>
       <c r="D504" s="9" t="inlineStr">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="E504" s="9" t="inlineStr">
         <is>
-          <t>GEOG212 Worlds of Development (20 points)</t>
+          <t>GEOS210 Introductory Field Methods (20 points)</t>
         </is>
       </c>
       <c r="F504" s="9" t="inlineStr">
@@ -30517,7 +30517,7 @@
       </c>
       <c r="G504" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H504" s="9" t="inlineStr">
@@ -30533,11 +30533,11 @@
       <c r="J504" s="9" t="n"/>
       <c r="K504" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="505" ht="30" customHeight="1" s="16">
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="60" customHeight="1" s="16">
       <c r="A505" s="9" t="inlineStr">
         <is>
           <t>Victoria University of Wellington — New Zealand</t>
@@ -30545,12 +30545,12 @@
       </c>
       <c r="B505" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C505" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D505" s="9" t="inlineStr">
@@ -30560,12 +30560,12 @@
       </c>
       <c r="E505" s="9" t="inlineStr">
         <is>
-          <t>GEOG306 Diverse Economies and Development: Shaping Ethical and Ecological Futures (20 points)</t>
+          <t>GEOS211 Earth’s Changing Surface (20 points)</t>
         </is>
       </c>
       <c r="F505" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G505" s="9" t="inlineStr">
@@ -30586,7 +30586,7 @@
       <c r="J505" s="9" t="n"/>
       <c r="K505" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -30598,12 +30598,12 @@
       </c>
       <c r="B506" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C506" s="9" t="inlineStr">
         <is>
-          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D506" s="9" t="inlineStr">
@@ -30613,7 +30613,7 @@
       </c>
       <c r="E506" s="9" t="inlineStr">
         <is>
-          <t>GEOG326 Research Project: Design and Methods (20 points)</t>
+          <t>GEOS308 Sustainable Resources and Infrastructure (20 points)</t>
         </is>
       </c>
       <c r="F506" s="9" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="G506" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H506" s="9" t="inlineStr">
@@ -30639,11 +30639,11 @@
       <c r="J506" s="9" t="n"/>
       <c r="K506" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="507" ht="60" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="30" customHeight="1" s="16">
       <c r="A507" s="9" t="inlineStr">
         <is>
           <t>Victoria University of Wellington — New Zealand</t>
@@ -30651,12 +30651,12 @@
       </c>
       <c r="B507" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C507" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES267 PHYSICAL GEOGRAPHY FIELD SKILLS</t>
         </is>
       </c>
       <c r="D507" s="9" t="inlineStr">
@@ -30666,7 +30666,7 @@
       </c>
       <c r="E507" s="9" t="inlineStr">
         <is>
-          <t>GEOS308 Sustainable Resources and Infrastructure (20 points)</t>
+          <t>GEOS310 Advanced Field Methods (20 points)</t>
         </is>
       </c>
       <c r="F507" s="9" t="inlineStr">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="G507" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H507" s="9" t="inlineStr">
@@ -30692,11 +30692,11 @@
       <c r="J507" s="9" t="n"/>
       <c r="K507" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="508" ht="60" customHeight="1" s="16">
+          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="30" customHeight="1" s="16">
       <c r="A508" s="9" t="inlineStr">
         <is>
           <t>Victoria University of Wellington — New Zealand</t>
@@ -30704,12 +30704,12 @@
       </c>
       <c r="B508" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C508" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D508" s="9" t="inlineStr">
@@ -30719,7 +30719,7 @@
       </c>
       <c r="E508" s="9" t="inlineStr">
         <is>
-          <t>INTP302 Global Politics of the Environment (20 points)</t>
+          <t>GEOS312 Topics in Environmental Science (20 points)</t>
         </is>
       </c>
       <c r="F508" s="9" t="inlineStr">
@@ -30745,24 +30745,24 @@
       <c r="J508" s="9" t="n"/>
       <c r="K508" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="509" ht="60" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="30" customHeight="1" s="16">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C509" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D509" s="9" t="inlineStr">
@@ -30772,12 +30772,12 @@
       </c>
       <c r="E509" s="9" t="inlineStr">
         <is>
-          <t>PUBL307 Environmental Policy and Governance (20 points)</t>
+          <t>SOE 210 Earth History &amp; Evolution</t>
         </is>
       </c>
       <c r="F509" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G509" s="9" t="inlineStr">
@@ -30787,35 +30787,35 @@
       </c>
       <c r="H509" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I509" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J509" s="9" t="n"/>
       <c r="K509" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="510" ht="60" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="30" customHeight="1" s="16">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C510" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D510" s="9" t="inlineStr">
@@ -30825,12 +30825,12 @@
       </c>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>ANTH319 Anthropology of Food and Eating (20 points)</t>
+          <t>SOE 275 Rivers: Form, Function and Management</t>
         </is>
       </c>
       <c r="F510" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G510" s="9" t="inlineStr">
@@ -30840,25 +30840,25 @@
       </c>
       <c r="H510" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I510" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J510" s="9" t="n"/>
       <c r="K510" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="511" ht="60" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="30" customHeight="1" s="16">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -30868,7 +30868,7 @@
       </c>
       <c r="C511" s="9" t="inlineStr">
         <is>
-          <t>SOES267 PHYSICAL GEOGRAPHY FIELD SKILLS</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D511" s="9" t="inlineStr">
@@ -30878,40 +30878,40 @@
       </c>
       <c r="E511" s="9" t="inlineStr">
         <is>
-          <t>GEOS210 Introductory Field Methods (20 points)</t>
+          <t>SOE 300 Natural Resources Ecology</t>
         </is>
       </c>
       <c r="F511" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G511" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H511" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I511" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J511" s="9" t="n"/>
       <c r="K511" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="512" ht="60" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="30" customHeight="1" s="16">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -30921,7 +30921,7 @@
       </c>
       <c r="C512" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D512" s="9" t="inlineStr">
@@ -30931,12 +30931,12 @@
       </c>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>GEOS211 Earth’s Changing Surface (20 points)</t>
+          <t>SOE 315 Water &amp; Earth</t>
         </is>
       </c>
       <c r="F512" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G512" s="9" t="inlineStr">
@@ -30946,25 +30946,25 @@
       </c>
       <c r="H512" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I512" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J512" s="9" t="n"/>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="513" ht="60" customHeight="1" s="16">
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="30" customHeight="1" s="16">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="C513" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D513" s="9" t="inlineStr">
@@ -30984,7 +30984,7 @@
       </c>
       <c r="E513" s="9" t="inlineStr">
         <is>
-          <t>GEOS308 Sustainable Resources and Infrastructure (20 points)</t>
+          <t>SOIL SCI 368 Introduction to GIS</t>
         </is>
       </c>
       <c r="F513" s="9" t="inlineStr">
@@ -30999,25 +30999,25 @@
       </c>
       <c r="H513" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I513" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J513" s="9" t="n"/>
       <c r="K513" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="514" ht="30" customHeight="1" s="16">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -31027,7 +31027,7 @@
       </c>
       <c r="C514" s="9" t="inlineStr">
         <is>
-          <t>SOES267 PHYSICAL GEOGRAPHY FIELD SKILLS</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D514" s="9" t="inlineStr">
@@ -31037,40 +31037,40 @@
       </c>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>GEOS310 Advanced Field Methods (20 points)</t>
+          <t>SOE 101 Welcome to the Earth: An Introduction to Geology (4 credits)</t>
         </is>
       </c>
       <c r="F514" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H514" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I514" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J514" s="9" t="n"/>
       <c r="K514" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
     <row r="515" ht="30" customHeight="1" s="16">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>Victoria University of Wellington — New Zealand</t>
+          <t>Washington State University — USA</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -31090,12 +31090,12 @@
       </c>
       <c r="E515" s="9" t="inlineStr">
         <is>
-          <t>GEOS312 Topics in Environmental Science (20 points)</t>
+          <t>SOE 464 Landscape Ecology (3 credits)</t>
         </is>
       </c>
       <c r="F515" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G515" s="9" t="inlineStr">
@@ -31105,12 +31105,12 @@
       </c>
       <c r="H515" s="9" t="inlineStr">
         <is>
-          <t>Trimester 1 2027</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I515" s="12" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Semester 1</t>
         </is>
       </c>
       <c r="J515" s="9" t="n"/>
@@ -31133,7 +31133,7 @@
       </c>
       <c r="C516" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D516" s="9" t="inlineStr">
@@ -31143,12 +31143,12 @@
       </c>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>SOE 210 Earth History &amp; Evolution</t>
+          <t>SOE 475 Groundwater (3 credits)</t>
         </is>
       </c>
       <c r="F516" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G516" s="9" t="inlineStr">
@@ -31169,24 +31169,24 @@
       <c r="J516" s="9" t="n"/>
       <c r="K516" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="517" ht="30" customHeight="1" s="16">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C517" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES220 CITIES AND REGIONS</t>
         </is>
       </c>
       <c r="D517" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
       </c>
       <c r="E517" s="9" t="inlineStr">
         <is>
-          <t>SOE 275 Rivers: Form, Function and Management</t>
+          <t>GEOGENV2010A/B Geography Of Canada (0.5 course)</t>
         </is>
       </c>
       <c r="F517" s="9" t="inlineStr">
@@ -31222,24 +31222,24 @@
       <c r="J517" s="9" t="n"/>
       <c r="K517" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS230 Cities and Regions (same module)</t>
         </is>
       </c>
     </row>
     <row r="518" ht="30" customHeight="1" s="16">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C518" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D518" s="9" t="inlineStr">
@@ -31249,12 +31249,12 @@
       </c>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>SOE 300 Natural Resources Ecology</t>
+          <t>GEOGENV2144A/B Geography Of Tourism (0.5 course)</t>
         </is>
       </c>
       <c r="F518" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G518" s="9" t="inlineStr">
@@ -31275,24 +31275,24 @@
       <c r="J518" s="9" t="n"/>
       <c r="K518" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
     <row r="519" ht="30" customHeight="1" s="16">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C519" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D519" s="9" t="inlineStr">
@@ -31302,12 +31302,12 @@
       </c>
       <c r="E519" s="9" t="inlineStr">
         <is>
-          <t>SOE 315 Water &amp; Earth</t>
+          <t>GEOGENV2420A/B Economic Geography</t>
         </is>
       </c>
       <c r="F519" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G519" s="9" t="inlineStr">
@@ -31328,24 +31328,24 @@
       <c r="J519" s="9" t="n"/>
       <c r="K519" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="520" ht="30" customHeight="1" s="16">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C520" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D520" s="9" t="inlineStr">
@@ -31355,12 +31355,12 @@
       </c>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>SOIL SCI 368 Introduction to GIS</t>
+          <t>GEOGENV2430A/B Public Health And Environment (0.5 course)</t>
         </is>
       </c>
       <c r="F520" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G520" s="9" t="inlineStr">
@@ -31381,14 +31381,14 @@
       <c r="J520" s="9" t="n"/>
       <c r="K520" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
     <row r="521" ht="30" customHeight="1" s="16">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -31398,7 +31398,7 @@
       </c>
       <c r="C521" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D521" s="9" t="inlineStr">
@@ -31408,12 +31408,12 @@
       </c>
       <c r="E521" s="9" t="inlineStr">
         <is>
-          <t>SOE 101 Welcome to the Earth: An Introduction to Geology (4 credits)</t>
+          <t>GEOGENV2133A/B Connecting For Climate Change Action (C4Cca) (0.5 course)</t>
         </is>
       </c>
       <c r="F521" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G521" s="9" t="inlineStr">
@@ -31434,14 +31434,14 @@
       <c r="J521" s="9" t="n"/>
       <c r="K521" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="522" ht="30" customHeight="1" s="16">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="C522" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D522" s="9" t="inlineStr">
@@ -31461,12 +31461,12 @@
       </c>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>SOE 464 Landscape Ecology (3 credits)</t>
+          <t>GEOGENV2220A/B Geographic Information Science I</t>
         </is>
       </c>
       <c r="F522" s="9" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G522" s="9" t="inlineStr">
@@ -31487,14 +31487,14 @@
       <c r="J522" s="9" t="n"/>
       <c r="K522" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="523" ht="30" customHeight="1" s="16">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>Washington State University — USA</t>
+          <t>Western University — Canada</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -31514,12 +31514,12 @@
       </c>
       <c r="E523" s="9" t="inlineStr">
         <is>
-          <t>SOE 475 Groundwater (3 credits)</t>
+          <t>GEOGENV2310A/B Weather and Climate</t>
         </is>
       </c>
       <c r="F523" s="9" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G523" s="9" t="inlineStr">
@@ -31552,12 +31552,12 @@
       </c>
       <c r="B524" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C524" s="9" t="inlineStr">
         <is>
-          <t>SOES220 CITIES AND REGIONS</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D524" s="9" t="inlineStr">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2010A/B Geography Of Canada (0.5 course)</t>
+          <t>GEOGENV2320A/B Introductory Biogeography</t>
         </is>
       </c>
       <c r="F524" s="9" t="inlineStr">
@@ -31593,11 +31593,11 @@
       <c r="J524" s="9" t="n"/>
       <c r="K524" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="525" ht="30" customHeight="1" s="16">
+          <t>ENVS214 Changing Environments (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" s="16">
       <c r="A525" s="9" t="inlineStr">
         <is>
           <t>Western University — Canada</t>
@@ -31605,12 +31605,12 @@
       </c>
       <c r="B525" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C525" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D525" s="9" t="inlineStr">
@@ -31620,12 +31620,12 @@
       </c>
       <c r="E525" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2144A/B Geography Of Tourism (0.5 course)</t>
+          <t>GEOGENV3311A/B Micrometeorology (0.5 course)</t>
         </is>
       </c>
       <c r="F525" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G525" s="9" t="inlineStr">
@@ -31646,7 +31646,7 @@
       <c r="J525" s="9" t="n"/>
       <c r="K525" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
@@ -31658,12 +31658,12 @@
       </c>
       <c r="B526" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C526" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D526" s="9" t="inlineStr">
@@ -31673,12 +31673,12 @@
       </c>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2420A/B Economic Geography</t>
+          <t>GEOGENV4210A/B Geocomputation</t>
         </is>
       </c>
       <c r="F526" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Upper-level undergraduate</t>
         </is>
       </c>
       <c r="G526" s="9" t="inlineStr">
@@ -31699,7 +31699,7 @@
       <c r="J526" s="9" t="n"/>
       <c r="K526" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="C527" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D527" s="9" t="inlineStr">
@@ -31726,12 +31726,12 @@
       </c>
       <c r="E527" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2430A/B Public Health And Environment (0.5 course)</t>
+          <t>GEOGENV1500F Environment and Development Challenges (0.5)</t>
         </is>
       </c>
       <c r="F527" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G527" s="9" t="inlineStr">
@@ -31752,24 +31752,24 @@
       <c r="J527" s="9" t="n"/>
       <c r="K527" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
     <row r="528" ht="30" customHeight="1" s="16">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C528" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
         </is>
       </c>
       <c r="D528" s="9" t="inlineStr">
@@ -31779,7 +31779,7 @@
       </c>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2133A/B Connecting For Climate Change Action (C4Cca) (0.5 course)</t>
+          <t>UEPP 261 Planning the American City (3 credits)</t>
         </is>
       </c>
       <c r="F528" s="9" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="H528" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I528" s="12" t="inlineStr">
@@ -31805,24 +31805,24 @@
       <c r="J528" s="9" t="n"/>
       <c r="K528" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
         </is>
       </c>
     </row>
     <row r="529" ht="30" customHeight="1" s="16">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C529" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D529" s="9" t="inlineStr">
@@ -31832,7 +31832,7 @@
       </c>
       <c r="E529" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2220A/B Geographic Information Science I</t>
+          <t>UEPP 270 Cities, Nature and Society (3 credits)</t>
         </is>
       </c>
       <c r="F529" s="9" t="inlineStr">
@@ -31847,7 +31847,7 @@
       </c>
       <c r="H529" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I529" s="12" t="inlineStr">
@@ -31858,14 +31858,14 @@
       <c r="J529" s="9" t="n"/>
       <c r="K529" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
     <row r="530" ht="30" customHeight="1" s="16">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="C530" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D530" s="9" t="inlineStr">
@@ -31885,12 +31885,12 @@
       </c>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2310A/B Weather and Climate</t>
+          <t>ENVS320 GIS I: Introduction to Geographic Information Science</t>
         </is>
       </c>
       <c r="F530" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G530" s="9" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="H530" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I530" s="12" t="inlineStr">
@@ -31911,14 +31911,14 @@
       <c r="J530" s="9" t="n"/>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="531" ht="30" customHeight="1" s="16">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -31928,7 +31928,7 @@
       </c>
       <c r="C531" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D531" s="9" t="inlineStr">
@@ -31938,12 +31938,12 @@
       </c>
       <c r="E531" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV2320A/B Introductory Biogeography</t>
+          <t>ENVS326 Climatology (4 credits)</t>
         </is>
       </c>
       <c r="F531" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G531" s="9" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="H531" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I531" s="12" t="inlineStr">
@@ -31964,14 +31964,14 @@
       <c r="J531" s="9" t="n"/>
       <c r="K531" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="532" s="16">
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="30" customHeight="1" s="16">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -31981,7 +31981,7 @@
       </c>
       <c r="C532" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D532" s="9" t="inlineStr">
@@ -31991,7 +31991,7 @@
       </c>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV3311A/B Micrometeorology (0.5 course)</t>
+          <t>ENVS362 U.S. Disaster Policy (4 credits)</t>
         </is>
       </c>
       <c r="F532" s="9" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="H532" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I532" s="12" t="inlineStr">
@@ -32017,14 +32017,14 @@
       <c r="J532" s="9" t="n"/>
       <c r="K532" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
     <row r="533" ht="30" customHeight="1" s="16">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -32034,7 +32034,7 @@
       </c>
       <c r="C533" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D533" s="9" t="inlineStr">
@@ -32044,7 +32044,7 @@
       </c>
       <c r="E533" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV4210A/B Geocomputation</t>
+          <t>ENVS418 GIS II: Cartography and Geovisualization</t>
         </is>
       </c>
       <c r="F533" s="9" t="inlineStr">
@@ -32059,7 +32059,7 @@
       </c>
       <c r="H533" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I533" s="12" t="inlineStr">
@@ -32070,24 +32070,24 @@
       <c r="J533" s="9" t="n"/>
       <c r="K533" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
     <row r="534" ht="30" customHeight="1" s="16">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>Western University — Canada</t>
+          <t>Western Washington University — USA</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C534" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D534" s="9" t="inlineStr">
@@ -32097,12 +32097,12 @@
       </c>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>GEOGENV1500F Environment and Development Challenges (0.5)</t>
+          <t>ENVS420 GIS III: Analysis and Modeling</t>
         </is>
       </c>
       <c r="F534" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Upper-level undergraduate</t>
         </is>
       </c>
       <c r="G534" s="9" t="inlineStr">
@@ -32112,7 +32112,7 @@
       </c>
       <c r="H534" s="9" t="inlineStr">
         <is>
-          <t>Fall 2026</t>
+          <t>Fall quarter 2026</t>
         </is>
       </c>
       <c r="I534" s="12" t="inlineStr">
@@ -32123,7 +32123,7 @@
       <c r="J534" s="9" t="n"/>
       <c r="K534" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
         </is>
       </c>
     </row>
@@ -32140,7 +32140,7 @@
       </c>
       <c r="C535" s="9" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D535" s="9" t="inlineStr">
@@ -32150,7 +32150,7 @@
       </c>
       <c r="E535" s="9" t="inlineStr">
         <is>
-          <t>UEPP 261 Planning the American City (3 credits)</t>
+          <t>ENVS 204 Human Geography (4 credits)</t>
         </is>
       </c>
       <c r="F535" s="9" t="inlineStr">
@@ -32176,7 +32176,7 @@
       <c r="J535" s="9" t="n"/>
       <c r="K535" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -32193,7 +32193,7 @@
       </c>
       <c r="C536" s="9" t="inlineStr">
         <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D536" s="9" t="inlineStr">
@@ -32203,12 +32203,12 @@
       </c>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>UEPP 270 Cities, Nature and Society (3 credits)</t>
+          <t>ENVS 333 East Asia: Society and Environment (4 credits)</t>
         </is>
       </c>
       <c r="F536" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G536" s="9" t="inlineStr">
@@ -32229,7 +32229,7 @@
       <c r="J536" s="9" t="n"/>
       <c r="K536" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS275 Social and Cultural Geographies (same module)</t>
         </is>
       </c>
     </row>
@@ -32241,12 +32241,12 @@
       </c>
       <c r="B537" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C537" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D537" s="9" t="inlineStr">
@@ -32256,7 +32256,7 @@
       </c>
       <c r="E537" s="9" t="inlineStr">
         <is>
-          <t>ENVS320 GIS I: Introduction to Geographic Information Science</t>
+          <t>ENVS 342 Geography of the World Economy (4 credits)</t>
         </is>
       </c>
       <c r="F537" s="9" t="inlineStr">
@@ -32282,7 +32282,7 @@
       <c r="J537" s="9" t="n"/>
       <c r="K537" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS264 Political Economies of Globalisation (closest)</t>
         </is>
       </c>
     </row>
@@ -32294,12 +32294,12 @@
       </c>
       <c r="B538" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C538" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D538" s="9" t="inlineStr">
@@ -32309,12 +32309,12 @@
       </c>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>ENVS326 Climatology (4 credits)</t>
+          <t>ENVS 467 Power, (in)Justice and the Environment (4 credits)</t>
         </is>
       </c>
       <c r="F538" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G538" s="9" t="inlineStr">
@@ -32335,7 +32335,7 @@
       <c r="J538" s="9" t="n"/>
       <c r="K538" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>No direct 2026/27 equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -32362,12 +32362,12 @@
       </c>
       <c r="E539" s="9" t="inlineStr">
         <is>
-          <t>ENVS362 U.S. Disaster Policy (4 credits)</t>
+          <t>ENVS 203 Physical Geography (4 credits)</t>
         </is>
       </c>
       <c r="F539" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G539" s="9" t="inlineStr">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="C540" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D540" s="9" t="inlineStr">
@@ -32415,12 +32415,12 @@
       </c>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>ENVS418 GIS II: Cartography and Geovisualization</t>
+          <t>ENVS 429 Pyrogeography (4 credits)</t>
         </is>
       </c>
       <c r="F540" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G540" s="9" t="inlineStr">
@@ -32441,7 +32441,7 @@
       <c r="J540" s="9" t="n"/>
       <c r="K540" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
@@ -32458,7 +32458,7 @@
       </c>
       <c r="C541" s="9" t="inlineStr">
         <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+          <t>SOES280 HYDROCLIMATE</t>
         </is>
       </c>
       <c r="D541" s="9" t="inlineStr">
@@ -32468,12 +32468,12 @@
       </c>
       <c r="E541" s="9" t="inlineStr">
         <is>
-          <t>ENVS420 GIS III: Analysis and Modeling</t>
+          <t>ESCI 392 Introduction to Climate Change (4 credits)</t>
         </is>
       </c>
       <c r="F541" s="9" t="inlineStr">
         <is>
-          <t>Upper-level undergraduate</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G541" s="9" t="inlineStr">
@@ -32494,14 +32494,14 @@
       <c r="J541" s="9" t="n"/>
       <c r="K541" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
         </is>
       </c>
     </row>
     <row r="542" ht="30" customHeight="1" s="16">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -32511,7 +32511,7 @@
       </c>
       <c r="C542" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
         </is>
       </c>
       <c r="D542" s="9" t="inlineStr">
@@ -32521,12 +32521,12 @@
       </c>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>ENVS 204 Human Geography (4 credits)</t>
+          <t>UPD102 Contemporary Planning Practice in Western Europe and North America (5)</t>
         </is>
       </c>
       <c r="F542" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G542" s="9" t="inlineStr">
@@ -32536,7 +32536,7 @@
       </c>
       <c r="H542" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I542" s="12" t="inlineStr">
@@ -32547,14 +32547,14 @@
       <c r="J542" s="9" t="n"/>
       <c r="K542" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
         </is>
       </c>
     </row>
     <row r="543" ht="30" customHeight="1" s="16">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="C543" s="9" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
         </is>
       </c>
       <c r="D543" s="9" t="inlineStr">
@@ -32574,12 +32574,12 @@
       </c>
       <c r="E543" s="9" t="inlineStr">
         <is>
-          <t>ENVS 333 East Asia: Society and Environment (4 credits)</t>
+          <t>UPD103 Issues and Practice of Planning in China (5)</t>
         </is>
       </c>
       <c r="F543" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G543" s="9" t="inlineStr">
@@ -32589,7 +32589,7 @@
       </c>
       <c r="H543" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I543" s="12" t="inlineStr">
@@ -32600,14 +32600,14 @@
       <c r="J543" s="9" t="n"/>
       <c r="K543" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
         </is>
       </c>
     </row>
     <row r="544" ht="30" customHeight="1" s="16">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -32617,7 +32617,7 @@
       </c>
       <c r="C544" s="9" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D544" s="9" t="inlineStr">
@@ -32627,12 +32627,12 @@
       </c>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>ENVS 342 Geography of the World Economy (4 credits)</t>
+          <t>UPD203 Networks and Cities (5)</t>
         </is>
       </c>
       <c r="F544" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G544" s="9" t="inlineStr">
@@ -32642,7 +32642,7 @@
       </c>
       <c r="H544" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I544" s="12" t="inlineStr">
@@ -32653,14 +32653,14 @@
       <c r="J544" s="9" t="n"/>
       <c r="K544" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="545" ht="30" customHeight="1" s="16">
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="60" customHeight="1" s="16">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -32670,7 +32670,7 @@
       </c>
       <c r="C545" s="9" t="inlineStr">
         <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
         </is>
       </c>
       <c r="D545" s="9" t="inlineStr">
@@ -32680,12 +32680,12 @@
       </c>
       <c r="E545" s="9" t="inlineStr">
         <is>
-          <t>ENVS 467 Power, (in)Justice and the Environment (4 credits)</t>
+          <t>UPD310 International Planning Studies (5)</t>
         </is>
       </c>
       <c r="F545" s="9" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G545" s="9" t="inlineStr">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="H545" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I545" s="12" t="inlineStr">
@@ -32706,24 +32706,24 @@
       <c r="J545" s="9" t="n"/>
       <c r="K545" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="546" ht="30" customHeight="1" s="16">
+          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="60" customHeight="1" s="16">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C546" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D546" s="9" t="inlineStr">
@@ -32733,12 +32733,12 @@
       </c>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>ENVS 203 Physical Geography (4 credits)</t>
+          <t>UPD314 Critical Debates in Contemporary Cities (5)</t>
         </is>
       </c>
       <c r="F546" s="9" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G546" s="9" t="inlineStr">
@@ -32748,7 +32748,7 @@
       </c>
       <c r="H546" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I546" s="12" t="inlineStr">
@@ -32759,14 +32759,14 @@
       <c r="J546" s="9" t="n"/>
       <c r="K546" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="547" ht="30" customHeight="1" s="16">
+          <t>ENVS205 People and Place (closest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="60" customHeight="1" s="16">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="C547" s="9" t="inlineStr">
         <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D547" s="9" t="inlineStr">
@@ -32786,12 +32786,12 @@
       </c>
       <c r="E547" s="9" t="inlineStr">
         <is>
-          <t>ENVS 429 Pyrogeography (4 credits)</t>
+          <t>UPD204 Geographic Information Systems (5)</t>
         </is>
       </c>
       <c r="F547" s="9" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G547" s="9" t="inlineStr">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="H547" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I547" s="12" t="inlineStr">
@@ -32812,14 +32812,14 @@
       <c r="J547" s="9" t="n"/>
       <c r="K547" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="548" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="60" customHeight="1" s="16">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>Western Washington University — USA</t>
+          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -32829,7 +32829,7 @@
       </c>
       <c r="C548" s="9" t="inlineStr">
         <is>
-          <t>SOES280 HYDROCLIMATE</t>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
       <c r="D548" s="9" t="inlineStr">
@@ -32839,12 +32839,12 @@
       </c>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>ESCI 392 Introduction to Climate Change (4 credits)</t>
+          <t>UPD408 Spatial Analysis and Visualisation (5)</t>
         </is>
       </c>
       <c r="F548" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Upper-level undergraduate</t>
         </is>
       </c>
       <c r="G548" s="9" t="inlineStr">
@@ -32854,7 +32854,7 @@
       </c>
       <c r="H548" s="9" t="inlineStr">
         <is>
-          <t>Fall quarter 2026</t>
+          <t>Semester 1 2026-27</t>
         </is>
       </c>
       <c r="I548" s="12" t="inlineStr">
@@ -32865,11 +32865,11 @@
       <c r="J548" s="9" t="n"/>
       <c r="K548" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="549" ht="30" customHeight="1" s="16">
+          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="60" customHeight="1" s="16">
       <c r="A549" s="9" t="inlineStr">
         <is>
           <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="B549" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C549" s="9" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
       <c r="D549" s="9" t="inlineStr">
@@ -32892,12 +32892,12 @@
       </c>
       <c r="E549" s="9" t="inlineStr">
         <is>
-          <t>UPD102 Contemporary Planning Practice in Western Europe and North America (5)</t>
+          <t>UPD402 Sustainable Urban Planning Strategies (5)</t>
         </is>
       </c>
       <c r="F549" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Upper-level undergraduate</t>
         </is>
       </c>
       <c r="G549" s="9" t="inlineStr">
@@ -32907,18 +32907,18 @@
       </c>
       <c r="H549" s="9" t="inlineStr">
         <is>
-          <t>Semester 1 2026-27</t>
+          <t>Semester 1 or 2 2026-27</t>
         </is>
       </c>
       <c r="I549" s="12" t="inlineStr">
         <is>
-          <t>Semester 1</t>
+          <t>Semester 1 or 2</t>
         </is>
       </c>
       <c r="J549" s="9" t="n"/>
       <c r="K549" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS205 People and Place (closest)</t>
         </is>
       </c>
     </row>
@@ -32935,7 +32935,7 @@
       </c>
       <c r="C550" s="9" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
       <c r="D550" s="9" t="inlineStr">
@@ -32945,37 +32945,37 @@
       </c>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>UPD103 Issues and Practice of Planning in China (5)</t>
+          <t>UPD209 Planning and Research Methodology (5)</t>
         </is>
       </c>
       <c r="F550" s="9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G550" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="H550" s="9" t="inlineStr">
         <is>
-          <t>Semester 1 2026-27</t>
+          <t>Semester 2 2026-27</t>
         </is>
       </c>
       <c r="I550" s="12" t="inlineStr">
         <is>
-          <t>Semester 1</t>
+          <t>Semester 2</t>
         </is>
       </c>
       <c r="J550" s="9" t="n"/>
       <c r="K550" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="551" ht="30" customHeight="1" s="16">
+          <t>ENVS225 Exploring the Social World (same module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="60" customHeight="1" s="16">
       <c r="A551" s="9" t="inlineStr">
         <is>
           <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
@@ -32983,7 +32983,7 @@
       </c>
       <c r="B551" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C551" s="9" t="inlineStr">
@@ -32998,7 +32998,7 @@
       </c>
       <c r="E551" s="9" t="inlineStr">
         <is>
-          <t>UPD203 Networks and Cities (5)</t>
+          <t>UPD202 Rural Planning (5)</t>
         </is>
       </c>
       <c r="F551" s="9" t="inlineStr">
@@ -33013,12 +33013,12 @@
       </c>
       <c r="H551" s="9" t="inlineStr">
         <is>
-          <t>Semester 1 2026-27</t>
+          <t>Semester 2 2026-27</t>
         </is>
       </c>
       <c r="I551" s="12" t="inlineStr">
         <is>
-          <t>Semester 1</t>
+          <t>Semester 2</t>
         </is>
       </c>
       <c r="J551" s="9" t="n"/>
@@ -33036,12 +33036,12 @@
       </c>
       <c r="B552" s="9" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C552" s="9" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
       <c r="D552" s="9" t="inlineStr">
@@ -33051,7 +33051,7 @@
       </c>
       <c r="E552" s="9" t="inlineStr">
         <is>
-          <t>UPD310 International Planning Studies (5)</t>
+          <t>UPD312 Spatial Project (5)</t>
         </is>
       </c>
       <c r="F552" s="9" t="inlineStr">
@@ -33066,394 +33066,31 @@
       </c>
       <c r="H552" s="9" t="inlineStr">
         <is>
-          <t>Semester 1 2026-27</t>
+          <t>Semester 2 2026-27</t>
         </is>
       </c>
       <c r="I552" s="12" t="inlineStr">
         <is>
-          <t>Semester 1</t>
+          <t>Semester 2</t>
         </is>
       </c>
       <c r="J552" s="9" t="n"/>
       <c r="K552" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="553" ht="60" customHeight="1" s="16">
-      <c r="A553" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B553" s="9" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C553" s="9" t="inlineStr">
-        <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
-        </is>
-      </c>
-      <c r="D553" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E553" s="9" t="inlineStr">
-        <is>
-          <t>UPD314 Critical Debates in Contemporary Cities (5)</t>
-        </is>
-      </c>
-      <c r="F553" s="9" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G553" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H553" s="9" t="inlineStr">
-        <is>
-          <t>Semester 1 2026-27</t>
-        </is>
-      </c>
-      <c r="I553" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J553" s="9" t="n"/>
-      <c r="K553" s="9" t="inlineStr">
-        <is>
-          <t>ENVS205 People and Place (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="554" ht="60" customHeight="1" s="16">
-      <c r="A554" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B554" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C554" s="9" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D554" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E554" s="9" t="inlineStr">
-        <is>
-          <t>UPD204 Geographic Information Systems (5)</t>
-        </is>
-      </c>
-      <c r="F554" s="9" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G554" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H554" s="9" t="inlineStr">
-        <is>
-          <t>Semester 1 2026-27</t>
-        </is>
-      </c>
-      <c r="I554" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J554" s="9" t="n"/>
-      <c r="K554" s="9" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="555" ht="60" customHeight="1" s="16">
-      <c r="A555" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B555" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C555" s="9" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D555" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E555" s="9" t="inlineStr">
-        <is>
-          <t>UPD408 Spatial Analysis and Visualisation (5)</t>
-        </is>
-      </c>
-      <c r="F555" s="9" t="inlineStr">
-        <is>
-          <t>Upper-level undergraduate</t>
-        </is>
-      </c>
-      <c r="G555" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H555" s="9" t="inlineStr">
-        <is>
-          <t>Semester 1 2026-27</t>
-        </is>
-      </c>
-      <c r="I555" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1</t>
-        </is>
-      </c>
-      <c r="J555" s="9" t="n"/>
-      <c r="K555" s="9" t="inlineStr">
-        <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
-        </is>
-      </c>
-    </row>
-    <row r="556" ht="60" customHeight="1" s="16">
-      <c r="A556" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B556" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C556" s="9" t="inlineStr">
-        <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
-        </is>
-      </c>
-      <c r="D556" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E556" s="9" t="inlineStr">
-        <is>
-          <t>UPD402 Sustainable Urban Planning Strategies (5)</t>
-        </is>
-      </c>
-      <c r="F556" s="9" t="inlineStr">
-        <is>
-          <t>Upper-level undergraduate</t>
-        </is>
-      </c>
-      <c r="G556" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H556" s="9" t="inlineStr">
-        <is>
-          <t>Semester 1 or 2 2026-27</t>
-        </is>
-      </c>
-      <c r="I556" s="12" t="inlineStr">
-        <is>
-          <t>Semester 1 or 2</t>
-        </is>
-      </c>
-      <c r="J556" s="9" t="n"/>
-      <c r="K556" s="9" t="inlineStr">
-        <is>
-          <t>ENVS205 People and Place (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="557" ht="30" customHeight="1" s="16">
-      <c r="A557" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B557" s="9" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C557" s="9" t="inlineStr">
-        <is>
-          <t>SOES226 EXPLORING THE SOCIAL WORLD</t>
-        </is>
-      </c>
-      <c r="D557" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E557" s="9" t="inlineStr">
-        <is>
-          <t>UPD209 Planning and Research Methodology (5)</t>
-        </is>
-      </c>
-      <c r="F557" s="9" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G557" s="9" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H557" s="9" t="inlineStr">
-        <is>
-          <t>Semester 2 2026-27</t>
-        </is>
-      </c>
-      <c r="I557" s="12" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J557" s="9" t="n"/>
-      <c r="K557" s="9" t="inlineStr">
-        <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
-        </is>
-      </c>
-    </row>
-    <row r="558" ht="60" customHeight="1" s="16">
-      <c r="A558" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B558" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C558" s="9" t="inlineStr">
-        <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
-        </is>
-      </c>
-      <c r="D558" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E558" s="9" t="inlineStr">
-        <is>
-          <t>UPD202 Rural Planning (5)</t>
-        </is>
-      </c>
-      <c r="F558" s="9" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G558" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H558" s="9" t="inlineStr">
-        <is>
-          <t>Semester 2 2026-27</t>
-        </is>
-      </c>
-      <c r="I558" s="12" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J558" s="9" t="n"/>
-      <c r="K558" s="9" t="inlineStr">
-        <is>
-          <t>ENVS205 People and Place (closest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="559" ht="60" customHeight="1" s="16">
-      <c r="A559" s="9" t="inlineStr">
-        <is>
-          <t>Xi’an Jiaotong-Liverpool University (XJTLU) — China</t>
-        </is>
-      </c>
-      <c r="B559" s="9" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C559" s="9" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D559" s="9" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E559" s="9" t="inlineStr">
-        <is>
-          <t>UPD312 Spatial Project (5)</t>
-        </is>
-      </c>
-      <c r="F559" s="9" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G559" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H559" s="9" t="inlineStr">
-        <is>
-          <t>Semester 2 2026-27</t>
-        </is>
-      </c>
-      <c r="I559" s="12" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="J559" s="9" t="n"/>
-      <c r="K559" s="9" t="inlineStr">
-        <is>
           <t>ENVS214 Changing Environments (same module)</t>
         </is>
       </c>
     </row>
+    <row r="553" s="16"/>
+    <row r="554" s="16"/>
+    <row r="555" s="16"/>
+    <row r="556" s="16"/>
+    <row r="557" s="16"/>
+    <row r="558" s="16"/>
+    <row r="559" s="16"/>
+    <row r="560" s="16"/>
   </sheetData>
-  <autoFilter ref="A1:K559">
+  <autoFilter ref="A1:K552">
     <sortState ref="A2:J528">
       <sortCondition ref="A1:A528"/>
     </sortState>

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -4828,7 +4828,7 @@
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       <c r="J148" s="9" t="n"/>
       <c r="K148" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16011,7 @@
       <c r="J230" s="9" t="n"/>
       <c r="K230" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
       <c r="J243" s="9" t="n"/>
       <c r="K243" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -17601,7 +17601,7 @@
       <c r="J260" s="9" t="n"/>
       <c r="K260" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -18343,7 +18343,7 @@
       <c r="J274" s="9" t="n"/>
       <c r="K274" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
       <c r="J297" s="9" t="n"/>
       <c r="K297" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -19668,7 +19668,7 @@
       <c r="J299" s="9" t="n"/>
       <c r="K299" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -22795,7 +22795,7 @@
       <c r="J358" s="9" t="n"/>
       <c r="K358" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -26876,7 +26876,7 @@
       <c r="J435" s="9" t="n"/>
       <c r="K435" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
       <c r="J445" s="9" t="n"/>
       <c r="K445" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       <c r="J457" s="9" t="n"/>
       <c r="K457" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
         </is>
       </c>
     </row>

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>UoL module 2026/27 (current code)</t>
+          <t>Old UoL code and title (ENVS)</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       <c r="J2" s="10" t="n"/>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       <c r="J4" s="10" t="n"/>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       <c r="J6" s="10" t="n"/>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,11 @@
         </is>
       </c>
       <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="16">
       <c r="A8" s="9" t="inlineStr">
@@ -4237,7 +4241,7 @@
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4294,7 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4347,7 @@
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4400,7 @@
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4453,7 @@
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4506,7 @@
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4557,11 @@
         </is>
       </c>
       <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="15" s="16">
       <c r="A15" s="9" t="inlineStr">
@@ -4604,7 +4612,7 @@
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4665,7 @@
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4718,7 @@
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4771,7 @@
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4824,7 @@
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4877,7 @@
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4930,7 @@
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4983,7 @@
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5036,7 @@
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5089,7 @@
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5142,7 @@
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5195,7 @@
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5248,7 @@
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5299,11 @@
         </is>
       </c>
       <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="16">
       <c r="A29" s="9" t="inlineStr">
@@ -5342,7 +5354,7 @@
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5405,11 @@
         </is>
       </c>
       <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="16">
       <c r="A31" s="9" t="inlineStr">
@@ -5444,7 +5460,7 @@
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5513,7 @@
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5566,7 @@
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5619,7 @@
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5672,7 @@
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5725,7 @@
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5778,7 @@
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5831,7 @@
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5884,7 @@
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5937,7 @@
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5990,7 @@
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6043,7 @@
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6094,11 @@
         </is>
       </c>
       <c r="J43" s="11" t="n"/>
-      <c r="K43" s="11" t="n"/>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1" s="16">
       <c r="A44" s="9" t="inlineStr">
@@ -6129,7 +6149,7 @@
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6202,7 @@
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6255,7 @@
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6306,11 @@
         </is>
       </c>
       <c r="J47" s="11" t="n"/>
-      <c r="K47" s="11" t="n"/>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1" s="16">
       <c r="A48" s="11" t="inlineStr">
@@ -6337,7 +6361,7 @@
       <c r="J48" s="11" t="n"/>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6414,7 @@
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6467,7 @@
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6520,7 @@
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6573,7 @@
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6626,7 @@
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6679,7 @@
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6732,7 @@
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6785,7 @@
       <c r="J56" s="9" t="n"/>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6838,7 @@
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6889,11 @@
         </is>
       </c>
       <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="45" customHeight="1" s="16">
       <c r="A59" s="9" t="inlineStr">
@@ -6916,7 +6944,7 @@
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>ENVS282/286/288 Field Class (Belfast/Edinburgh/Glasgow) (closest)</t>
+          <t>ENVS282/286/288 FIELD CLASS (BELFAST/EDINBURGH/GLASGOW)</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6997,7 @@
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7050,7 @@
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7103,7 @@
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7156,7 @@
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7209,7 @@
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7262,7 @@
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7315,7 @@
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7366,11 @@
         </is>
       </c>
       <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="45" customHeight="1" s="16">
       <c r="A68" s="9" t="inlineStr">
@@ -7389,7 +7421,7 @@
       <c r="J68" s="9" t="n"/>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7474,7 @@
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7525,11 @@
         </is>
       </c>
       <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="45" customHeight="1" s="16">
       <c r="A71" s="9" t="inlineStr">
@@ -7544,7 +7580,7 @@
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7633,7 @@
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7686,7 @@
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7739,7 @@
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7792,7 @@
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7845,7 @@
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7898,7 @@
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7949,11 @@
         </is>
       </c>
       <c r="J78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1" s="16">
       <c r="A79" s="9" t="inlineStr">
@@ -7964,7 +8004,7 @@
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8057,7 @@
       <c r="J80" s="9" t="n"/>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8110,7 @@
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8163,7 @@
       <c r="J82" s="9" t="n"/>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8216,7 @@
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8267,11 @@
         </is>
       </c>
       <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1" s="16">
       <c r="A85" s="9" t="inlineStr">
@@ -8278,7 +8322,7 @@
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8375,7 @@
       <c r="J86" s="9" t="n"/>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8428,7 @@
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8481,7 @@
       <c r="J88" s="9" t="n"/>
       <c r="K88" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8534,7 @@
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8587,7 @@
       <c r="J90" s="9" t="n"/>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8640,7 @@
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8693,7 @@
       <c r="J92" s="9" t="n"/>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8746,7 @@
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8799,7 @@
       <c r="J94" s="9" t="n"/>
       <c r="K94" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8850,11 @@
         </is>
       </c>
       <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="45" customHeight="1" s="16">
       <c r="A96" s="10" t="inlineStr">
@@ -8857,7 +8905,7 @@
       <c r="J96" s="10" t="n"/>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8958,7 @@
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -8963,7 +9011,7 @@
       <c r="J98" s="11" t="n"/>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9064,7 @@
       <c r="J99" s="11" t="n"/>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9117,7 @@
       <c r="J100" s="10" t="n"/>
       <c r="K100" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9170,7 @@
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9223,7 @@
       <c r="J102" s="10" t="n"/>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9276,7 @@
       <c r="J103" s="10" t="n"/>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9329,7 @@
       <c r="J104" s="10" t="n"/>
       <c r="K104" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9382,7 @@
       <c r="J105" s="10" t="n"/>
       <c r="K105" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9435,7 @@
       <c r="J106" s="10" t="n"/>
       <c r="K106" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9486,11 @@
         </is>
       </c>
       <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
+      <c r="K107" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="60" customHeight="1" s="16">
       <c r="A108" s="11" t="inlineStr">
@@ -9489,7 +9541,7 @@
       <c r="J108" s="11" t="n"/>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9594,7 @@
       <c r="J109" s="10" t="n"/>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9645,11 @@
         </is>
       </c>
       <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
+      <c r="K110" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="60" customHeight="1" s="16">
       <c r="A111" s="9" t="inlineStr">
@@ -9644,7 +9700,7 @@
       <c r="J111" s="9" t="n"/>
       <c r="K111" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9753,7 @@
       <c r="J112" s="9" t="n"/>
       <c r="K112" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9806,7 @@
       <c r="J113" s="9" t="n"/>
       <c r="K113" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -9803,7 +9859,7 @@
       <c r="J114" s="9" t="n"/>
       <c r="K114" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9912,7 @@
       <c r="J115" s="9" t="n"/>
       <c r="K115" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9965,7 @@
       <c r="J116" s="9" t="n"/>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -9962,7 +10018,7 @@
       <c r="J117" s="9" t="n"/>
       <c r="K117" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10071,7 @@
       <c r="J118" s="9" t="n"/>
       <c r="K118" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10124,7 @@
       <c r="J119" s="9" t="n"/>
       <c r="K119" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10177,7 @@
       <c r="J120" s="9" t="n"/>
       <c r="K120" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10230,7 @@
       <c r="J121" s="9" t="n"/>
       <c r="K121" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10283,7 @@
       <c r="J122" s="9" t="n"/>
       <c r="K122" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10334,11 @@
         </is>
       </c>
       <c r="J123" s="9" t="n"/>
-      <c r="K123" s="9" t="n"/>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1" s="16">
       <c r="A124" s="9" t="inlineStr">
@@ -10329,7 +10389,7 @@
       <c r="J124" s="9" t="n"/>
       <c r="K124" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10442,7 @@
       <c r="J125" s="9" t="n"/>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10493,11 @@
         </is>
       </c>
       <c r="J126" s="9" t="n"/>
-      <c r="K126" s="9" t="n"/>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="127" s="16">
       <c r="A127" s="9" t="inlineStr">
@@ -10484,7 +10548,7 @@
       <c r="J127" s="9" t="n"/>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10601,7 @@
       <c r="J128" s="9" t="n"/>
       <c r="K128" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10654,7 @@
       <c r="J129" s="9" t="n"/>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10707,7 @@
       <c r="J130" s="9" t="n"/>
       <c r="K130" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10760,7 @@
       <c r="J131" s="9" t="n"/>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10813,7 @@
       <c r="J132" s="9" t="n"/>
       <c r="K132" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10866,7 @@
       <c r="J133" s="9" t="n"/>
       <c r="K133" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10919,7 @@
       <c r="J134" s="9" t="n"/>
       <c r="K134" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10970,11 @@
         </is>
       </c>
       <c r="J135" s="11" t="n"/>
-      <c r="K135" s="11" t="n"/>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="30" customHeight="1" s="16">
       <c r="A136" s="9" t="inlineStr">
@@ -10957,7 +11025,7 @@
       <c r="J136" s="9" t="n"/>
       <c r="K136" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11078,7 @@
       <c r="J137" s="9" t="n"/>
       <c r="K137" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11131,7 @@
       <c r="J138" s="9" t="n"/>
       <c r="K138" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11184,7 @@
       <c r="J139" s="9" t="n"/>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11235,11 @@
         </is>
       </c>
       <c r="J140" s="11" t="n"/>
-      <c r="K140" s="11" t="n"/>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="141" s="16">
       <c r="A141" s="11" t="inlineStr">
@@ -11218,7 +11290,7 @@
       <c r="J141" s="11" t="n"/>
       <c r="K141" s="11" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11343,7 @@
       <c r="J142" s="9" t="n"/>
       <c r="K142" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11396,7 @@
       <c r="J143" s="9" t="n"/>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11449,7 @@
       <c r="J144" s="9" t="n"/>
       <c r="K144" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11502,7 @@
       <c r="J145" s="9" t="n"/>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11555,7 @@
       <c r="J146" s="9" t="n"/>
       <c r="K146" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -11536,7 +11608,7 @@
       <c r="J147" s="9" t="n"/>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11661,7 @@
       <c r="J148" s="9" t="n"/>
       <c r="K148" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11714,7 @@
       <c r="J149" s="9" t="n"/>
       <c r="K149" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11767,7 @@
       <c r="J150" s="9" t="n"/>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11820,7 @@
       <c r="J151" s="9" t="n"/>
       <c r="K151" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11873,7 @@
       <c r="J152" s="9" t="n"/>
       <c r="K152" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11926,7 @@
       <c r="J153" s="9" t="n"/>
       <c r="K153" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11979,7 @@
       <c r="J154" s="9" t="n"/>
       <c r="K154" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -11960,7 +12032,7 @@
       <c r="J155" s="9" t="n"/>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12085,7 @@
       <c r="J156" s="9" t="n"/>
       <c r="K156" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12138,7 @@
       <c r="J157" s="9" t="n"/>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12191,7 @@
       <c r="J158" s="9" t="n"/>
       <c r="K158" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12244,7 @@
       <c r="J159" s="9" t="n"/>
       <c r="K159" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12295,11 @@
         </is>
       </c>
       <c r="J160" s="9" t="n"/>
-      <c r="K160" s="9" t="n"/>
+      <c r="K160" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="30" customHeight="1" s="16">
       <c r="A161" s="9" t="inlineStr">
@@ -12274,7 +12350,7 @@
       <c r="J161" s="9" t="n"/>
       <c r="K161" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12403,7 @@
       <c r="J162" s="9" t="n"/>
       <c r="K162" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12456,7 @@
       <c r="J163" s="9" t="n"/>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12509,7 @@
       <c r="J164" s="9" t="n"/>
       <c r="K164" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12562,7 @@
       <c r="J165" s="9" t="n"/>
       <c r="K165" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -12537,7 +12613,11 @@
         </is>
       </c>
       <c r="J166" s="9" t="n"/>
-      <c r="K166" s="9" t="n"/>
+      <c r="K166" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="30" customHeight="1" s="16">
       <c r="A167" s="9" t="inlineStr">
@@ -12588,7 +12668,7 @@
       <c r="J167" s="9" t="n"/>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12721,7 @@
       <c r="J168" s="9" t="n"/>
       <c r="K168" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -12694,7 +12774,7 @@
       <c r="J169" s="9" t="n"/>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12827,7 @@
       <c r="J170" s="9" t="n"/>
       <c r="K170" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -12800,7 +12880,7 @@
       <c r="J171" s="9" t="n"/>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12933,7 @@
       <c r="J172" s="9" t="n"/>
       <c r="K172" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12986,7 @@
       <c r="J173" s="9" t="n"/>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -12959,7 +13039,7 @@
       <c r="J174" s="9" t="n"/>
       <c r="K174" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -13012,7 +13092,7 @@
       <c r="J175" s="9" t="n"/>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13145,7 @@
       <c r="J176" s="9" t="n"/>
       <c r="K176" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13198,7 @@
       <c r="J177" s="9" t="n"/>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13251,7 @@
       <c r="J178" s="9" t="n"/>
       <c r="K178" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13304,7 @@
       <c r="J179" s="9" t="n"/>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13357,7 @@
       <c r="J180" s="9" t="n"/>
       <c r="K180" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13410,7 @@
       <c r="J181" s="9" t="n"/>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13461,11 @@
         </is>
       </c>
       <c r="J182" s="9" t="n"/>
-      <c r="K182" s="9" t="n"/>
+      <c r="K182" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="30" customHeight="1" s="16">
       <c r="A183" s="9" t="inlineStr">
@@ -13432,7 +13516,7 @@
       <c r="J183" s="9" t="n"/>
       <c r="K183" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13569,7 @@
       <c r="J184" s="9" t="n"/>
       <c r="K184" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13620,11 @@
         </is>
       </c>
       <c r="J185" s="9" t="n"/>
-      <c r="K185" s="9" t="n"/>
+      <c r="K185" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="30" customHeight="1" s="16">
       <c r="A186" s="10" t="inlineStr">
@@ -13587,7 +13675,7 @@
       <c r="J186" s="10" t="n"/>
       <c r="K186" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13728,7 @@
       <c r="J187" s="9" t="n"/>
       <c r="K187" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -13693,7 +13781,7 @@
       <c r="J188" s="9" t="n"/>
       <c r="K188" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13834,7 @@
       <c r="J189" s="9" t="n"/>
       <c r="K189" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13887,7 @@
       <c r="J190" s="9" t="n"/>
       <c r="K190" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13940,7 @@
       <c r="J191" s="9" t="n"/>
       <c r="K191" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -13905,7 +13993,7 @@
       <c r="J192" s="9" t="n"/>
       <c r="K192" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -13958,7 +14046,7 @@
       <c r="J193" s="9" t="n"/>
       <c r="K193" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -14011,7 +14099,7 @@
       <c r="J194" s="9" t="n"/>
       <c r="K194" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14152,7 @@
       <c r="J195" s="9" t="n"/>
       <c r="K195" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -14117,7 +14205,7 @@
       <c r="J196" s="9" t="n"/>
       <c r="K196" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14258,7 @@
       <c r="J197" s="9" t="n"/>
       <c r="K197" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14311,7 @@
       <c r="J198" s="9" t="n"/>
       <c r="K198" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14364,7 @@
       <c r="J199" s="9" t="n"/>
       <c r="K199" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14417,7 @@
       <c r="J200" s="9" t="n"/>
       <c r="K200" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14470,7 @@
       <c r="J201" s="9" t="n"/>
       <c r="K201" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14521,11 @@
         </is>
       </c>
       <c r="J202" s="9" t="n"/>
-      <c r="K202" s="9" t="n"/>
+      <c r="K202" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="45" customHeight="1" s="16">
       <c r="A203" s="9" t="inlineStr">
@@ -14484,7 +14576,7 @@
       <c r="J203" s="9" t="n"/>
       <c r="K203" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14629,7 @@
       <c r="J204" s="9" t="n"/>
       <c r="K204" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -14590,7 +14682,7 @@
       <c r="J205" s="9" t="n"/>
       <c r="K205" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14735,7 @@
       <c r="J206" s="9" t="n"/>
       <c r="K206" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14788,7 @@
       <c r="J207" s="9" t="n"/>
       <c r="K207" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -14747,7 +14839,11 @@
         </is>
       </c>
       <c r="J208" s="9" t="n"/>
-      <c r="K208" s="9" t="n"/>
+      <c r="K208" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="45" customHeight="1" s="16">
       <c r="A209" s="9" t="inlineStr">
@@ -14798,7 +14894,7 @@
       <c r="J209" s="9" t="n"/>
       <c r="K209" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14947,7 @@
       <c r="J210" s="9" t="n"/>
       <c r="K210" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -14904,7 +15000,7 @@
       <c r="J211" s="9" t="n"/>
       <c r="K211" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -14957,7 +15053,7 @@
       <c r="J212" s="9" t="n"/>
       <c r="K212" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15106,7 @@
       <c r="J213" s="9" t="n"/>
       <c r="K213" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15159,7 @@
       <c r="J214" s="9" t="n"/>
       <c r="K214" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15212,7 @@
       <c r="J215" s="9" t="n"/>
       <c r="K215" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -15169,7 +15265,7 @@
       <c r="J216" s="9" t="n"/>
       <c r="K216" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15318,7 @@
       <c r="J217" s="9" t="n"/>
       <c r="K217" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15371,7 @@
       <c r="J218" s="9" t="n"/>
       <c r="K218" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -15328,7 +15424,7 @@
       <c r="J219" s="9" t="n"/>
       <c r="K219" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15475,11 @@
         </is>
       </c>
       <c r="J220" s="9" t="n"/>
-      <c r="K220" s="9" t="n"/>
+      <c r="K220" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="30" customHeight="1" s="16">
       <c r="A221" s="9" t="inlineStr">
@@ -15430,7 +15530,7 @@
       <c r="J221" s="9" t="n"/>
       <c r="K221" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15583,7 @@
       <c r="J222" s="9" t="n"/>
       <c r="K222" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15634,11 @@
         </is>
       </c>
       <c r="J223" s="9" t="n"/>
-      <c r="K223" s="9" t="n"/>
+      <c r="K223" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="224" s="16">
       <c r="A224" s="9" t="inlineStr">
@@ -15585,7 +15689,7 @@
       <c r="J224" s="9" t="n"/>
       <c r="K224" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15742,7 @@
       <c r="J225" s="9" t="n"/>
       <c r="K225" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15795,7 @@
       <c r="J226" s="9" t="n"/>
       <c r="K226" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15848,7 @@
       <c r="J227" s="9" t="n"/>
       <c r="K227" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15901,7 @@
       <c r="J228" s="9" t="n"/>
       <c r="K228" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15954,7 @@
       <c r="J229" s="9" t="n"/>
       <c r="K229" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -15903,7 +16007,7 @@
       <c r="J230" s="9" t="n"/>
       <c r="K230" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -15956,7 +16060,7 @@
       <c r="J231" s="9" t="n"/>
       <c r="K231" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16113,7 @@
       <c r="J232" s="9" t="n"/>
       <c r="K232" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16164,11 @@
         </is>
       </c>
       <c r="J233" s="9" t="n"/>
-      <c r="K233" s="9" t="n"/>
+      <c r="K233" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="30" customHeight="1" s="16">
       <c r="A234" s="9" t="inlineStr">
@@ -16111,7 +16219,7 @@
       <c r="J234" s="9" t="n"/>
       <c r="K234" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16272,7 @@
       <c r="J235" s="9" t="n"/>
       <c r="K235" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16325,7 @@
       <c r="J236" s="9" t="n"/>
       <c r="K236" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -16270,7 +16378,7 @@
       <c r="J237" s="9" t="n"/>
       <c r="K237" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -16321,7 +16429,11 @@
         </is>
       </c>
       <c r="J238" s="9" t="n"/>
-      <c r="K238" s="9" t="n"/>
+      <c r="K238" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="239" s="16">
       <c r="A239" s="9" t="inlineStr">
@@ -16372,7 +16484,7 @@
       <c r="J239" s="9" t="n"/>
       <c r="K239" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16537,7 @@
       <c r="J240" s="10" t="n"/>
       <c r="K240" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16590,7 @@
       <c r="J241" s="10" t="n"/>
       <c r="K241" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -16531,7 +16643,7 @@
       <c r="J242" s="10" t="n"/>
       <c r="K242" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16696,7 @@
       <c r="J243" s="10" t="n"/>
       <c r="K243" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16749,7 @@
       <c r="J244" s="10" t="n"/>
       <c r="K244" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -16690,7 +16802,7 @@
       <c r="J245" s="10" t="n"/>
       <c r="K245" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -16743,7 +16855,7 @@
       <c r="J246" s="10" t="n"/>
       <c r="K246" s="10" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -16796,7 +16908,7 @@
       <c r="J247" s="10" t="n"/>
       <c r="K247" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16961,7 @@
       <c r="J248" s="10" t="n"/>
       <c r="K248" s="10" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -16902,7 +17014,7 @@
       <c r="J249" s="10" t="n"/>
       <c r="K249" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -16955,7 +17067,7 @@
       <c r="J250" s="10" t="n"/>
       <c r="K250" s="10" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17120,7 @@
       <c r="J251" s="10" t="n"/>
       <c r="K251" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17173,7 @@
       <c r="J252" s="10" t="n"/>
       <c r="K252" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17224,11 @@
         </is>
       </c>
       <c r="J253" s="9" t="n"/>
-      <c r="K253" s="9" t="n"/>
+      <c r="K253" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="30" customHeight="1" s="16">
       <c r="A254" s="10" t="inlineStr">
@@ -17163,7 +17279,7 @@
       <c r="J254" s="10" t="n"/>
       <c r="K254" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17332,7 @@
       <c r="J255" s="10" t="n"/>
       <c r="K255" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17385,7 @@
       <c r="J256" s="10" t="n"/>
       <c r="K256" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17438,7 @@
       <c r="J257" s="10" t="n"/>
       <c r="K257" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17489,11 @@
         </is>
       </c>
       <c r="J258" s="9" t="n"/>
-      <c r="K258" s="9" t="n"/>
+      <c r="K258" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="30" customHeight="1" s="16">
       <c r="A259" s="9" t="inlineStr">
@@ -17424,7 +17544,7 @@
       <c r="J259" s="9" t="n"/>
       <c r="K259" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17597,7 @@
       <c r="J260" s="9" t="n"/>
       <c r="K260" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17650,7 @@
       <c r="J261" s="9" t="n"/>
       <c r="K261" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -17583,7 +17703,7 @@
       <c r="J262" s="9" t="n"/>
       <c r="K262" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -17636,7 +17756,7 @@
       <c r="J263" s="9" t="n"/>
       <c r="K263" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17809,7 @@
       <c r="J264" s="9" t="n"/>
       <c r="K264" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17862,7 @@
       <c r="J265" s="9" t="n"/>
       <c r="K265" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17915,7 @@
       <c r="J266" s="9" t="n"/>
       <c r="K266" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17968,7 @@
       <c r="J267" s="9" t="n"/>
       <c r="K267" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -17901,7 +18021,7 @@
       <c r="J268" s="9" t="n"/>
       <c r="K268" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -17954,7 +18074,7 @@
       <c r="J269" s="9" t="n"/>
       <c r="K269" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18125,11 @@
         </is>
       </c>
       <c r="J270" s="9" t="n"/>
-      <c r="K270" s="9" t="n"/>
+      <c r="K270" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="30" customHeight="1" s="16">
       <c r="A271" s="9" t="inlineStr">
@@ -18056,7 +18180,7 @@
       <c r="J271" s="9" t="n"/>
       <c r="K271" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18233,7 @@
       <c r="J272" s="9" t="n"/>
       <c r="K272" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -18162,7 +18286,7 @@
       <c r="J273" s="9" t="n"/>
       <c r="K273" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18339,7 @@
       <c r="J274" s="9" t="n"/>
       <c r="K274" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -18266,7 +18390,11 @@
         </is>
       </c>
       <c r="J275" s="9" t="n"/>
-      <c r="K275" s="9" t="n"/>
+      <c r="K275" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="30" customHeight="1" s="16">
       <c r="A276" s="9" t="inlineStr">
@@ -18317,7 +18445,7 @@
       <c r="J276" s="9" t="n"/>
       <c r="K276" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -18370,7 +18498,7 @@
       <c r="J277" s="9" t="n"/>
       <c r="K277" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18551,7 @@
       <c r="J278" s="9" t="n"/>
       <c r="K278" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -18476,7 +18604,7 @@
       <c r="J279" s="9" t="n"/>
       <c r="K279" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18657,7 @@
       <c r="J280" s="9" t="n"/>
       <c r="K280" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -18582,7 +18710,7 @@
       <c r="J281" s="9" t="n"/>
       <c r="K281" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18763,7 @@
       <c r="J282" s="9" t="n"/>
       <c r="K282" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18816,7 @@
       <c r="J283" s="9" t="n"/>
       <c r="K283" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -18741,7 +18869,7 @@
       <c r="J284" s="9" t="n"/>
       <c r="K284" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18920,11 @@
         </is>
       </c>
       <c r="J285" s="11" t="n"/>
-      <c r="K285" s="11" t="n"/>
+      <c r="K285" s="11" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="30" customHeight="1" s="16">
       <c r="A286" s="9" t="inlineStr">
@@ -18843,7 +18975,7 @@
       <c r="J286" s="9" t="n"/>
       <c r="K286" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -18896,7 +19028,7 @@
       <c r="J287" s="9" t="n"/>
       <c r="K287" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -18949,7 +19081,7 @@
       <c r="J288" s="9" t="n"/>
       <c r="K288" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19134,7 @@
       <c r="J289" s="9" t="n"/>
       <c r="K289" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19187,7 @@
       <c r="J290" s="9" t="n"/>
       <c r="K290" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19240,7 @@
       <c r="J291" s="9" t="n"/>
       <c r="K291" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19291,11 @@
         </is>
       </c>
       <c r="J292" s="11" t="n"/>
-      <c r="K292" s="11" t="n"/>
+      <c r="K292" s="11" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="30" customHeight="1" s="16">
       <c r="A293" s="9" t="inlineStr">
@@ -19210,7 +19346,7 @@
       <c r="J293" s="9" t="n"/>
       <c r="K293" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19399,7 @@
       <c r="J294" s="9" t="n"/>
       <c r="K294" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -19316,7 +19452,7 @@
       <c r="J295" s="9" t="n"/>
       <c r="K295" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -19369,7 +19505,7 @@
       <c r="J296" s="9" t="n"/>
       <c r="K296" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -19422,7 +19558,7 @@
       <c r="J297" s="9" t="n"/>
       <c r="K297" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19611,7 @@
       <c r="J298" s="9" t="n"/>
       <c r="K298" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -19528,7 +19664,7 @@
       <c r="J299" s="9" t="n"/>
       <c r="K299" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19717,7 @@
       <c r="J300" s="9" t="n"/>
       <c r="K300" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19770,7 @@
       <c r="J301" s="9" t="n"/>
       <c r="K301" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -19687,7 +19823,7 @@
       <c r="J302" s="9" t="n"/>
       <c r="K302" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19874,11 @@
         </is>
       </c>
       <c r="J303" s="9" t="n"/>
-      <c r="K303" s="9" t="n"/>
+      <c r="K303" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="30" customHeight="1" s="16">
       <c r="A304" s="9" t="inlineStr">
@@ -19789,7 +19929,7 @@
       <c r="J304" s="9" t="n"/>
       <c r="K304" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -19842,7 +19982,7 @@
       <c r="J305" s="9" t="n"/>
       <c r="K305" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -19895,7 +20035,7 @@
       <c r="J306" s="9" t="n"/>
       <c r="K306" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -19948,7 +20088,7 @@
       <c r="J307" s="9" t="n"/>
       <c r="K307" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20141,7 @@
       <c r="J308" s="9" t="n"/>
       <c r="K308" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20194,7 @@
       <c r="J309" s="9" t="n"/>
       <c r="K309" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20247,7 @@
       <c r="J310" s="9" t="n"/>
       <c r="K310" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -20158,7 +20298,11 @@
         </is>
       </c>
       <c r="J311" s="9" t="n"/>
-      <c r="K311" s="9" t="n"/>
+      <c r="K311" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="30" customHeight="1" s="16">
       <c r="A312" s="9" t="inlineStr">
@@ -20209,7 +20353,7 @@
       <c r="J312" s="9" t="n"/>
       <c r="K312" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20406,7 @@
       <c r="J313" s="9" t="n"/>
       <c r="K313" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20459,7 @@
       <c r="J314" s="9" t="n"/>
       <c r="K314" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -20368,7 +20512,7 @@
       <c r="J315" s="9" t="n"/>
       <c r="K315" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -20421,7 +20565,7 @@
       <c r="J316" s="9" t="n"/>
       <c r="K316" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20618,7 @@
       <c r="J317" s="9" t="n"/>
       <c r="K317" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20671,7 @@
       <c r="J318" s="9" t="n"/>
       <c r="K318" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20724,7 @@
       <c r="J319" s="9" t="n"/>
       <c r="K319" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20777,7 @@
       <c r="J320" s="9" t="n"/>
       <c r="K320" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20830,7 @@
       <c r="J321" s="9" t="n"/>
       <c r="K321" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -20739,7 +20883,7 @@
       <c r="J322" s="9" t="n"/>
       <c r="K322" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -20792,7 +20936,7 @@
       <c r="J323" s="9" t="n"/>
       <c r="K323" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20989,7 @@
       <c r="J324" s="9" t="n"/>
       <c r="K324" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -20896,7 +21040,11 @@
         </is>
       </c>
       <c r="J325" s="9" t="n"/>
-      <c r="K325" s="9" t="n"/>
+      <c r="K325" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="45" customHeight="1" s="16">
       <c r="A326" s="9" t="inlineStr">
@@ -20947,7 +21095,7 @@
       <c r="J326" s="9" t="n"/>
       <c r="K326" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21148,7 @@
       <c r="J327" s="9" t="n"/>
       <c r="K327" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21201,7 @@
       <c r="J328" s="9" t="n"/>
       <c r="K328" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21252,11 @@
         </is>
       </c>
       <c r="J329" s="9" t="n"/>
-      <c r="K329" s="9" t="n"/>
+      <c r="K329" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="45" customHeight="1" s="16">
       <c r="A330" s="9" t="inlineStr">
@@ -21155,7 +21307,7 @@
       <c r="J330" s="9" t="n"/>
       <c r="K330" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21360,7 @@
       <c r="J331" s="9" t="n"/>
       <c r="K331" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21413,7 @@
       <c r="J332" s="9" t="n"/>
       <c r="K332" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21466,7 @@
       <c r="J333" s="9" t="n"/>
       <c r="K333" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -21367,7 +21519,7 @@
       <c r="J334" s="9" t="n"/>
       <c r="K334" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -21420,7 +21572,7 @@
       <c r="J335" s="9" t="n"/>
       <c r="K335" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21625,7 @@
       <c r="J336" s="9" t="n"/>
       <c r="K336" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -21526,7 +21678,7 @@
       <c r="J337" s="12" t="n"/>
       <c r="K337" s="12" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21731,7 @@
       <c r="J338" s="12" t="n"/>
       <c r="K338" s="12" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -21630,7 +21782,11 @@
         </is>
       </c>
       <c r="J339" s="12" t="n"/>
-      <c r="K339" s="12" t="n"/>
+      <c r="K339" s="12" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="30" customHeight="1" s="16">
       <c r="A340" s="11" t="inlineStr">
@@ -21681,7 +21837,7 @@
       <c r="J340" s="11" t="n"/>
       <c r="K340" s="11" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21890,7 @@
       <c r="J341" s="12" t="n"/>
       <c r="K341" s="12" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -21787,7 +21943,7 @@
       <c r="J342" s="12" t="n"/>
       <c r="K342" s="12" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -21838,7 +21994,11 @@
         </is>
       </c>
       <c r="J343" s="12" t="n"/>
-      <c r="K343" s="12" t="n"/>
+      <c r="K343" s="12" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="30" customHeight="1" s="16">
       <c r="A344" s="9" t="inlineStr">
@@ -21889,7 +22049,7 @@
       <c r="J344" s="12" t="n"/>
       <c r="K344" s="12" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -21942,7 +22102,7 @@
       <c r="J345" s="9" t="n"/>
       <c r="K345" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -21995,7 +22155,7 @@
       <c r="J346" s="9" t="n"/>
       <c r="K346" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -22048,7 +22208,7 @@
       <c r="J347" s="9" t="n"/>
       <c r="K347" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -22101,7 +22261,7 @@
       <c r="J348" s="9" t="n"/>
       <c r="K348" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22314,7 @@
       <c r="J349" s="9" t="n"/>
       <c r="K349" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -22207,7 +22367,7 @@
       <c r="J350" s="9" t="n"/>
       <c r="K350" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22420,7 @@
       <c r="J351" s="9" t="n"/>
       <c r="K351" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -22313,7 +22473,7 @@
       <c r="J352" s="9" t="n"/>
       <c r="K352" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -22366,7 +22526,7 @@
       <c r="J353" s="9" t="n"/>
       <c r="K353" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -22419,7 +22579,7 @@
       <c r="J354" s="9" t="n"/>
       <c r="K354" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -22472,7 +22632,7 @@
       <c r="J355" s="9" t="n"/>
       <c r="K355" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -22525,7 +22685,7 @@
       <c r="J356" s="9" t="n"/>
       <c r="K356" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22738,7 @@
       <c r="J357" s="9" t="n"/>
       <c r="K357" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22791,7 @@
       <c r="J358" s="9" t="n"/>
       <c r="K358" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22844,7 @@
       <c r="J359" s="9" t="n"/>
       <c r="K359" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -22737,7 +22897,7 @@
       <c r="J360" s="9" t="n"/>
       <c r="K360" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -22790,7 +22950,7 @@
       <c r="J361" s="9" t="n"/>
       <c r="K361" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -22843,7 +23003,7 @@
       <c r="J362" s="9" t="n"/>
       <c r="K362" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -22896,7 +23056,7 @@
       <c r="J363" s="9" t="n"/>
       <c r="K363" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -22949,7 +23109,7 @@
       <c r="J364" s="9" t="n"/>
       <c r="K364" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -23002,7 +23162,7 @@
       <c r="J365" s="9" t="n"/>
       <c r="K365" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23215,7 @@
       <c r="J366" s="9" t="n"/>
       <c r="K366" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -23108,7 +23268,7 @@
       <c r="J367" s="9" t="n"/>
       <c r="K367" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -23161,7 +23321,7 @@
       <c r="J368" s="9" t="n"/>
       <c r="K368" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23374,7 @@
       <c r="J369" s="9" t="n"/>
       <c r="K369" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -23267,7 +23427,7 @@
       <c r="J370" s="9" t="n"/>
       <c r="K370" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23478,11 @@
         </is>
       </c>
       <c r="J371" s="9" t="n"/>
-      <c r="K371" s="9" t="n"/>
+      <c r="K371" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="372" s="16">
       <c r="A372" s="9" t="inlineStr">
@@ -23369,7 +23533,7 @@
       <c r="J372" s="9" t="n"/>
       <c r="K372" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -23422,7 +23586,7 @@
       <c r="J373" s="9" t="n"/>
       <c r="K373" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -23475,7 +23639,7 @@
       <c r="J374" s="9" t="n"/>
       <c r="K374" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23692,7 @@
       <c r="J375" s="9" t="n"/>
       <c r="K375" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -23579,7 +23743,11 @@
         </is>
       </c>
       <c r="J376" s="9" t="n"/>
-      <c r="K376" s="9" t="n"/>
+      <c r="K376" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="30" customHeight="1" s="16">
       <c r="A377" s="9" t="inlineStr">
@@ -23630,7 +23798,7 @@
       <c r="J377" s="9" t="n"/>
       <c r="K377" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -23683,7 +23851,7 @@
       <c r="J378" s="9" t="n"/>
       <c r="K378" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -23736,7 +23904,7 @@
       <c r="J379" s="9" t="n"/>
       <c r="K379" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -23789,7 +23957,7 @@
       <c r="J380" s="9" t="n"/>
       <c r="K380" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -23842,7 +24010,7 @@
       <c r="J381" s="9" t="n"/>
       <c r="K381" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -23895,7 +24063,7 @@
       <c r="J382" s="9" t="n"/>
       <c r="K382" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -23948,7 +24116,7 @@
       <c r="J383" s="9" t="n"/>
       <c r="K383" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -24001,7 +24169,7 @@
       <c r="J384" s="9" t="n"/>
       <c r="K384" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -24054,7 +24222,7 @@
       <c r="J385" s="9" t="n"/>
       <c r="K385" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -24107,7 +24275,7 @@
       <c r="J386" s="9" t="n"/>
       <c r="K386" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -24158,7 +24326,11 @@
         </is>
       </c>
       <c r="J387" s="9" t="n"/>
-      <c r="K387" s="9" t="n"/>
+      <c r="K387" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="30" customHeight="1" s="16">
       <c r="A388" s="9" t="inlineStr">
@@ -24209,7 +24381,7 @@
       <c r="J388" s="9" t="n"/>
       <c r="K388" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -24262,7 +24434,7 @@
       <c r="J389" s="9" t="n"/>
       <c r="K389" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -24315,7 +24487,7 @@
       <c r="J390" s="9" t="n"/>
       <c r="K390" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -24368,7 +24540,7 @@
       <c r="J391" s="9" t="n"/>
       <c r="K391" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -24419,7 +24591,11 @@
         </is>
       </c>
       <c r="J392" s="9" t="n"/>
-      <c r="K392" s="9" t="n"/>
+      <c r="K392" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="30" customHeight="1" s="16">
       <c r="A393" s="9" t="inlineStr">
@@ -24470,7 +24646,7 @@
       <c r="J393" s="9" t="n"/>
       <c r="K393" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24699,7 @@
       <c r="J394" s="9" t="n"/>
       <c r="K394" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24752,7 @@
       <c r="J395" s="9" t="n"/>
       <c r="K395" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -24629,7 +24805,7 @@
       <c r="J396" s="9" t="n"/>
       <c r="K396" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -24682,7 +24858,7 @@
       <c r="J397" s="9" t="n"/>
       <c r="K397" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -24735,7 +24911,7 @@
       <c r="J398" s="9" t="n"/>
       <c r="K398" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -24788,7 +24964,7 @@
       <c r="J399" s="9" t="n"/>
       <c r="K399" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -24839,7 +25015,11 @@
         </is>
       </c>
       <c r="J400" s="9" t="n"/>
-      <c r="K400" s="9" t="n"/>
+      <c r="K400" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="30" customHeight="1" s="16">
       <c r="A401" s="9" t="inlineStr">
@@ -24890,7 +25070,7 @@
       <c r="J401" s="9" t="n"/>
       <c r="K401" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -24943,7 +25123,7 @@
       <c r="J402" s="12" t="n"/>
       <c r="K402" s="12" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -24996,7 +25176,7 @@
       <c r="J403" s="9" t="n"/>
       <c r="K403" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -25049,7 +25229,7 @@
       <c r="J404" s="9" t="n"/>
       <c r="K404" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -25102,7 +25282,7 @@
       <c r="J405" s="9" t="n"/>
       <c r="K405" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -25155,7 +25335,7 @@
       <c r="J406" s="9" t="n"/>
       <c r="K406" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25386,11 @@
         </is>
       </c>
       <c r="J407" s="9" t="n"/>
-      <c r="K407" s="9" t="n"/>
+      <c r="K407" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="30" customHeight="1" s="16">
       <c r="A408" s="9" t="inlineStr">
@@ -25257,7 +25441,7 @@
       <c r="J408" s="9" t="n"/>
       <c r="K408" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25494,7 @@
       <c r="J409" s="9" t="n"/>
       <c r="K409" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -25363,7 +25547,7 @@
       <c r="J410" s="9" t="n"/>
       <c r="K410" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -25416,7 +25600,7 @@
       <c r="J411" s="9" t="n"/>
       <c r="K411" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25653,7 @@
       <c r="J412" s="9" t="n"/>
       <c r="K412" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -25522,7 +25706,7 @@
       <c r="J413" s="9" t="n"/>
       <c r="K413" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -25573,7 +25757,11 @@
         </is>
       </c>
       <c r="J414" s="9" t="n"/>
-      <c r="K414" s="9" t="n"/>
+      <c r="K414" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="30" customHeight="1" s="16">
       <c r="A415" s="9" t="inlineStr">
@@ -25624,7 +25812,7 @@
       <c r="J415" s="9" t="n"/>
       <c r="K415" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -25677,7 +25865,7 @@
       <c r="J416" s="9" t="n"/>
       <c r="K416" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25918,7 @@
       <c r="J417" s="9" t="n"/>
       <c r="K417" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -25783,7 +25971,7 @@
       <c r="J418" s="9" t="n"/>
       <c r="K418" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -25836,7 +26024,7 @@
       <c r="J419" s="9" t="n"/>
       <c r="K419" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -25889,7 +26077,7 @@
       <c r="J420" s="9" t="n"/>
       <c r="K420" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -25940,7 +26128,11 @@
         </is>
       </c>
       <c r="J421" s="9" t="n"/>
-      <c r="K421" s="9" t="n"/>
+      <c r="K421" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="45" customHeight="1" s="16">
       <c r="A422" s="10" t="inlineStr">
@@ -25991,7 +26183,7 @@
       <c r="J422" s="10" t="n"/>
       <c r="K422" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26236,7 @@
       <c r="J423" s="10" t="n"/>
       <c r="K423" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26289,7 @@
       <c r="J424" s="10" t="n"/>
       <c r="K424" s="10" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -26150,7 +26342,7 @@
       <c r="J425" s="10" t="n"/>
       <c r="K425" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -26203,7 +26395,7 @@
       <c r="J426" s="10" t="n"/>
       <c r="K426" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -26254,7 +26446,11 @@
         </is>
       </c>
       <c r="J427" s="10" t="n"/>
-      <c r="K427" s="10" t="n"/>
+      <c r="K427" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="30" customHeight="1" s="16">
       <c r="A428" s="10" t="inlineStr">
@@ -26305,7 +26501,7 @@
       <c r="J428" s="10" t="n"/>
       <c r="K428" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26554,7 @@
       <c r="J429" s="10" t="n"/>
       <c r="K429" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -26411,7 +26607,7 @@
       <c r="J430" s="10" t="n"/>
       <c r="K430" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -26464,7 +26660,7 @@
       <c r="J431" s="10" t="n"/>
       <c r="K431" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -26517,7 +26713,7 @@
       <c r="J432" s="10" t="n"/>
       <c r="K432" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -26568,7 +26764,11 @@
         </is>
       </c>
       <c r="J433" s="10" t="n"/>
-      <c r="K433" s="10" t="n"/>
+      <c r="K433" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="30" customHeight="1" s="16">
       <c r="A434" s="10" t="inlineStr">
@@ -26619,7 +26819,7 @@
       <c r="J434" s="10" t="n"/>
       <c r="K434" s="10" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -26672,7 +26872,7 @@
       <c r="J435" s="10" t="n"/>
       <c r="K435" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -26725,7 +26925,7 @@
       <c r="J436" s="10" t="n"/>
       <c r="K436" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -26778,7 +26978,7 @@
       <c r="J437" s="10" t="n"/>
       <c r="K437" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -26831,7 +27031,7 @@
       <c r="J438" s="10" t="n"/>
       <c r="K438" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -26884,7 +27084,7 @@
       <c r="J439" s="10" t="n"/>
       <c r="K439" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -26937,7 +27137,7 @@
       <c r="J440" s="10" t="n"/>
       <c r="K440" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -26990,7 +27190,7 @@
       <c r="J441" s="10" t="n"/>
       <c r="K441" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -27043,7 +27243,7 @@
       <c r="J442" s="10" t="n"/>
       <c r="K442" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -27096,7 +27296,7 @@
       <c r="J443" s="10" t="n"/>
       <c r="K443" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27347,11 @@
         </is>
       </c>
       <c r="J444" s="10" t="n"/>
-      <c r="K444" s="10" t="n"/>
+      <c r="K444" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="30" customHeight="1" s="16">
       <c r="A445" s="10" t="inlineStr">
@@ -27198,7 +27402,7 @@
       <c r="J445" s="10" t="n"/>
       <c r="K445" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27455,7 @@
       <c r="J446" s="10" t="n"/>
       <c r="K446" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -27304,7 +27508,7 @@
       <c r="J447" s="10" t="n"/>
       <c r="K447" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -27355,7 +27559,11 @@
         </is>
       </c>
       <c r="J448" s="10" t="n"/>
-      <c r="K448" s="10" t="n"/>
+      <c r="K448" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="30" customHeight="1" s="16">
       <c r="A449" s="10" t="inlineStr">
@@ -27406,7 +27614,7 @@
       <c r="J449" s="10" t="n"/>
       <c r="K449" s="10" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -27459,7 +27667,7 @@
       <c r="J450" s="9" t="n"/>
       <c r="K450" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27720,7 @@
       <c r="J451" s="9" t="n"/>
       <c r="K451" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -27565,7 +27773,7 @@
       <c r="J452" s="9" t="n"/>
       <c r="K452" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -27618,7 +27826,7 @@
       <c r="J453" s="9" t="n"/>
       <c r="K453" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27879,7 @@
       <c r="J454" s="9" t="n"/>
       <c r="K454" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -27724,7 +27932,7 @@
       <c r="J455" s="9" t="n"/>
       <c r="K455" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -27777,7 +27985,7 @@
       <c r="J456" s="9" t="n"/>
       <c r="K456" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -27830,7 +28038,7 @@
       <c r="J457" s="9" t="n"/>
       <c r="K457" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -27883,7 +28091,7 @@
       <c r="J458" s="9" t="n"/>
       <c r="K458" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -27936,7 +28144,7 @@
       <c r="J459" s="9" t="n"/>
       <c r="K459" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -27989,7 +28197,7 @@
       <c r="J460" s="9" t="n"/>
       <c r="K460" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28250,7 @@
       <c r="J461" s="9" t="n"/>
       <c r="K461" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -28095,7 +28303,7 @@
       <c r="J462" s="9" t="n"/>
       <c r="K462" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28356,7 @@
       <c r="J463" s="9" t="n"/>
       <c r="K463" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -28201,7 +28409,7 @@
       <c r="J464" s="12" t="n"/>
       <c r="K464" s="12" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28462,7 @@
       <c r="J465" s="12" t="n"/>
       <c r="K465" s="12" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -28305,7 +28513,11 @@
         </is>
       </c>
       <c r="J466" s="14" t="n"/>
-      <c r="K466" s="14" t="n"/>
+      <c r="K466" s="14" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="30" customHeight="1" s="16">
       <c r="A467" s="9" t="inlineStr">
@@ -28356,7 +28568,7 @@
       <c r="J467" s="9" t="n"/>
       <c r="K467" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -28409,7 +28621,7 @@
       <c r="J468" s="12" t="n"/>
       <c r="K468" s="12" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28674,7 @@
       <c r="J469" s="12" t="n"/>
       <c r="K469" s="12" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -28513,7 +28725,11 @@
         </is>
       </c>
       <c r="J470" s="14" t="n"/>
-      <c r="K470" s="14" t="n"/>
+      <c r="K470" s="14" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="471" s="16">
       <c r="A471" s="9" t="inlineStr">
@@ -28564,7 +28780,7 @@
       <c r="J471" s="12" t="n"/>
       <c r="K471" s="12" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -28617,7 +28833,7 @@
       <c r="J472" s="9" t="n"/>
       <c r="K472" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -28670,7 +28886,7 @@
       <c r="J473" s="9" t="n"/>
       <c r="K473" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -28723,7 +28939,7 @@
       <c r="J474" s="9" t="n"/>
       <c r="K474" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -28776,7 +28992,7 @@
       <c r="J475" s="9" t="n"/>
       <c r="K475" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -28829,7 +29045,7 @@
       <c r="J476" s="9" t="n"/>
       <c r="K476" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -28882,7 +29098,7 @@
       <c r="J477" s="9" t="n"/>
       <c r="K477" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -28935,7 +29151,7 @@
       <c r="J478" s="9" t="n"/>
       <c r="K478" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
         </is>
       </c>
     </row>
@@ -28986,7 +29202,11 @@
         </is>
       </c>
       <c r="J479" s="9" t="n"/>
-      <c r="K479" s="9" t="n"/>
+      <c r="K479" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="30" customHeight="1" s="16">
       <c r="A480" s="9" t="inlineStr">
@@ -29037,7 +29257,7 @@
       <c r="J480" s="9" t="n"/>
       <c r="K480" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29310,7 @@
       <c r="J481" s="9" t="n"/>
       <c r="K481" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -29143,7 +29363,7 @@
       <c r="J482" s="9" t="n"/>
       <c r="K482" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -29196,7 +29416,7 @@
       <c r="J483" s="9" t="n"/>
       <c r="K483" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29469,7 @@
       <c r="J484" s="9" t="n"/>
       <c r="K484" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29522,7 @@
       <c r="J485" s="9" t="n"/>
       <c r="K485" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29575,7 @@
       <c r="J486" s="9" t="n"/>
       <c r="K486" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -29408,7 +29628,7 @@
       <c r="J487" s="9" t="n"/>
       <c r="K487" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -29459,7 +29679,11 @@
         </is>
       </c>
       <c r="J488" s="9" t="n"/>
-      <c r="K488" s="9" t="n"/>
+      <c r="K488" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="489" ht="30" customHeight="1" s="16">
       <c r="A489" s="9" t="inlineStr">
@@ -29510,7 +29734,7 @@
       <c r="J489" s="9" t="n"/>
       <c r="K489" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -29563,7 +29787,7 @@
       <c r="J490" s="9" t="n"/>
       <c r="K490" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -29616,7 +29840,7 @@
       <c r="J491" s="9" t="n"/>
       <c r="K491" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -29669,7 +29893,7 @@
       <c r="J492" s="9" t="n"/>
       <c r="K492" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -29722,7 +29946,7 @@
       <c r="J493" s="9" t="n"/>
       <c r="K493" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -29775,7 +29999,7 @@
       <c r="J494" s="9" t="n"/>
       <c r="K494" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -29828,7 +30052,7 @@
       <c r="J495" s="9" t="n"/>
       <c r="K495" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -29881,7 +30105,7 @@
       <c r="J496" s="9" t="n"/>
       <c r="K496" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -29934,7 +30158,7 @@
       <c r="J497" s="9" t="n"/>
       <c r="K497" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -29987,7 +30211,7 @@
       <c r="J498" s="9" t="n"/>
       <c r="K498" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -30038,7 +30262,11 @@
         </is>
       </c>
       <c r="J499" s="9" t="n"/>
-      <c r="K499" s="9" t="n"/>
+      <c r="K499" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="30" customHeight="1" s="16">
       <c r="A500" s="9" t="inlineStr">
@@ -30089,7 +30317,7 @@
       <c r="J500" s="9" t="n"/>
       <c r="K500" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -30142,7 +30370,7 @@
       <c r="J501" s="9" t="n"/>
       <c r="K501" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -30193,7 +30421,11 @@
         </is>
       </c>
       <c r="J502" s="9" t="n"/>
-      <c r="K502" s="9" t="n"/>
+      <c r="K502" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="503" ht="30" customHeight="1" s="16">
       <c r="A503" s="9" t="inlineStr">
@@ -30244,7 +30476,7 @@
       <c r="J503" s="9" t="n"/>
       <c r="K503" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -30297,7 +30529,7 @@
       <c r="J504" s="9" t="n"/>
       <c r="K504" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -30350,7 +30582,7 @@
       <c r="J505" s="9" t="n"/>
       <c r="K505" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -30403,7 +30635,7 @@
       <c r="J506" s="9" t="n"/>
       <c r="K506" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -30456,7 +30688,7 @@
       <c r="J507" s="9" t="n"/>
       <c r="K507" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -30509,7 +30741,7 @@
       <c r="J508" s="9" t="n"/>
       <c r="K508" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -30562,7 +30794,7 @@
       <c r="J509" s="9" t="n"/>
       <c r="K509" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -30615,7 +30847,7 @@
       <c r="J510" s="9" t="n"/>
       <c r="K510" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -30668,7 +30900,7 @@
       <c r="J511" s="9" t="n"/>
       <c r="K511" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -30721,7 +30953,7 @@
       <c r="J512" s="9" t="n"/>
       <c r="K512" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -30772,7 +31004,11 @@
         </is>
       </c>
       <c r="J513" s="9" t="n"/>
-      <c r="K513" s="9" t="n"/>
+      <c r="K513" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="30" customHeight="1" s="16">
       <c r="A514" s="9" t="inlineStr">
@@ -30823,7 +31059,7 @@
       <c r="J514" s="9" t="n"/>
       <c r="K514" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -30876,7 +31112,7 @@
       <c r="J515" s="9" t="n"/>
       <c r="K515" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -30929,7 +31165,7 @@
       <c r="J516" s="9" t="n"/>
       <c r="K516" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -30982,7 +31218,7 @@
       <c r="J517" s="9" t="n"/>
       <c r="K517" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31271,7 @@
       <c r="J518" s="9" t="n"/>
       <c r="K518" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -31088,7 +31324,7 @@
       <c r="J519" s="9" t="n"/>
       <c r="K519" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -31139,7 +31375,11 @@
         </is>
       </c>
       <c r="J520" s="9" t="n"/>
-      <c r="K520" s="9" t="n"/>
+      <c r="K520" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="521" ht="30" customHeight="1" s="16">
       <c r="A521" s="9" t="inlineStr">
@@ -31190,7 +31430,7 @@
       <c r="J521" s="9" t="n"/>
       <c r="K521" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -31243,7 +31483,7 @@
       <c r="J522" s="9" t="n"/>
       <c r="K522" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -31296,7 +31536,7 @@
       <c r="J523" s="9" t="n"/>
       <c r="K523" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -31349,7 +31589,7 @@
       <c r="J524" s="9" t="n"/>
       <c r="K524" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -31402,7 +31642,7 @@
       <c r="J525" s="9" t="n"/>
       <c r="K525" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -31455,7 +31695,7 @@
       <c r="J526" s="9" t="n"/>
       <c r="K526" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -31508,7 +31748,7 @@
       <c r="J527" s="9" t="n"/>
       <c r="K527" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31799,11 @@
         </is>
       </c>
       <c r="J528" s="9" t="n"/>
-      <c r="K528" s="9" t="n"/>
+      <c r="K528" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="30" customHeight="1" s="16">
       <c r="A529" s="9" t="inlineStr">
@@ -31610,7 +31854,7 @@
       <c r="J529" s="9" t="n"/>
       <c r="K529" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -31663,7 +31907,7 @@
       <c r="J530" s="9" t="n"/>
       <c r="K530" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -31716,7 +31960,7 @@
       <c r="J531" s="9" t="n"/>
       <c r="K531" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -31769,7 +32013,7 @@
       <c r="J532" s="9" t="n"/>
       <c r="K532" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -31822,7 +32066,7 @@
       <c r="J533" s="9" t="n"/>
       <c r="K533" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -31875,7 +32119,7 @@
       <c r="J534" s="9" t="n"/>
       <c r="K534" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -31928,7 +32172,7 @@
       <c r="J535" s="9" t="n"/>
       <c r="K535" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -31981,7 +32225,7 @@
       <c r="J536" s="9" t="n"/>
       <c r="K536" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -32032,7 +32276,11 @@
         </is>
       </c>
       <c r="J537" s="9" t="n"/>
-      <c r="K537" s="9" t="n"/>
+      <c r="K537" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="30" customHeight="1" s="16">
       <c r="A538" s="9" t="inlineStr">
@@ -32083,7 +32331,7 @@
       <c r="J538" s="9" t="n"/>
       <c r="K538" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -32136,7 +32384,7 @@
       <c r="J539" s="9" t="n"/>
       <c r="K539" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -32189,7 +32437,7 @@
       <c r="J540" s="9" t="n"/>
       <c r="K540" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -32242,7 +32490,7 @@
       <c r="J541" s="9" t="n"/>
       <c r="K541" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -32295,7 +32543,7 @@
       <c r="J542" s="9" t="n"/>
       <c r="K542" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -32348,7 +32596,7 @@
       <c r="J543" s="9" t="n"/>
       <c r="K543" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -32401,7 +32649,7 @@
       <c r="J544" s="9" t="n"/>
       <c r="K544" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -32454,7 +32702,7 @@
       <c r="J545" s="9" t="n"/>
       <c r="K545" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -32507,7 +32755,7 @@
       <c r="J546" s="9" t="n"/>
       <c r="K546" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -32560,7 +32808,7 @@
       <c r="J547" s="9" t="n"/>
       <c r="K547" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -32613,7 +32861,7 @@
       <c r="J548" s="9" t="n"/>
       <c r="K548" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -32666,7 +32914,7 @@
       <c r="J549" s="9" t="n"/>
       <c r="K549" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -32719,7 +32967,7 @@
       <c r="J550" s="9" t="n"/>
       <c r="K550" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -32772,7 +33020,7 @@
       <c r="J551" s="9" t="n"/>
       <c r="K551" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -32823,7 +33071,11 @@
         </is>
       </c>
       <c r="J552" s="9" t="n"/>
-      <c r="K552" s="9" t="n"/>
+      <c r="K552" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="553" ht="30" customHeight="1" s="16">
       <c r="A553" s="9" t="inlineStr">
@@ -32874,7 +33126,7 @@
       <c r="J553" s="9" t="n"/>
       <c r="K553" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -32925,7 +33177,11 @@
         </is>
       </c>
       <c r="J554" s="9" t="n"/>
-      <c r="K554" s="9" t="n"/>
+      <c r="K554" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="555" ht="30" customHeight="1" s="16">
       <c r="A555" s="10" t="inlineStr">
@@ -32976,7 +33232,7 @@
       <c r="J555" s="10" t="n"/>
       <c r="K555" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -33029,7 +33285,7 @@
       <c r="J556" s="10" t="n"/>
       <c r="K556" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -33082,7 +33338,7 @@
       <c r="J557" s="10" t="n"/>
       <c r="K557" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -33135,7 +33391,7 @@
       <c r="J558" s="10" t="n"/>
       <c r="K558" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -33188,7 +33444,7 @@
       <c r="J559" s="10" t="n"/>
       <c r="K559" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -33241,7 +33497,7 @@
       <c r="J560" s="10" t="n"/>
       <c r="K560" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -33294,7 +33550,7 @@
       <c r="J561" s="10" t="n"/>
       <c r="K561" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -33347,7 +33603,7 @@
       <c r="J562" s="10" t="n"/>
       <c r="K562" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -33400,7 +33656,7 @@
       <c r="J563" s="10" t="n"/>
       <c r="K563" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -33451,7 +33707,11 @@
         </is>
       </c>
       <c r="J564" s="10" t="n"/>
-      <c r="K564" s="10" t="n"/>
+      <c r="K564" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="30" customHeight="1" s="16">
       <c r="A565" s="10" t="inlineStr">
@@ -33502,7 +33762,7 @@
       <c r="J565" s="10" t="n"/>
       <c r="K565" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -33555,7 +33815,7 @@
       <c r="J566" s="10" t="n"/>
       <c r="K566" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -33608,7 +33868,7 @@
       <c r="J567" s="10" t="n"/>
       <c r="K567" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -33661,7 +33921,7 @@
       <c r="J568" s="10" t="n"/>
       <c r="K568" s="10" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -33714,7 +33974,7 @@
       <c r="J569" s="10" t="n"/>
       <c r="K569" s="10" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -33767,7 +34027,7 @@
       <c r="J570" s="10" t="n"/>
       <c r="K570" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -33820,7 +34080,7 @@
       <c r="J571" s="10" t="n"/>
       <c r="K571" s="10" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -33871,7 +34131,11 @@
         </is>
       </c>
       <c r="J572" s="10" t="n"/>
-      <c r="K572" s="10" t="n"/>
+      <c r="K572" s="10" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="573" ht="30" customHeight="1" s="16">
       <c r="A573" s="10" t="inlineStr">
@@ -33922,7 +34186,7 @@
       <c r="J573" s="10" t="n"/>
       <c r="K573" s="10" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -33975,7 +34239,7 @@
       <c r="J574" s="10" t="n"/>
       <c r="K574" s="10" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -34028,7 +34292,7 @@
       <c r="J575" s="10" t="n"/>
       <c r="K575" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -34081,7 +34345,7 @@
       <c r="J576" s="9" t="n"/>
       <c r="K576" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -34134,7 +34398,7 @@
       <c r="J577" s="9" t="n"/>
       <c r="K577" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -34187,7 +34451,7 @@
       <c r="J578" s="9" t="n"/>
       <c r="K578" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -34240,7 +34504,7 @@
       <c r="J579" s="9" t="n"/>
       <c r="K579" s="9" t="inlineStr">
         <is>
-          <t>ENVS252 Geomorphology: Ice, Sea and Air (closest)</t>
+          <t>ENVS252 GEOMORPHOLOGY: ICE, SEA AND AIR (closest)</t>
         </is>
       </c>
     </row>
@@ -34293,7 +34557,7 @@
       <c r="J580" s="9" t="n"/>
       <c r="K580" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS for Human Geography (closest)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -34344,7 +34608,11 @@
         </is>
       </c>
       <c r="J581" s="9" t="n"/>
-      <c r="K581" s="9" t="n"/>
+      <c r="K581" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="582" ht="30" customHeight="1" s="16">
       <c r="A582" s="9" t="inlineStr">
@@ -34395,7 +34663,7 @@
       <c r="J582" s="9" t="n"/>
       <c r="K582" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -34448,7 +34716,7 @@
       <c r="J583" s="9" t="n"/>
       <c r="K583" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -34501,7 +34769,7 @@
       <c r="J584" s="9" t="n"/>
       <c r="K584" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -34554,7 +34822,7 @@
       <c r="J585" s="9" t="n"/>
       <c r="K585" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -34605,7 +34873,11 @@
         </is>
       </c>
       <c r="J586" s="9" t="n"/>
-      <c r="K586" s="9" t="n"/>
+      <c r="K586" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="587" ht="30" customHeight="1" s="16">
       <c r="A587" s="10" t="inlineStr">
@@ -34656,7 +34928,7 @@
       <c r="J587" s="10" t="n"/>
       <c r="K587" s="10" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -34709,7 +34981,7 @@
       <c r="J588" s="9" t="n"/>
       <c r="K588" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -34762,7 +35034,7 @@
       <c r="J589" s="9" t="n"/>
       <c r="K589" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -34815,7 +35087,7 @@
       <c r="J590" s="9" t="n"/>
       <c r="K590" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -34868,7 +35140,7 @@
       <c r="J591" s="9" t="n"/>
       <c r="K591" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -34921,7 +35193,7 @@
       <c r="J592" s="9" t="n"/>
       <c r="K592" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -34974,7 +35246,7 @@
       <c r="J593" s="9" t="n"/>
       <c r="K593" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -35027,7 +35299,7 @@
       <c r="J594" s="9" t="n"/>
       <c r="K594" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -35080,7 +35352,7 @@
       <c r="J595" s="9" t="n"/>
       <c r="K595" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -35131,7 +35403,11 @@
         </is>
       </c>
       <c r="J596" s="9" t="n"/>
-      <c r="K596" s="9" t="n"/>
+      <c r="K596" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="597" ht="60" customHeight="1" s="16">
       <c r="A597" s="9" t="inlineStr">
@@ -35182,7 +35458,7 @@
       <c r="J597" s="9" t="n"/>
       <c r="K597" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
         </is>
       </c>
     </row>
@@ -35235,7 +35511,7 @@
       <c r="J598" s="9" t="n"/>
       <c r="K598" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35288,7 +35564,7 @@
       <c r="J599" s="9" t="n"/>
       <c r="K599" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35341,7 +35617,7 @@
       <c r="J600" s="9" t="n"/>
       <c r="K600" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 Physical Geography Fieldwork Course (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
         </is>
       </c>
     </row>
@@ -35394,7 +35670,7 @@
       <c r="J601" s="9" t="n"/>
       <c r="K601" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35445,7 +35721,11 @@
         </is>
       </c>
       <c r="J602" s="9" t="n"/>
-      <c r="K602" s="9" t="n"/>
+      <c r="K602" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="603" ht="30" customHeight="1" s="16">
       <c r="A603" s="10" t="inlineStr">
@@ -35496,7 +35776,7 @@
       <c r="J603" s="10" t="n"/>
       <c r="K603" s="10" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -35549,7 +35829,7 @@
       <c r="J604" s="9" t="n"/>
       <c r="K604" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35602,7 +35882,7 @@
       <c r="J605" s="9" t="n"/>
       <c r="K605" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35655,7 +35935,7 @@
       <c r="J606" s="9" t="n"/>
       <c r="K606" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35708,7 +35988,7 @@
       <c r="J607" s="9" t="n"/>
       <c r="K607" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -35761,7 +36041,7 @@
       <c r="J608" s="9" t="n"/>
       <c r="K608" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +36094,7 @@
       <c r="J609" s="9" t="n"/>
       <c r="K609" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35867,7 +36147,7 @@
       <c r="J610" s="9" t="n"/>
       <c r="K610" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -35920,7 +36200,7 @@
       <c r="J611" s="9" t="n"/>
       <c r="K611" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -35971,7 +36251,11 @@
         </is>
       </c>
       <c r="J612" s="9" t="n"/>
-      <c r="K612" s="9" t="n"/>
+      <c r="K612" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="613" ht="30" customHeight="1" s="16">
       <c r="A613" s="9" t="inlineStr">
@@ -36022,7 +36306,7 @@
       <c r="J613" s="9" t="n"/>
       <c r="K613" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -36075,7 +36359,7 @@
       <c r="J614" s="9" t="n"/>
       <c r="K614" s="9" t="inlineStr">
         <is>
-          <t>ENVS230 Cities and Regions (same module)</t>
+          <t>ENVS230 CITIES AND REGIONS</t>
         </is>
       </c>
     </row>
@@ -36128,7 +36412,7 @@
       <c r="J615" s="9" t="n"/>
       <c r="K615" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -36181,7 +36465,7 @@
       <c r="J616" s="9" t="n"/>
       <c r="K616" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -36234,7 +36518,7 @@
       <c r="J617" s="9" t="n"/>
       <c r="K617" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -36287,7 +36571,7 @@
       <c r="J618" s="9" t="n"/>
       <c r="K618" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -36340,7 +36624,7 @@
       <c r="J619" s="9" t="n"/>
       <c r="K619" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -36393,7 +36677,7 @@
       <c r="J620" s="9" t="n"/>
       <c r="K620" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -36446,7 +36730,7 @@
       <c r="J621" s="9" t="n"/>
       <c r="K621" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36783,7 @@
       <c r="J622" s="9" t="n"/>
       <c r="K622" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -36552,7 +36836,7 @@
       <c r="J623" s="9" t="n"/>
       <c r="K623" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -36603,7 +36887,11 @@
         </is>
       </c>
       <c r="J624" s="9" t="n"/>
-      <c r="K624" s="9" t="n"/>
+      <c r="K624" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="625" ht="30" customHeight="1" s="16">
       <c r="A625" s="9" t="inlineStr">
@@ -36654,7 +36942,7 @@
       <c r="J625" s="9" t="n"/>
       <c r="K625" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -36707,7 +36995,7 @@
       <c r="J626" s="9" t="n"/>
       <c r="K626" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -36758,7 +37046,11 @@
         </is>
       </c>
       <c r="J627" s="9" t="n"/>
-      <c r="K627" s="9" t="n"/>
+      <c r="K627" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="628" ht="30" customHeight="1" s="16">
       <c r="A628" s="9" t="inlineStr">
@@ -36809,7 +37101,7 @@
       <c r="J628" s="9" t="n"/>
       <c r="K628" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -36862,7 +37154,7 @@
       <c r="J629" s="9" t="n"/>
       <c r="K629" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -36915,7 +37207,7 @@
       <c r="J630" s="9" t="n"/>
       <c r="K630" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -36968,7 +37260,7 @@
       <c r="J631" s="9" t="n"/>
       <c r="K631" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -37021,7 +37313,7 @@
       <c r="J632" s="9" t="n"/>
       <c r="K632" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -37074,7 +37366,7 @@
       <c r="J633" s="9" t="n"/>
       <c r="K633" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -37127,7 +37419,7 @@
       <c r="J634" s="9" t="n"/>
       <c r="K634" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -37180,7 +37472,7 @@
       <c r="J635" s="9" t="n"/>
       <c r="K635" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37525,7 @@
       <c r="J636" s="9" t="n"/>
       <c r="K636" s="9" t="inlineStr">
         <is>
-          <t>ENVS275 Social and Cultural Geographies (same module)</t>
+          <t>ENVS275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
     </row>
@@ -37286,7 +37578,7 @@
       <c r="J637" s="9" t="n"/>
       <c r="K637" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 Political Economies of Globalisation (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
         </is>
       </c>
     </row>
@@ -37339,7 +37631,7 @@
       <c r="J638" s="9" t="n"/>
       <c r="K638" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (new module)</t>
+          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
         </is>
       </c>
     </row>
@@ -37390,7 +37682,11 @@
         </is>
       </c>
       <c r="J639" s="9" t="n"/>
-      <c r="K639" s="9" t="n"/>
+      <c r="K639" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="640" ht="30" customHeight="1" s="16">
       <c r="A640" s="9" t="inlineStr">
@@ -37441,7 +37737,7 @@
       <c r="J640" s="9" t="n"/>
       <c r="K640" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -37494,7 +37790,7 @@
       <c r="J641" s="9" t="n"/>
       <c r="K641" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -37547,7 +37843,7 @@
       <c r="J642" s="9" t="n"/>
       <c r="K642" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 Climatology / ENVS217 Catchment Hydrology (closest)</t>
+          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
         </is>
       </c>
     </row>
@@ -37598,7 +37894,11 @@
         </is>
       </c>
       <c r="J643" s="9" t="n"/>
-      <c r="K643" s="9" t="n"/>
+      <c r="K643" s="9" t="inlineStr">
+        <is>
+          <t>ENVS249 PRINCIPLES AND THEORY IN GEOGRAPHY (Year 1 in new curriculum: SOES164 GEOGRAPHICAL THOUGHT)</t>
+        </is>
+      </c>
     </row>
     <row r="644" ht="30" customHeight="1" s="16">
       <c r="A644" s="9" t="inlineStr">
@@ -37649,7 +37949,7 @@
       <c r="J644" s="9" t="n"/>
       <c r="K644" s="9" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>
@@ -37702,7 +38002,7 @@
       <c r="J645" s="9" t="n"/>
       <c r="K645" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -37755,7 +38055,7 @@
       <c r="J646" s="9" t="n"/>
       <c r="K646" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -37808,7 +38108,7 @@
       <c r="J647" s="9" t="n"/>
       <c r="K647" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -37861,7 +38161,7 @@
       <c r="J648" s="9" t="n"/>
       <c r="K648" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 Planning for Environmental Sustainability (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
         </is>
       </c>
     </row>
@@ -37914,7 +38214,7 @@
       <c r="J649" s="9" t="n"/>
       <c r="K649" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -37967,7 +38267,7 @@
       <c r="J650" s="9" t="n"/>
       <c r="K650" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -38020,7 +38320,7 @@
       <c r="J651" s="9" t="n"/>
       <c r="K651" s="9" t="inlineStr">
         <is>
-          <t>No direct 2026/27 equivalent (nearest: ENVS257 GIS for Human Geography)</t>
+          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
         </is>
       </c>
     </row>
@@ -38073,7 +38373,7 @@
       <c r="J652" s="9" t="n"/>
       <c r="K652" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -38126,7 +38426,7 @@
       <c r="J653" s="9" t="n"/>
       <c r="K653" s="9" t="inlineStr">
         <is>
-          <t>ENVS225 Exploring the Social World (same module)</t>
+          <t>ENVS225 EXPLORING THE SOCIAL WORLD</t>
         </is>
       </c>
     </row>
@@ -38179,7 +38479,7 @@
       <c r="J654" s="9" t="n"/>
       <c r="K654" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 People and Place (closest)</t>
+          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
         </is>
       </c>
     </row>
@@ -38232,7 +38532,7 @@
       <c r="J655" s="9" t="n"/>
       <c r="K655" s="9" t="inlineStr">
         <is>
-          <t>ENVS214 Changing Environments (same module)</t>
+          <t>ENVS214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
     </row>
@@ -38285,7 +38585,7 @@
       <c r="J656" s="11" t="n"/>
       <c r="K656" s="11" t="inlineStr">
         <is>
-          <t>ENVS202 Key Skills for Environmental Data Analysis (closest)</t>
+          <t>ENVS202 KEY SKILLS FOR ENVIRONMENTAL DATA ANALYSIS (closest)</t>
         </is>
       </c>
     </row>

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -3976,7 +3976,7 @@
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       <c r="J4" s="10" t="n"/>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       <c r="J6" s="10" t="n"/>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       <c r="J56" s="9" t="n"/>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7315,7 @@
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -7845,7 +7845,7 @@
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="J82" s="9" t="n"/>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       <c r="J86" s="9" t="n"/>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
       <c r="J88" s="9" t="n"/>
       <c r="K88" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
       <c r="J92" s="9" t="n"/>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       <c r="J96" s="10" t="n"/>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
       <c r="J100" s="10" t="n"/>
       <c r="K100" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       <c r="J103" s="10" t="n"/>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       <c r="J106" s="10" t="n"/>
       <c r="K106" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       <c r="J109" s="10" t="n"/>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       <c r="J111" s="9" t="n"/>
       <c r="K111" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       <c r="J112" s="9" t="n"/>
       <c r="K112" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       <c r="J113" s="9" t="n"/>
       <c r="K113" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9912,7 @@
       <c r="J115" s="9" t="n"/>
       <c r="K115" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       <c r="J116" s="9" t="n"/>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       <c r="J117" s="9" t="n"/>
       <c r="K117" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       <c r="J118" s="9" t="n"/>
       <c r="K118" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       <c r="J119" s="9" t="n"/>
       <c r="K119" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       <c r="J120" s="9" t="n"/>
       <c r="K120" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       <c r="J124" s="9" t="n"/>
       <c r="K124" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       <c r="J125" s="9" t="n"/>
       <c r="K125" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       <c r="J127" s="9" t="n"/>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       <c r="J128" s="9" t="n"/>
       <c r="K128" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       <c r="J130" s="9" t="n"/>
       <c r="K130" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       <c r="J131" s="9" t="n"/>
       <c r="K131" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       <c r="J136" s="9" t="n"/>
       <c r="K136" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       <c r="J138" s="9" t="n"/>
       <c r="K138" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       <c r="J139" s="9" t="n"/>
       <c r="K139" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       <c r="J142" s="9" t="n"/>
       <c r="K142" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       <c r="J143" s="9" t="n"/>
       <c r="K143" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
       <c r="J144" s="9" t="n"/>
       <c r="K144" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
       <c r="J146" s="9" t="n"/>
       <c r="K146" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       <c r="J148" s="9" t="n"/>
       <c r="K148" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       <c r="J150" s="9" t="n"/>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       <c r="J154" s="9" t="n"/>
       <c r="K154" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       <c r="J155" s="9" t="n"/>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12085,7 @@
       <c r="J156" s="9" t="n"/>
       <c r="K156" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       <c r="J158" s="9" t="n"/>
       <c r="K158" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12403,7 @@
       <c r="J162" s="9" t="n"/>
       <c r="K162" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       <c r="J163" s="9" t="n"/>
       <c r="K163" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12721,7 @@
       <c r="J168" s="9" t="n"/>
       <c r="K168" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       <c r="J169" s="9" t="n"/>
       <c r="K169" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       <c r="J174" s="9" t="n"/>
       <c r="K174" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13198,7 @@
       <c r="J177" s="9" t="n"/>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       <c r="J178" s="9" t="n"/>
       <c r="K178" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       <c r="J179" s="9" t="n"/>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       <c r="J180" s="9" t="n"/>
       <c r="K180" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
       <c r="J181" s="9" t="n"/>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -13516,7 +13516,7 @@
       <c r="J183" s="9" t="n"/>
       <c r="K183" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
       <c r="J184" s="9" t="n"/>
       <c r="K184" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       <c r="J187" s="9" t="n"/>
       <c r="K187" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       <c r="J189" s="9" t="n"/>
       <c r="K189" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -13887,7 +13887,7 @@
       <c r="J190" s="9" t="n"/>
       <c r="K190" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14099,7 @@
       <c r="J194" s="9" t="n"/>
       <c r="K194" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       <c r="J196" s="9" t="n"/>
       <c r="K196" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       <c r="J197" s="9" t="n"/>
       <c r="K197" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       <c r="J198" s="9" t="n"/>
       <c r="K198" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       <c r="J199" s="9" t="n"/>
       <c r="K199" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14576,7 @@
       <c r="J203" s="9" t="n"/>
       <c r="K203" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       <c r="J205" s="9" t="n"/>
       <c r="K205" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       <c r="J207" s="9" t="n"/>
       <c r="K207" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -15053,7 +15053,7 @@
       <c r="J212" s="9" t="n"/>
       <c r="K212" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       <c r="J213" s="9" t="n"/>
       <c r="K213" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -15318,7 +15318,7 @@
       <c r="J217" s="9" t="n"/>
       <c r="K217" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -15424,7 +15424,7 @@
       <c r="J219" s="9" t="n"/>
       <c r="K219" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       <c r="J221" s="9" t="n"/>
       <c r="K221" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -15583,7 +15583,7 @@
       <c r="J222" s="9" t="n"/>
       <c r="K222" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       <c r="J225" s="9" t="n"/>
       <c r="K225" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -15795,7 +15795,7 @@
       <c r="J226" s="9" t="n"/>
       <c r="K226" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       <c r="J227" s="9" t="n"/>
       <c r="K227" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -15901,7 +15901,7 @@
       <c r="J228" s="9" t="n"/>
       <c r="K228" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       <c r="J230" s="9" t="n"/>
       <c r="K230" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16060,7 @@
       <c r="J231" s="9" t="n"/>
       <c r="K231" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16113,7 @@
       <c r="J232" s="9" t="n"/>
       <c r="K232" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -16537,7 +16537,7 @@
       <c r="J240" s="10" t="n"/>
       <c r="K240" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       <c r="J241" s="10" t="n"/>
       <c r="K241" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       <c r="J244" s="10" t="n"/>
       <c r="K244" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -16908,7 +16908,7 @@
       <c r="J247" s="10" t="n"/>
       <c r="K247" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17014,7 @@
       <c r="J249" s="10" t="n"/>
       <c r="K249" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -17385,7 +17385,7 @@
       <c r="J256" s="10" t="n"/>
       <c r="K256" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       <c r="J257" s="10" t="n"/>
       <c r="K257" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       <c r="J260" s="9" t="n"/>
       <c r="K260" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       <c r="J263" s="9" t="n"/>
       <c r="K263" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18074,7 @@
       <c r="J269" s="9" t="n"/>
       <c r="K269" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18180,7 +18180,7 @@
       <c r="J271" s="9" t="n"/>
       <c r="K271" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
       <c r="J276" s="9" t="n"/>
       <c r="K276" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       <c r="J277" s="9" t="n"/>
       <c r="K277" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18604,7 +18604,7 @@
       <c r="J279" s="9" t="n"/>
       <c r="K279" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -18710,7 +18710,7 @@
       <c r="J281" s="9" t="n"/>
       <c r="K281" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18763,7 +18763,7 @@
       <c r="J282" s="9" t="n"/>
       <c r="K282" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -18869,7 +18869,7 @@
       <c r="J284" s="9" t="n"/>
       <c r="K284" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       <c r="J289" s="9" t="n"/>
       <c r="K289" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       <c r="J290" s="9" t="n"/>
       <c r="K290" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19240,7 @@
       <c r="J291" s="9" t="n"/>
       <c r="K291" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -19611,7 +19611,7 @@
       <c r="J298" s="9" t="n"/>
       <c r="K298" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -19664,7 +19664,7 @@
       <c r="J299" s="9" t="n"/>
       <c r="K299" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -19717,7 +19717,7 @@
       <c r="J300" s="9" t="n"/>
       <c r="K300" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       <c r="J304" s="9" t="n"/>
       <c r="K304" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -20088,7 +20088,7 @@
       <c r="J307" s="9" t="n"/>
       <c r="K307" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -20141,7 +20141,7 @@
       <c r="J308" s="9" t="n"/>
       <c r="K308" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       <c r="J309" s="9" t="n"/>
       <c r="K309" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -20353,7 +20353,7 @@
       <c r="J312" s="9" t="n"/>
       <c r="K312" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       <c r="J313" s="9" t="n"/>
       <c r="K313" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -20512,7 +20512,7 @@
       <c r="J315" s="9" t="n"/>
       <c r="K315" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       <c r="J318" s="9" t="n"/>
       <c r="K318" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       <c r="J319" s="9" t="n"/>
       <c r="K319" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       <c r="J322" s="9" t="n"/>
       <c r="K322" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -21095,7 +21095,7 @@
       <c r="J326" s="9" t="n"/>
       <c r="K326" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       <c r="J327" s="9" t="n"/>
       <c r="K327" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -21307,7 +21307,7 @@
       <c r="J330" s="9" t="n"/>
       <c r="K330" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21360,7 @@
       <c r="J331" s="9" t="n"/>
       <c r="K331" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -21466,7 +21466,7 @@
       <c r="J333" s="9" t="n"/>
       <c r="K333" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -21519,7 +21519,7 @@
       <c r="J334" s="9" t="n"/>
       <c r="K334" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -21572,7 +21572,7 @@
       <c r="J335" s="9" t="n"/>
       <c r="K335" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -21678,7 +21678,7 @@
       <c r="J337" s="12" t="n"/>
       <c r="K337" s="12" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -21943,7 +21943,7 @@
       <c r="J342" s="12" t="n"/>
       <c r="K342" s="12" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -22102,7 +22102,7 @@
       <c r="J345" s="9" t="n"/>
       <c r="K345" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22155,7 @@
       <c r="J346" s="9" t="n"/>
       <c r="K346" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22208,7 @@
       <c r="J347" s="9" t="n"/>
       <c r="K347" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -22632,7 +22632,7 @@
       <c r="J355" s="9" t="n"/>
       <c r="K355" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -22791,7 +22791,7 @@
       <c r="J358" s="9" t="n"/>
       <c r="K358" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22844,7 @@
       <c r="J359" s="9" t="n"/>
       <c r="K359" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -22950,7 +22950,7 @@
       <c r="J361" s="9" t="n"/>
       <c r="K361" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -23056,7 +23056,7 @@
       <c r="J363" s="9" t="n"/>
       <c r="K363" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -23109,7 +23109,7 @@
       <c r="J364" s="9" t="n"/>
       <c r="K364" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -23215,7 +23215,7 @@
       <c r="J366" s="9" t="n"/>
       <c r="K366" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -23427,7 +23427,7 @@
       <c r="J370" s="9" t="n"/>
       <c r="K370" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -23586,7 +23586,7 @@
       <c r="J373" s="9" t="n"/>
       <c r="K373" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       <c r="J375" s="9" t="n"/>
       <c r="K375" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -23851,7 +23851,7 @@
       <c r="J378" s="9" t="n"/>
       <c r="K378" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -23957,7 +23957,7 @@
       <c r="J380" s="9" t="n"/>
       <c r="K380" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -24010,7 +24010,7 @@
       <c r="J381" s="9" t="n"/>
       <c r="K381" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -24116,7 +24116,7 @@
       <c r="J383" s="9" t="n"/>
       <c r="K383" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       <c r="J384" s="9" t="n"/>
       <c r="K384" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -24275,7 +24275,7 @@
       <c r="J386" s="9" t="n"/>
       <c r="K386" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -24805,7 +24805,7 @@
       <c r="J396" s="9" t="n"/>
       <c r="K396" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -24911,7 +24911,7 @@
       <c r="J398" s="9" t="n"/>
       <c r="K398" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -25123,7 +25123,7 @@
       <c r="J402" s="12" t="n"/>
       <c r="K402" s="12" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -25176,7 +25176,7 @@
       <c r="J403" s="9" t="n"/>
       <c r="K403" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       <c r="J408" s="9" t="n"/>
       <c r="K408" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       <c r="J409" s="9" t="n"/>
       <c r="K409" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -25918,7 +25918,7 @@
       <c r="J417" s="9" t="n"/>
       <c r="K417" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
       <c r="J418" s="9" t="n"/>
       <c r="K418" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26024,7 +26024,7 @@
       <c r="J419" s="9" t="n"/>
       <c r="K419" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -26183,7 +26183,7 @@
       <c r="J422" s="10" t="n"/>
       <c r="K422" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26236,7 +26236,7 @@
       <c r="J423" s="10" t="n"/>
       <c r="K423" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26289,7 +26289,7 @@
       <c r="J424" s="10" t="n"/>
       <c r="K424" s="10" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       <c r="J425" s="10" t="n"/>
       <c r="K425" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26395,7 +26395,7 @@
       <c r="J426" s="10" t="n"/>
       <c r="K426" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26501,7 +26501,7 @@
       <c r="J428" s="10" t="n"/>
       <c r="K428" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26713,7 +26713,7 @@
       <c r="J432" s="10" t="n"/>
       <c r="K432" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -26872,7 +26872,7 @@
       <c r="J435" s="10" t="n"/>
       <c r="K435" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -26925,7 +26925,7 @@
       <c r="J436" s="10" t="n"/>
       <c r="K436" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -27137,7 +27137,7 @@
       <c r="J440" s="10" t="n"/>
       <c r="K440" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -27190,7 +27190,7 @@
       <c r="J441" s="10" t="n"/>
       <c r="K441" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -27243,7 +27243,7 @@
       <c r="J442" s="10" t="n"/>
       <c r="K442" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -27296,7 +27296,7 @@
       <c r="J443" s="10" t="n"/>
       <c r="K443" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -27667,7 +27667,7 @@
       <c r="J450" s="9" t="n"/>
       <c r="K450" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -27826,7 +27826,7 @@
       <c r="J453" s="9" t="n"/>
       <c r="K453" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -27985,7 +27985,7 @@
       <c r="J456" s="9" t="n"/>
       <c r="K456" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28091,7 @@
       <c r="J458" s="9" t="n"/>
       <c r="K458" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -28144,7 +28144,7 @@
       <c r="J459" s="9" t="n"/>
       <c r="K459" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -28197,7 +28197,7 @@
       <c r="J460" s="9" t="n"/>
       <c r="K460" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -28250,7 +28250,7 @@
       <c r="J461" s="9" t="n"/>
       <c r="K461" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -28356,7 +28356,7 @@
       <c r="J463" s="9" t="n"/>
       <c r="K463" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -28409,7 +28409,7 @@
       <c r="J464" s="12" t="n"/>
       <c r="K464" s="12" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -28674,7 +28674,7 @@
       <c r="J469" s="12" t="n"/>
       <c r="K469" s="12" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
       <c r="J473" s="9" t="n"/>
       <c r="K473" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -28992,7 +28992,7 @@
       <c r="J475" s="9" t="n"/>
       <c r="K475" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -29045,7 +29045,7 @@
       <c r="J476" s="9" t="n"/>
       <c r="K476" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -29098,7 +29098,7 @@
       <c r="J477" s="9" t="n"/>
       <c r="K477" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -29151,7 +29151,7 @@
       <c r="J478" s="9" t="n"/>
       <c r="K478" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE</t>
         </is>
       </c>
     </row>
@@ -29416,7 +29416,7 @@
       <c r="J483" s="9" t="n"/>
       <c r="K483" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -29469,7 +29469,7 @@
       <c r="J484" s="9" t="n"/>
       <c r="K484" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -29522,7 +29522,7 @@
       <c r="J485" s="9" t="n"/>
       <c r="K485" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -29575,7 +29575,7 @@
       <c r="J486" s="9" t="n"/>
       <c r="K486" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       <c r="J491" s="9" t="n"/>
       <c r="K491" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -29893,7 +29893,7 @@
       <c r="J492" s="9" t="n"/>
       <c r="K492" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -29946,7 +29946,7 @@
       <c r="J493" s="9" t="n"/>
       <c r="K493" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -29999,7 +29999,7 @@
       <c r="J494" s="9" t="n"/>
       <c r="K494" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30158,7 @@
       <c r="J497" s="9" t="n"/>
       <c r="K497" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -30211,7 +30211,7 @@
       <c r="J498" s="9" t="n"/>
       <c r="K498" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       <c r="J500" s="9" t="n"/>
       <c r="K500" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -30370,7 +30370,7 @@
       <c r="J501" s="9" t="n"/>
       <c r="K501" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -30529,7 +30529,7 @@
       <c r="J504" s="9" t="n"/>
       <c r="K504" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30582,7 @@
       <c r="J505" s="9" t="n"/>
       <c r="K505" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -30688,7 +30688,7 @@
       <c r="J507" s="9" t="n"/>
       <c r="K507" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -30847,7 +30847,7 @@
       <c r="J510" s="9" t="n"/>
       <c r="K510" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       <c r="J511" s="9" t="n"/>
       <c r="K511" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -31165,7 +31165,7 @@
       <c r="J516" s="9" t="n"/>
       <c r="K516" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -31218,7 +31218,7 @@
       <c r="J517" s="9" t="n"/>
       <c r="K517" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -31271,7 +31271,7 @@
       <c r="J518" s="9" t="n"/>
       <c r="K518" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -31324,7 +31324,7 @@
       <c r="J519" s="9" t="n"/>
       <c r="K519" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -31589,7 +31589,7 @@
       <c r="J524" s="9" t="n"/>
       <c r="K524" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -31642,7 +31642,7 @@
       <c r="J525" s="9" t="n"/>
       <c r="K525" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -31748,7 +31748,7 @@
       <c r="J527" s="9" t="n"/>
       <c r="K527" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -32119,7 +32119,7 @@
       <c r="J534" s="9" t="n"/>
       <c r="K534" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -32172,7 +32172,7 @@
       <c r="J535" s="9" t="n"/>
       <c r="K535" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -32225,7 +32225,7 @@
       <c r="J536" s="9" t="n"/>
       <c r="K536" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       <c r="J538" s="9" t="n"/>
       <c r="K538" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -32384,7 +32384,7 @@
       <c r="J539" s="9" t="n"/>
       <c r="K539" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -32702,7 +32702,7 @@
       <c r="J545" s="9" t="n"/>
       <c r="K545" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -32808,7 +32808,7 @@
       <c r="J547" s="9" t="n"/>
       <c r="K547" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -32861,7 +32861,7 @@
       <c r="J548" s="9" t="n"/>
       <c r="K548" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -33126,7 +33126,7 @@
       <c r="J553" s="9" t="n"/>
       <c r="K553" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -33232,7 +33232,7 @@
       <c r="J555" s="10" t="n"/>
       <c r="K555" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -33285,7 +33285,7 @@
       <c r="J556" s="10" t="n"/>
       <c r="K556" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -33338,7 +33338,7 @@
       <c r="J557" s="10" t="n"/>
       <c r="K557" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -33391,7 +33391,7 @@
       <c r="J558" s="10" t="n"/>
       <c r="K558" s="10" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       <c r="J560" s="10" t="n"/>
       <c r="K560" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -33603,7 +33603,7 @@
       <c r="J562" s="10" t="n"/>
       <c r="K562" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -33656,7 +33656,7 @@
       <c r="J563" s="10" t="n"/>
       <c r="K563" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -33762,7 +33762,7 @@
       <c r="J565" s="10" t="n"/>
       <c r="K565" s="10" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -34027,7 +34027,7 @@
       <c r="J570" s="10" t="n"/>
       <c r="K570" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       <c r="J571" s="10" t="n"/>
       <c r="K571" s="10" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -34292,7 +34292,7 @@
       <c r="J575" s="10" t="n"/>
       <c r="K575" s="10" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -34345,7 +34345,7 @@
       <c r="J576" s="9" t="n"/>
       <c r="K576" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -34398,7 +34398,7 @@
       <c r="J577" s="9" t="n"/>
       <c r="K577" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -34663,7 +34663,7 @@
       <c r="J582" s="9" t="n"/>
       <c r="K582" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -34716,7 +34716,7 @@
       <c r="J583" s="9" t="n"/>
       <c r="K583" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       <c r="J588" s="9" t="n"/>
       <c r="K588" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -35034,7 +35034,7 @@
       <c r="J589" s="9" t="n"/>
       <c r="K589" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -35087,7 +35087,7 @@
       <c r="J590" s="9" t="n"/>
       <c r="K590" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       <c r="J592" s="9" t="n"/>
       <c r="K592" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -35246,7 +35246,7 @@
       <c r="J593" s="9" t="n"/>
       <c r="K593" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -35299,7 +35299,7 @@
       <c r="J594" s="9" t="n"/>
       <c r="K594" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -35458,7 +35458,7 @@
       <c r="J597" s="9" t="n"/>
       <c r="K597" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE</t>
         </is>
       </c>
     </row>
@@ -35617,7 +35617,7 @@
       <c r="J600" s="9" t="n"/>
       <c r="K600" s="9" t="inlineStr">
         <is>
-          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE (closest)</t>
+          <t>ENVS228 PHYSICAL GEOGRAPHY FIELDWORK COURSE</t>
         </is>
       </c>
     </row>
@@ -35988,7 +35988,7 @@
       <c r="J607" s="9" t="n"/>
       <c r="K607" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -36041,7 +36041,7 @@
       <c r="J608" s="9" t="n"/>
       <c r="K608" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -36200,7 +36200,7 @@
       <c r="J611" s="9" t="n"/>
       <c r="K611" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -36465,7 +36465,7 @@
       <c r="J616" s="9" t="n"/>
       <c r="K616" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -36518,7 +36518,7 @@
       <c r="J617" s="9" t="n"/>
       <c r="K617" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -36571,7 +36571,7 @@
       <c r="J618" s="9" t="n"/>
       <c r="K618" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36624,7 @@
       <c r="J619" s="9" t="n"/>
       <c r="K619" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -36677,7 +36677,7 @@
       <c r="J620" s="9" t="n"/>
       <c r="K620" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -36783,7 +36783,7 @@
       <c r="J622" s="9" t="n"/>
       <c r="K622" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -36995,7 +36995,7 @@
       <c r="J626" s="9" t="n"/>
       <c r="K626" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -37101,7 +37101,7 @@
       <c r="J628" s="9" t="n"/>
       <c r="K628" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -37154,7 +37154,7 @@
       <c r="J629" s="9" t="n"/>
       <c r="K629" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -37207,7 +37207,7 @@
       <c r="J630" s="9" t="n"/>
       <c r="K630" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -37260,7 +37260,7 @@
       <c r="J631" s="9" t="n"/>
       <c r="K631" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -37366,7 +37366,7 @@
       <c r="J633" s="9" t="n"/>
       <c r="K633" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -37419,7 +37419,7 @@
       <c r="J634" s="9" t="n"/>
       <c r="K634" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -37472,7 +37472,7 @@
       <c r="J635" s="9" t="n"/>
       <c r="K635" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -37578,7 +37578,7 @@
       <c r="J637" s="9" t="n"/>
       <c r="K637" s="9" t="inlineStr">
         <is>
-          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION (closest)</t>
+          <t>ENVS264 POLITICAL ECONOMIES OF GLOBALISATION</t>
         </is>
       </c>
     </row>
@@ -37631,7 +37631,7 @@
       <c r="J638" s="9" t="n"/>
       <c r="K638" s="9" t="inlineStr">
         <is>
-          <t>ENVS223 AN INTRODUCTION TO ENVIRONMENTAL HISTORY (closest - new module, no direct equivalent)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -37843,7 +37843,7 @@
       <c r="J642" s="9" t="n"/>
       <c r="K642" s="9" t="inlineStr">
         <is>
-          <t>ENVS231 CLIMATOLOGY / ENVS217 CATCHMENT HYDROLOGY (closest)</t>
+          <t>ENVS217 CATCHMENT HYDROLOGY</t>
         </is>
       </c>
     </row>
@@ -38002,7 +38002,7 @@
       <c r="J645" s="9" t="n"/>
       <c r="K645" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -38055,7 +38055,7 @@
       <c r="J646" s="9" t="n"/>
       <c r="K646" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -38108,7 +38108,7 @@
       <c r="J647" s="9" t="n"/>
       <c r="K647" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -38161,7 +38161,7 @@
       <c r="J648" s="9" t="n"/>
       <c r="K648" s="9" t="inlineStr">
         <is>
-          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY (closest)</t>
+          <t>ENVS218 PLANNING FOR ENVIRONMENTAL SUSTAINABILITY</t>
         </is>
       </c>
     </row>
@@ -38214,7 +38214,7 @@
       <c r="J649" s="9" t="n"/>
       <c r="K649" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -38267,7 +38267,7 @@
       <c r="J650" s="9" t="n"/>
       <c r="K650" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -38320,7 +38320,7 @@
       <c r="J651" s="9" t="n"/>
       <c r="K651" s="9" t="inlineStr">
         <is>
-          <t>ENVS257 GIS FOR HUMAN GEOGRAPHY (closest - no physical-geography GIS module in Year 2)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -38373,7 +38373,7 @@
       <c r="J652" s="9" t="n"/>
       <c r="K652" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>
@@ -38479,7 +38479,7 @@
       <c r="J654" s="9" t="n"/>
       <c r="K654" s="9" t="inlineStr">
         <is>
-          <t>ENVS205 PEOPLE AND PLACE (closest)</t>
+          <t>No ENVS equivalent (new module)</t>
         </is>
       </c>
     </row>

--- a/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
+++ b/curriculum_mapping_2026-27/20261013_CurriculumMapping_Geography.xlsx
@@ -5350,7 +5350,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Not confirmed</t>
+          <t>Fall 2026</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G300" s="9" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G341" s="9" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G342" s="9" t="inlineStr">
@@ -31787,7 +31787,7 @@
       </c>
       <c r="F528" s="9" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G528" s="9" t="inlineStr">
